--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="1131">
   <si>
     <t xml:space="preserve">FIN·OS phone app — parity with the website</t>
   </si>
@@ -215,7 +215,10 @@
     <t xml:space="preserve">S</t>
   </si>
   <si>
-    <t xml:space="preserve">tracker/credit-score</t>
+    <t xml:space="preserve">tools/credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIBIL band, home-loan rate impact, ranked improvement tips; nothing assumed when a figure was not typed; parity-tested vs js/finos-credit-score.js</t>
   </si>
   <si>
     <t xml:space="preserve">T-05</t>
@@ -230,7 +233,7 @@
     <t xml:space="preserve">tracker/crypto</t>
   </si>
   <si>
-    <t xml:space="preserve">Needs live prices (arya-ai CoinGecko route exists)</t>
+    <t xml:space="preserve">Holdings, P&amp;L, 31.2% tax on each coin's gain, 1% TDS what-if; prices are typed (never fetched); parity-tested vs js/finos-crypto-tracker.js</t>
   </si>
   <si>
     <t xml:space="preserve">T-06</t>
@@ -245,6 +248,9 @@
     <t xml:space="preserve">tools/debt</t>
   </si>
   <si>
+    <t xml:space="preserve">Avalanche vs snowball + home-loan prepayment impact; shares balances with Net Worth; parity-tested vs js/finos-debt-optimizer.js</t>
+  </si>
+  <si>
     <t xml:space="preserve">T-07</t>
   </si>
   <si>
@@ -278,10 +284,10 @@
     <t xml:space="preserve">html/fd-tracker.html</t>
   </si>
   <si>
-    <t xml:space="preserve">tracker/fd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feeds net worth</t>
+    <t xml:space="preserve">tracker/fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FD, RD, PPF, NSC, SCSS, Sukanya, bonds, post office; same finos_fd_portfolio key as the web; parity-tested; RD 0% division guarded</t>
   </si>
   <si>
     <t xml:space="preserve">T-10</t>
@@ -296,10 +302,10 @@
     <t xml:space="preserve">L</t>
   </si>
   <si>
-    <t xml:space="preserve">tracker/calendar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subscriptions, SIPs, renewals, tax dates; needs local notifications</t>
+    <t xml:space="preserve">tools/calendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month grid, day detail, coming-up list, summary cards: SIP, deposit maturities (real terms), insurance, goals, subscriptions, tax dates; parity-tested. Phone notifications NOT built: need an OS notification permission, which the privacy guard test currently forbids (owner decision).</t>
   </si>
   <si>
     <t xml:space="preserve">T-11</t>
@@ -341,6 +347,9 @@
     <t xml:space="preserve">tracker/gold</t>
   </si>
   <si>
+    <t xml:space="preserve">Physical, SGB, gold ETF, gold MF; user-typed price only (no invented rate); coupon; parity-tested vs js/finos-gold-tracker.js</t>
+  </si>
+  <si>
     <t xml:space="preserve">T-14</t>
   </si>
   <si>
@@ -350,10 +359,10 @@
     <t xml:space="preserve">html/home-loan.html</t>
   </si>
   <si>
-    <t xml:space="preserve">tools/home-loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amortisation schedule + 24(b)/80C benefits</t>
+    <t xml:space="preserve">tools/homeloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMI, amortisation, affordability, 24(b)/80C deductions, prepayment impact; parity-tested. Website's PMAY-CLSS 'eligible' banner deliberately not ported (scheme bands ended); writes loan keys only on 'Save as my home loan'.</t>
   </si>
   <si>
     <t xml:space="preserve">T-15</t>
@@ -518,6 +527,9 @@
     <t xml:space="preserve">tools/salary</t>
   </si>
   <si>
+    <t xml:space="preserve">CTC breakup → gross, HRA three-way minimum, tax in both regimes, take-home, restructuring tips; parity-tested. Take-home becomes income only on tap (the website overwrites finos_monthly_income on every render).</t>
+  </si>
+  <si>
     <t xml:space="preserve">T-28</t>
   </si>
   <si>
@@ -527,7 +539,10 @@
     <t xml:space="preserve">html/sip-stepup.html</t>
   </si>
   <si>
-    <t xml:space="preserve">tools/sip-stepup</t>
+    <t xml:space="preserve">tools/stepup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat vs stepped-up SIP, scenario cards (5/10/15/20%), corpus chart, year table, milestones; parity-tested vs js/finos-sip-stepup.js incl. out-of-range inputs</t>
   </si>
   <si>
     <t xml:space="preserve">T-29</t>
@@ -569,7 +584,7 @@
     <t xml:space="preserve">tools/tax</t>
   </si>
   <si>
-    <t xml:space="preserve">FinosTaxCore.savingsPlan() is not ported yet; taxNew/taxOld/best are</t>
+    <t xml:space="preserve">Tax Savings Tracker done: regime compare, deduction headroom per section, break-even deductions, saves finos_tax_savings (parity-tested savingsPlan). Tax Planner (HRA, surcharge, capital gains: finos-tax-calc.js) still to build.</t>
   </si>
   <si>
     <t xml:space="preserve">T-32</t>
@@ -599,7 +614,7 @@
     <t xml:space="preserve">tools/leak</t>
   </si>
   <si>
-    <t xml:space="preserve">Money Score uses finos_leak_monthly if present</t>
+    <t xml:space="preserve">Monthly leak from the ledger + subscriptions, 10/20/30-year future value, redirect share; parity-tested vs js/finos-leak.js</t>
   </si>
   <si>
     <t xml:space="preserve">T-34</t>
@@ -2663,21 +2678,24 @@
     <t xml:space="preserve">js/finos-import.js</t>
   </si>
   <si>
+    <t xml:space="preserve">tracker/holdings-import (Portfolio ⇪ Import)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zerodha / Groww / generic CSV parsed identically to js/finos-import.js; rows become Portfolio holdings (replace units + avg cost, never add twice); holdings with no ticker/scheme code keep the broker price. CAS PDF import (S-03) still needs the document-ai backend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio: CAS statement import (PDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">js/finos-import.js + document-ai/cas_import.py</t>
+  </si>
+  <si>
     <t xml:space="preserve">portfolio/import</t>
   </si>
   <si>
-    <t xml:space="preserve">Reuse the CSV helpers already ported for statements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio: CAS statement import (PDF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">js/finos-import.js + document-ai/cas_import.py</t>
-  </si>
-  <si>
     <t xml:space="preserve">Needs the document-ai backend</t>
   </si>
   <si>
@@ -2840,7 +2858,7 @@
     <t xml:space="preserve">js/arya-guardrails.js</t>
   </si>
   <si>
-    <t xml:space="preserve">Port the pure guardrail rules; important before store release</t>
+    <t xml:space="preserve">Same rules and wording as js/arya-guardrails.js (parity-tested on 420+ pairs); tax-evasion requests are refused on the phone before any network call; notes are appended to finished or stopped answers.</t>
   </si>
   <si>
     <t xml:space="preserve">A-08</t>
@@ -3312,6 +3330,63 @@
   </si>
   <si>
     <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-31 (savings tracker), T-33, T-09, T-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax Savings (deduction headroom vs regime), Future Loss, Deposits &amp; fixed income, Debt payoff (avalanche / snowball)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">savingsPlan identical to the website on 2,000 random cases; leak on 800 ledgers; FD on 1,500 entries; debt on 600 loan sets; preview run of all four screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-27, T-28, T-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary structure (CTC → take-home, HRA, tips), SIP step-up planner, Home loan EMI &amp; prepayment planner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary 1,500 random salaries + tips identical to the website; step-up 1,500 inputs incl. junk; home loan 1,200 loans + prepayment; preview run of all three screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-13, T-10 (calendar view)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold tracker; Financial calendar (month grid, upcoming, summary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold total/coupon identical to the website on 400 portfolios; calendar events identical on 150 random households with a frozen clock; tax dates identical over 4 ranges; preview run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-02, A-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broker holdings CSV import (preview, replace-not-add, undo-safe); Arya safety guardrails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holdings parser identical to the website on 700 random files; guardrails identical on 405 user×reply pairs; preview run: import into Portfolio, evasion refused with no /api/chat request, normal answer streams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-04, T-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit score tracker; Crypto tracker (found in the tree from a parallel session, verified and logged here)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both screens rendered in the preview without console errors; their parity tests are part of the 146</t>
   </si>
   <si>
     <t xml:space="preserve">Term</t>
@@ -4016,15 +4091,15 @@
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A5,'Parity Tracker'!$E$2:$E$255,"Done")</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A5,'Parity Tracker'!$E$2:$E$255,"Partial")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A5,'Parity Tracker'!$E$2:$E$255,"Pending")</f>
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A5,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
@@ -4040,7 +4115,7 @@
       </c>
       <c r="H5" s="7" t="n">
         <f aca="false">IF((G5-F5)=0,0,(B5+0.5*C5)/(G5-F5))</f>
-        <v>0.333333333333333</v>
+        <v>0.58974358974359</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4148,7 +4223,7 @@
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A9,'Parity Tracker'!$E$2:$E$255,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A9,'Parity Tracker'!$E$2:$E$255,"Partial")</f>
@@ -4156,7 +4231,7 @@
       </c>
       <c r="D9" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A9,'Parity Tracker'!$E$2:$E$255,"Pending")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A9,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
@@ -4172,7 +4247,7 @@
       </c>
       <c r="H9" s="7" t="n">
         <f aca="false">IF((G9-F9)=0,0,(B9+0.5*C9)/(G9-F9))</f>
-        <v>0.111111111111111</v>
+        <v>0.222222222222222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4181,7 +4256,7 @@
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A10,'Parity Tracker'!$E$2:$E$255,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A10,'Parity Tracker'!$E$2:$E$255,"Partial")</f>
@@ -4189,7 +4264,7 @@
       </c>
       <c r="D10" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A10,'Parity Tracker'!$E$2:$E$255,"Pending")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A10,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
@@ -4205,7 +4280,7 @@
       </c>
       <c r="H10" s="7" t="n">
         <f aca="false">IF((G10-F10)=0,0,(B10+0.5*C10)/(G10-F10))</f>
-        <v>0.111111111111111</v>
+        <v>0.222222222222222</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4280,15 +4355,15 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">SUM(B5:B12)</f>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">SUM(C5:C12)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">SUM(D5:D12)</f>
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">SUM(E5:E12)</f>
@@ -4304,7 +4379,7 @@
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">IF((G13-F13)=0,0,(B13+0.5*C13)/(G13-F13))</f>
-        <v>0.107142857142857</v>
+        <v>0.154761904761905</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4341,7 +4416,7 @@
       </c>
       <c r="B18" s="5" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$F$2:$F$255,$A18,'Parity Tracker'!$E$2:$E$255,"Partial")+COUNTIFS('Parity Tracker'!$F$2:$F$255,$A18,'Parity Tracker'!$E$2:$E$255,"Pending")+COUNTIFS('Parity Tracker'!$F$2:$F$255,$A18,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>26</v>
@@ -4353,7 +4428,7 @@
       </c>
       <c r="B19" s="5" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$F$2:$F$255,$A19,'Parity Tracker'!$E$2:$E$255,"Partial")+COUNTIFS('Parity Tracker'!$F$2:$F$255,$A19,'Parity Tracker'!$E$2:$E$255,"Pending")+COUNTIFS('Parity Tracker'!$F$2:$F$255,$A19,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>28</v>
@@ -4559,7 +4634,7 @@
         <v>60</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>27</v>
@@ -4571,26 +4646,28 @@
       <c r="I5" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="14"/>
+      <c r="J5" s="14" t="s">
+        <v>63</v>
+      </c>
       <c r="K5" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>27</v>
@@ -4600,10 +4677,10 @@
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>47</v>
@@ -4611,19 +4688,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>25</v>
@@ -4635,25 +4712,27 @@
         <v>7</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>73</v>
+      </c>
       <c r="K7" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>3</v>
@@ -4666,7 +4745,7 @@
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="14" t="s">
@@ -4675,16 +4754,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>3</v>
@@ -4697,7 +4776,7 @@
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="14" t="s">
@@ -4706,19 +4785,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>25</v>
@@ -4730,10 +4809,10 @@
         <v>9</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>47</v>
@@ -4741,34 +4820,34 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H11" s="14" t="n">
         <v>11</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>47</v>
@@ -4776,16 +4855,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>7</v>
@@ -4799,7 +4878,7 @@
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K12" s="14" t="s">
         <v>47</v>
@@ -4807,16 +4886,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>4</v>
@@ -4829,10 +4908,10 @@
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>47</v>
@@ -4840,19 +4919,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>25</v>
@@ -4864,10 +4943,10 @@
         <v>10</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>47</v>
@@ -4875,19 +4954,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" s="14" t="s">
         <v>25</v>
@@ -4899,10 +4978,10 @@
         <v>8</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>47</v>
@@ -4910,16 +4989,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>4</v>
@@ -4932,10 +5011,10 @@
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>47</v>
@@ -4943,16 +5022,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>5</v>
@@ -4965,10 +5044,10 @@
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>47</v>
@@ -4976,16 +5055,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>4</v>
@@ -4998,10 +5077,10 @@
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>47</v>
@@ -5009,16 +5088,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>5</v>
@@ -5031,7 +5110,7 @@
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="14" t="s">
@@ -5040,16 +5119,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>5</v>
@@ -5058,11 +5137,11 @@
         <v>27</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="14" t="s">
@@ -5071,16 +5150,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>3</v>
@@ -5093,7 +5172,7 @@
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="14" t="s">
@@ -5102,16 +5181,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>3</v>
@@ -5124,7 +5203,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="14" t="s">
@@ -5133,16 +5212,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>5</v>
@@ -5155,7 +5234,7 @@
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="14" t="s">
@@ -5164,16 +5243,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>5</v>
@@ -5186,7 +5265,7 @@
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J24" s="14"/>
       <c r="K24" s="14" t="s">
@@ -5195,16 +5274,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>3</v>
@@ -5217,7 +5296,7 @@
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J25" s="14"/>
       <c r="K25" s="14" t="s">
@@ -5226,16 +5305,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>5</v>
@@ -5248,7 +5327,7 @@
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J26" s="14"/>
       <c r="K26" s="14" t="s">
@@ -5257,16 +5336,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>3</v>
@@ -5275,16 +5354,16 @@
         <v>25</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H27" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>47</v>
@@ -5292,19 +5371,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>25</v>
@@ -5316,10 +5395,10 @@
         <v>5</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>47</v>
@@ -5327,19 +5406,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>25</v>
@@ -5351,25 +5430,27 @@
         <v>6</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="J29" s="14"/>
+        <v>170</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>171</v>
+      </c>
       <c r="K29" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>5</v>
@@ -5382,10 +5463,10 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="14" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K30" s="14" t="s">
         <v>47</v>
@@ -5393,16 +5474,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>5</v>
@@ -5415,7 +5496,7 @@
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="14" t="s">
@@ -5424,34 +5505,34 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H32" s="14" t="n">
         <v>4</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K32" s="14" t="s">
         <v>47</v>
@@ -5459,16 +5540,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>3</v>
@@ -5477,14 +5558,14 @@
         <v>25</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K33" s="14" t="s">
         <v>47</v>
@@ -5492,19 +5573,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>25</v>
@@ -5516,10 +5597,10 @@
         <v>12</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K34" s="14" t="s">
         <v>47</v>
@@ -5527,16 +5608,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>3</v>
@@ -5549,7 +5630,7 @@
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J35" s="14"/>
       <c r="K35" s="14" t="s">
@@ -5558,16 +5639,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>3</v>
@@ -5576,14 +5657,14 @@
         <v>25</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>47</v>
@@ -5591,16 +5672,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>3</v>
@@ -5613,7 +5694,7 @@
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="14" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="14" t="s">
@@ -5622,16 +5703,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>5</v>
@@ -5644,7 +5725,7 @@
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="14" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="J38" s="14"/>
       <c r="K38" s="14" t="s">
@@ -5653,16 +5734,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>5</v>
@@ -5671,14 +5752,14 @@
         <v>29</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H39" s="14"/>
       <c r="I39" s="14" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K39" s="14" t="s">
         <v>47</v>
@@ -5686,16 +5767,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>5</v>
@@ -5708,7 +5789,7 @@
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="14" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="J40" s="14"/>
       <c r="K40" s="14" t="s">
@@ -5717,16 +5798,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>5</v>
@@ -5735,14 +5816,14 @@
         <v>29</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="14" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K41" s="14" t="s">
         <v>47</v>
@@ -5750,16 +5831,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>5</v>
@@ -5772,10 +5853,10 @@
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="14" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K42" s="14" t="s">
         <v>47</v>
@@ -5783,16 +5864,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>5</v>
@@ -5805,10 +5886,10 @@
       </c>
       <c r="H43" s="14"/>
       <c r="I43" s="14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K43" s="14" t="s">
         <v>47</v>
@@ -5816,16 +5897,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>5</v>
@@ -5838,10 +5919,10 @@
       </c>
       <c r="H44" s="14"/>
       <c r="I44" s="14" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K44" s="14" t="s">
         <v>47</v>
@@ -5849,16 +5930,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>5</v>
@@ -5871,10 +5952,10 @@
       </c>
       <c r="H45" s="14"/>
       <c r="I45" s="14" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K45" s="14" t="s">
         <v>47</v>
@@ -5882,16 +5963,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E46" s="14" t="s">
         <v>5</v>
@@ -5904,10 +5985,10 @@
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="14" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K46" s="14" t="s">
         <v>47</v>
@@ -5915,16 +5996,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>5</v>
@@ -5937,10 +6018,10 @@
       </c>
       <c r="H47" s="14"/>
       <c r="I47" s="14" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K47" s="14" t="s">
         <v>47</v>
@@ -5948,16 +6029,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>5</v>
@@ -5970,10 +6051,10 @@
       </c>
       <c r="H48" s="14"/>
       <c r="I48" s="14" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K48" s="14" t="s">
         <v>47</v>
@@ -5981,16 +6062,16 @@
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>5</v>
@@ -6003,10 +6084,10 @@
       </c>
       <c r="H49" s="14"/>
       <c r="I49" s="14" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K49" s="14" t="s">
         <v>47</v>
@@ -6014,16 +6095,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>5</v>
@@ -6036,10 +6117,10 @@
       </c>
       <c r="H50" s="14"/>
       <c r="I50" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K50" s="14" t="s">
         <v>47</v>
@@ -6047,16 +6128,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>5</v>
@@ -6069,10 +6150,10 @@
       </c>
       <c r="H51" s="14"/>
       <c r="I51" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K51" s="14" t="s">
         <v>47</v>
@@ -6080,16 +6161,16 @@
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>5</v>
@@ -6102,10 +6183,10 @@
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="14" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K52" s="14" t="s">
         <v>47</v>
@@ -6113,16 +6194,16 @@
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>5</v>
@@ -6135,10 +6216,10 @@
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K53" s="14" t="s">
         <v>47</v>
@@ -6146,16 +6227,16 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>5</v>
@@ -6168,10 +6249,10 @@
       </c>
       <c r="H54" s="14"/>
       <c r="I54" s="14" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K54" s="14" t="s">
         <v>47</v>
@@ -6179,16 +6260,16 @@
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>5</v>
@@ -6201,10 +6282,10 @@
       </c>
       <c r="H55" s="14"/>
       <c r="I55" s="14" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K55" s="14" t="s">
         <v>47</v>
@@ -6212,16 +6293,16 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>5</v>
@@ -6234,10 +6315,10 @@
       </c>
       <c r="H56" s="14"/>
       <c r="I56" s="14" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K56" s="14" t="s">
         <v>47</v>
@@ -6245,16 +6326,16 @@
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>5</v>
@@ -6267,10 +6348,10 @@
       </c>
       <c r="H57" s="14"/>
       <c r="I57" s="14" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K57" s="14" t="s">
         <v>47</v>
@@ -6278,16 +6359,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>5</v>
@@ -6300,10 +6381,10 @@
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K58" s="14" t="s">
         <v>47</v>
@@ -6311,16 +6392,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>5</v>
@@ -6333,10 +6414,10 @@
       </c>
       <c r="H59" s="14"/>
       <c r="I59" s="14" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K59" s="14" t="s">
         <v>47</v>
@@ -6344,16 +6425,16 @@
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>5</v>
@@ -6366,10 +6447,10 @@
       </c>
       <c r="H60" s="14"/>
       <c r="I60" s="14" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K60" s="14" t="s">
         <v>47</v>
@@ -6377,16 +6458,16 @@
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>5</v>
@@ -6399,10 +6480,10 @@
       </c>
       <c r="H61" s="14"/>
       <c r="I61" s="14" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K61" s="14" t="s">
         <v>47</v>
@@ -6410,16 +6491,16 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>5</v>
@@ -6432,10 +6513,10 @@
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="14" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K62" s="14" t="s">
         <v>47</v>
@@ -6443,16 +6524,16 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>5</v>
@@ -6465,10 +6546,10 @@
       </c>
       <c r="H63" s="14"/>
       <c r="I63" s="14" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K63" s="14" t="s">
         <v>47</v>
@@ -6476,16 +6557,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>5</v>
@@ -6498,10 +6579,10 @@
       </c>
       <c r="H64" s="14"/>
       <c r="I64" s="14" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K64" s="14" t="s">
         <v>47</v>
@@ -6509,16 +6590,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>5</v>
@@ -6531,10 +6612,10 @@
       </c>
       <c r="H65" s="14"/>
       <c r="I65" s="14" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K65" s="14" t="s">
         <v>47</v>
@@ -6542,16 +6623,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>5</v>
@@ -6564,10 +6645,10 @@
       </c>
       <c r="H66" s="14"/>
       <c r="I66" s="14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K66" s="14" t="s">
         <v>47</v>
@@ -6575,16 +6656,16 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>5</v>
@@ -6597,10 +6678,10 @@
       </c>
       <c r="H67" s="14"/>
       <c r="I67" s="14" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="J67" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K67" s="14" t="s">
         <v>47</v>
@@ -6608,16 +6689,16 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>5</v>
@@ -6630,10 +6711,10 @@
       </c>
       <c r="H68" s="14"/>
       <c r="I68" s="14" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K68" s="14" t="s">
         <v>47</v>
@@ -6641,16 +6722,16 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>5</v>
@@ -6663,10 +6744,10 @@
       </c>
       <c r="H69" s="14"/>
       <c r="I69" s="14" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K69" s="14" t="s">
         <v>47</v>
@@ -6674,16 +6755,16 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>5</v>
@@ -6696,10 +6777,10 @@
       </c>
       <c r="H70" s="14"/>
       <c r="I70" s="14" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K70" s="14" t="s">
         <v>47</v>
@@ -6707,16 +6788,16 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>5</v>
@@ -6729,10 +6810,10 @@
       </c>
       <c r="H71" s="14"/>
       <c r="I71" s="14" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K71" s="14" t="s">
         <v>47</v>
@@ -6740,16 +6821,16 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>5</v>
@@ -6762,10 +6843,10 @@
       </c>
       <c r="H72" s="14"/>
       <c r="I72" s="14" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K72" s="14" t="s">
         <v>47</v>
@@ -6773,16 +6854,16 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>5</v>
@@ -6795,10 +6876,10 @@
       </c>
       <c r="H73" s="14"/>
       <c r="I73" s="14" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K73" s="14" t="s">
         <v>47</v>
@@ -6806,16 +6887,16 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B74" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E74" s="14" t="s">
         <v>5</v>
@@ -6828,10 +6909,10 @@
       </c>
       <c r="H74" s="14"/>
       <c r="I74" s="14" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K74" s="14" t="s">
         <v>47</v>
@@ -6839,16 +6920,16 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>5</v>
@@ -6861,10 +6942,10 @@
       </c>
       <c r="H75" s="14"/>
       <c r="I75" s="14" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K75" s="14" t="s">
         <v>47</v>
@@ -6872,16 +6953,16 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E76" s="14" t="s">
         <v>5</v>
@@ -6894,10 +6975,10 @@
       </c>
       <c r="H76" s="14"/>
       <c r="I76" s="14" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K76" s="14" t="s">
         <v>47</v>
@@ -6905,16 +6986,16 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>5</v>
@@ -6927,10 +7008,10 @@
       </c>
       <c r="H77" s="14"/>
       <c r="I77" s="14" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K77" s="14" t="s">
         <v>47</v>
@@ -6938,16 +7019,16 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E78" s="14" t="s">
         <v>5</v>
@@ -6960,10 +7041,10 @@
       </c>
       <c r="H78" s="14"/>
       <c r="I78" s="14" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K78" s="14" t="s">
         <v>47</v>
@@ -6971,16 +7052,16 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>5</v>
@@ -6993,10 +7074,10 @@
       </c>
       <c r="H79" s="14"/>
       <c r="I79" s="14" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K79" s="14" t="s">
         <v>47</v>
@@ -7004,16 +7085,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E80" s="14" t="s">
         <v>5</v>
@@ -7026,10 +7107,10 @@
       </c>
       <c r="H80" s="14"/>
       <c r="I80" s="14" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K80" s="14" t="s">
         <v>47</v>
@@ -7037,16 +7118,16 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E81" s="14" t="s">
         <v>5</v>
@@ -7059,10 +7140,10 @@
       </c>
       <c r="H81" s="14"/>
       <c r="I81" s="14" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K81" s="14" t="s">
         <v>47</v>
@@ -7070,16 +7151,16 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E82" s="14" t="s">
         <v>5</v>
@@ -7092,10 +7173,10 @@
       </c>
       <c r="H82" s="14"/>
       <c r="I82" s="14" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K82" s="14" t="s">
         <v>47</v>
@@ -7103,16 +7184,16 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>5</v>
@@ -7125,10 +7206,10 @@
       </c>
       <c r="H83" s="14"/>
       <c r="I83" s="14" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K83" s="14" t="s">
         <v>47</v>
@@ -7136,16 +7217,16 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E84" s="14" t="s">
         <v>5</v>
@@ -7158,10 +7239,10 @@
       </c>
       <c r="H84" s="14"/>
       <c r="I84" s="14" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K84" s="14" t="s">
         <v>47</v>
@@ -7169,16 +7250,16 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E85" s="14" t="s">
         <v>5</v>
@@ -7191,10 +7272,10 @@
       </c>
       <c r="H85" s="14"/>
       <c r="I85" s="14" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K85" s="14" t="s">
         <v>47</v>
@@ -7202,16 +7283,16 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E86" s="14" t="s">
         <v>5</v>
@@ -7224,10 +7305,10 @@
       </c>
       <c r="H86" s="14"/>
       <c r="I86" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K86" s="14" t="s">
         <v>47</v>
@@ -7235,16 +7316,16 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E87" s="14" t="s">
         <v>5</v>
@@ -7257,10 +7338,10 @@
       </c>
       <c r="H87" s="14"/>
       <c r="I87" s="14" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K87" s="14" t="s">
         <v>47</v>
@@ -7268,16 +7349,16 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E88" s="14" t="s">
         <v>5</v>
@@ -7290,10 +7371,10 @@
       </c>
       <c r="H88" s="14"/>
       <c r="I88" s="14" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K88" s="14" t="s">
         <v>47</v>
@@ -7301,16 +7382,16 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E89" s="14" t="s">
         <v>5</v>
@@ -7323,10 +7404,10 @@
       </c>
       <c r="H89" s="14"/>
       <c r="I89" s="14" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K89" s="14" t="s">
         <v>47</v>
@@ -7334,16 +7415,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B90" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E90" s="14" t="s">
         <v>5</v>
@@ -7356,10 +7437,10 @@
       </c>
       <c r="H90" s="14"/>
       <c r="I90" s="14" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K90" s="14" t="s">
         <v>47</v>
@@ -7367,16 +7448,16 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E91" s="14" t="s">
         <v>5</v>
@@ -7389,10 +7470,10 @@
       </c>
       <c r="H91" s="14"/>
       <c r="I91" s="14" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K91" s="14" t="s">
         <v>47</v>
@@ -7400,16 +7481,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="14" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B92" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E92" s="14" t="s">
         <v>5</v>
@@ -7422,10 +7503,10 @@
       </c>
       <c r="H92" s="14"/>
       <c r="I92" s="14" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K92" s="14" t="s">
         <v>47</v>
@@ -7433,16 +7514,16 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E93" s="14" t="s">
         <v>5</v>
@@ -7455,10 +7536,10 @@
       </c>
       <c r="H93" s="14"/>
       <c r="I93" s="14" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K93" s="14" t="s">
         <v>47</v>
@@ -7466,16 +7547,16 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B94" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E94" s="14" t="s">
         <v>5</v>
@@ -7488,10 +7569,10 @@
       </c>
       <c r="H94" s="14"/>
       <c r="I94" s="14" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K94" s="14" t="s">
         <v>47</v>
@@ -7499,16 +7580,16 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="14" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B95" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E95" s="14" t="s">
         <v>5</v>
@@ -7521,10 +7602,10 @@
       </c>
       <c r="H95" s="14"/>
       <c r="I95" s="14" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K95" s="14" t="s">
         <v>47</v>
@@ -7532,16 +7613,16 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="14" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E96" s="14" t="s">
         <v>5</v>
@@ -7554,10 +7635,10 @@
       </c>
       <c r="H96" s="14"/>
       <c r="I96" s="14" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K96" s="14" t="s">
         <v>47</v>
@@ -7565,16 +7646,16 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E97" s="14" t="s">
         <v>5</v>
@@ -7587,10 +7668,10 @@
       </c>
       <c r="H97" s="14"/>
       <c r="I97" s="14" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K97" s="14" t="s">
         <v>47</v>
@@ -7598,16 +7679,16 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>5</v>
@@ -7620,10 +7701,10 @@
       </c>
       <c r="H98" s="14"/>
       <c r="I98" s="14" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K98" s="14" t="s">
         <v>47</v>
@@ -7631,16 +7712,16 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B99" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>5</v>
@@ -7653,10 +7734,10 @@
       </c>
       <c r="H99" s="14"/>
       <c r="I99" s="14" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K99" s="14" t="s">
         <v>47</v>
@@ -7664,16 +7745,16 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="14" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>5</v>
@@ -7686,10 +7767,10 @@
       </c>
       <c r="H100" s="14"/>
       <c r="I100" s="14" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K100" s="14" t="s">
         <v>47</v>
@@ -7697,16 +7778,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B101" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E101" s="14" t="s">
         <v>5</v>
@@ -7719,10 +7800,10 @@
       </c>
       <c r="H101" s="14"/>
       <c r="I101" s="14" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K101" s="14" t="s">
         <v>47</v>
@@ -7730,16 +7811,16 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="14" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B102" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="E102" s="14" t="s">
         <v>5</v>
@@ -7752,10 +7833,10 @@
       </c>
       <c r="H102" s="14"/>
       <c r="I102" s="14" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K102" s="14" t="s">
         <v>47</v>
@@ -7763,16 +7844,16 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="14" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="E103" s="14" t="s">
         <v>5</v>
@@ -7785,10 +7866,10 @@
       </c>
       <c r="H103" s="14"/>
       <c r="I103" s="14" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="J103" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K103" s="14" t="s">
         <v>47</v>
@@ -7796,16 +7877,16 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="14" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E104" s="14" t="s">
         <v>5</v>
@@ -7818,10 +7899,10 @@
       </c>
       <c r="H104" s="14"/>
       <c r="I104" s="14" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K104" s="14" t="s">
         <v>47</v>
@@ -7829,16 +7910,16 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E105" s="14" t="s">
         <v>3</v>
@@ -7851,10 +7932,10 @@
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="14" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K105" s="14" t="s">
         <v>47</v>
@@ -7862,16 +7943,16 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="14" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>5</v>
@@ -7884,10 +7965,10 @@
       </c>
       <c r="H106" s="14"/>
       <c r="I106" s="14" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K106" s="14" t="s">
         <v>47</v>
@@ -7895,16 +7976,16 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="14" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B107" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>5</v>
@@ -7917,10 +7998,10 @@
       </c>
       <c r="H107" s="14"/>
       <c r="I107" s="14" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K107" s="14" t="s">
         <v>47</v>
@@ -7928,16 +8009,16 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="14" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B108" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="E108" s="14" t="s">
         <v>5</v>
@@ -7950,10 +8031,10 @@
       </c>
       <c r="H108" s="14"/>
       <c r="I108" s="14" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K108" s="14" t="s">
         <v>47</v>
@@ -7961,16 +8042,16 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="14" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E109" s="14" t="s">
         <v>5</v>
@@ -7983,10 +8064,10 @@
       </c>
       <c r="H109" s="14"/>
       <c r="I109" s="14" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K109" s="14" t="s">
         <v>47</v>
@@ -7994,16 +8075,16 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="14" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B110" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>5</v>
@@ -8016,10 +8097,10 @@
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="14" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K110" s="14" t="s">
         <v>47</v>
@@ -8027,16 +8108,16 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="14" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B111" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="E111" s="14" t="s">
         <v>5</v>
@@ -8049,10 +8130,10 @@
       </c>
       <c r="H111" s="14"/>
       <c r="I111" s="14" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="J111" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K111" s="14" t="s">
         <v>47</v>
@@ -8060,16 +8141,16 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="14" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B112" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="E112" s="14" t="s">
         <v>5</v>
@@ -8082,10 +8163,10 @@
       </c>
       <c r="H112" s="14"/>
       <c r="I112" s="14" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K112" s="14" t="s">
         <v>47</v>
@@ -8093,16 +8174,16 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="14" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B113" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="E113" s="14" t="s">
         <v>5</v>
@@ -8115,10 +8196,10 @@
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="14" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="J113" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K113" s="14" t="s">
         <v>47</v>
@@ -8126,16 +8207,16 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="14" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B114" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E114" s="14" t="s">
         <v>5</v>
@@ -8148,10 +8229,10 @@
       </c>
       <c r="H114" s="14"/>
       <c r="I114" s="14" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="J114" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K114" s="14" t="s">
         <v>47</v>
@@ -8159,16 +8240,16 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="14" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B115" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E115" s="14" t="s">
         <v>5</v>
@@ -8181,10 +8262,10 @@
       </c>
       <c r="H115" s="14"/>
       <c r="I115" s="14" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="J115" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K115" s="14" t="s">
         <v>47</v>
@@ -8192,16 +8273,16 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="14" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B116" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="E116" s="14" t="s">
         <v>5</v>
@@ -8214,10 +8295,10 @@
       </c>
       <c r="H116" s="14"/>
       <c r="I116" s="14" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K116" s="14" t="s">
         <v>47</v>
@@ -8225,16 +8306,16 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="14" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="E117" s="14" t="s">
         <v>5</v>
@@ -8247,10 +8328,10 @@
       </c>
       <c r="H117" s="14"/>
       <c r="I117" s="14" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="J117" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K117" s="14" t="s">
         <v>47</v>
@@ -8258,16 +8339,16 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="14" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E118" s="14" t="s">
         <v>5</v>
@@ -8280,10 +8361,10 @@
       </c>
       <c r="H118" s="14"/>
       <c r="I118" s="14" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="J118" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K118" s="14" t="s">
         <v>47</v>
@@ -8291,16 +8372,16 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="14" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E119" s="14" t="s">
         <v>5</v>
@@ -8313,10 +8394,10 @@
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="14" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="J119" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K119" s="14" t="s">
         <v>47</v>
@@ -8324,16 +8405,16 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="14" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E120" s="14" t="s">
         <v>3</v>
@@ -8346,10 +8427,10 @@
       </c>
       <c r="H120" s="14"/>
       <c r="I120" s="14" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="J120" s="14" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K120" s="14" t="s">
         <v>47</v>
@@ -8357,16 +8438,16 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="14" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B121" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="E121" s="14" t="s">
         <v>5</v>
@@ -8379,10 +8460,10 @@
       </c>
       <c r="H121" s="14"/>
       <c r="I121" s="14" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="J121" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K121" s="14" t="s">
         <v>47</v>
@@ -8390,16 +8471,16 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="14" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B122" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E122" s="14" t="s">
         <v>5</v>
@@ -8412,10 +8493,10 @@
       </c>
       <c r="H122" s="14"/>
       <c r="I122" s="14" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="J122" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K122" s="14" t="s">
         <v>47</v>
@@ -8423,16 +8504,16 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="14" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E123" s="14" t="s">
         <v>5</v>
@@ -8445,10 +8526,10 @@
       </c>
       <c r="H123" s="14"/>
       <c r="I123" s="14" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K123" s="14" t="s">
         <v>47</v>
@@ -8456,16 +8537,16 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="14" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B124" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E124" s="14" t="s">
         <v>5</v>
@@ -8478,10 +8559,10 @@
       </c>
       <c r="H124" s="14"/>
       <c r="I124" s="14" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="J124" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K124" s="14" t="s">
         <v>47</v>
@@ -8489,16 +8570,16 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="14" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B125" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="E125" s="14" t="s">
         <v>5</v>
@@ -8511,10 +8592,10 @@
       </c>
       <c r="H125" s="14"/>
       <c r="I125" s="14" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="J125" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K125" s="14" t="s">
         <v>47</v>
@@ -8522,16 +8603,16 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="14" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="B126" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="E126" s="14" t="s">
         <v>5</v>
@@ -8544,10 +8625,10 @@
       </c>
       <c r="H126" s="14"/>
       <c r="I126" s="14" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="J126" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K126" s="14" t="s">
         <v>47</v>
@@ -8555,16 +8636,16 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="14" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B127" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E127" s="14" t="s">
         <v>5</v>
@@ -8577,10 +8658,10 @@
       </c>
       <c r="H127" s="14"/>
       <c r="I127" s="14" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="J127" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K127" s="14" t="s">
         <v>47</v>
@@ -8588,16 +8669,16 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="14" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B128" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E128" s="14" t="s">
         <v>5</v>
@@ -8610,10 +8691,10 @@
       </c>
       <c r="H128" s="14"/>
       <c r="I128" s="14" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="J128" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K128" s="14" t="s">
         <v>47</v>
@@ -8621,16 +8702,16 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="14" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B129" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E129" s="14" t="s">
         <v>5</v>
@@ -8643,10 +8724,10 @@
       </c>
       <c r="H129" s="14"/>
       <c r="I129" s="14" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="J129" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K129" s="14" t="s">
         <v>47</v>
@@ -8654,16 +8735,16 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="14" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E130" s="14" t="s">
         <v>5</v>
@@ -8676,10 +8757,10 @@
       </c>
       <c r="H130" s="14"/>
       <c r="I130" s="14" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="J130" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K130" s="14" t="s">
         <v>47</v>
@@ -8687,16 +8768,16 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="14" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B131" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E131" s="14" t="s">
         <v>5</v>
@@ -8709,10 +8790,10 @@
       </c>
       <c r="H131" s="14"/>
       <c r="I131" s="14" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K131" s="14" t="s">
         <v>47</v>
@@ -8720,16 +8801,16 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="14" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B132" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E132" s="14" t="s">
         <v>5</v>
@@ -8742,10 +8823,10 @@
       </c>
       <c r="H132" s="14"/>
       <c r="I132" s="14" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="J132" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K132" s="14" t="s">
         <v>47</v>
@@ -8753,16 +8834,16 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="14" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B133" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="E133" s="14" t="s">
         <v>5</v>
@@ -8775,10 +8856,10 @@
       </c>
       <c r="H133" s="14"/>
       <c r="I133" s="14" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K133" s="14" t="s">
         <v>47</v>
@@ -8786,16 +8867,16 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B134" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="E134" s="14" t="s">
         <v>5</v>
@@ -8808,10 +8889,10 @@
       </c>
       <c r="H134" s="14"/>
       <c r="I134" s="14" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="J134" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K134" s="14" t="s">
         <v>47</v>
@@ -8819,16 +8900,16 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="14" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B135" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E135" s="14" t="s">
         <v>5</v>
@@ -8841,10 +8922,10 @@
       </c>
       <c r="H135" s="14"/>
       <c r="I135" s="14" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K135" s="14" t="s">
         <v>47</v>
@@ -8852,16 +8933,16 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="14" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B136" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="E136" s="14" t="s">
         <v>5</v>
@@ -8874,10 +8955,10 @@
       </c>
       <c r="H136" s="14"/>
       <c r="I136" s="14" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K136" s="14" t="s">
         <v>47</v>
@@ -8885,16 +8966,16 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="14" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="E137" s="14" t="s">
         <v>5</v>
@@ -8907,10 +8988,10 @@
       </c>
       <c r="H137" s="14"/>
       <c r="I137" s="14" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="J137" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K137" s="14" t="s">
         <v>47</v>
@@ -8918,16 +8999,16 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="14" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B138" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="E138" s="14" t="s">
         <v>5</v>
@@ -8940,10 +9021,10 @@
       </c>
       <c r="H138" s="14"/>
       <c r="I138" s="14" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K138" s="14" t="s">
         <v>47</v>
@@ -8951,16 +9032,16 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="14" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B139" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="E139" s="14" t="s">
         <v>5</v>
@@ -8973,10 +9054,10 @@
       </c>
       <c r="H139" s="14"/>
       <c r="I139" s="14" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="J139" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K139" s="14" t="s">
         <v>47</v>
@@ -8984,16 +9065,16 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="14" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B140" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="E140" s="14" t="s">
         <v>5</v>
@@ -9006,10 +9087,10 @@
       </c>
       <c r="H140" s="14"/>
       <c r="I140" s="14" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="J140" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K140" s="14" t="s">
         <v>47</v>
@@ -9017,16 +9098,16 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="14" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B141" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D141" s="14" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E141" s="14" t="s">
         <v>5</v>
@@ -9039,10 +9120,10 @@
       </c>
       <c r="H141" s="14"/>
       <c r="I141" s="14" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="J141" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K141" s="14" t="s">
         <v>47</v>
@@ -9050,16 +9131,16 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="14" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B142" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D142" s="14" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="E142" s="14" t="s">
         <v>5</v>
@@ -9072,10 +9153,10 @@
       </c>
       <c r="H142" s="14"/>
       <c r="I142" s="14" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="J142" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K142" s="14" t="s">
         <v>47</v>
@@ -9083,16 +9164,16 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="14" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B143" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D143" s="14" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="E143" s="14" t="s">
         <v>5</v>
@@ -9105,10 +9186,10 @@
       </c>
       <c r="H143" s="14"/>
       <c r="I143" s="14" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="J143" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K143" s="14" t="s">
         <v>47</v>
@@ -9116,16 +9197,16 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="14" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B144" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="E144" s="14" t="s">
         <v>5</v>
@@ -9138,10 +9219,10 @@
       </c>
       <c r="H144" s="14"/>
       <c r="I144" s="14" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="J144" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K144" s="14" t="s">
         <v>47</v>
@@ -9149,16 +9230,16 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="14" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="B145" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D145" s="14" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E145" s="14" t="s">
         <v>5</v>
@@ -9171,10 +9252,10 @@
       </c>
       <c r="H145" s="14"/>
       <c r="I145" s="14" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="J145" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K145" s="14" t="s">
         <v>47</v>
@@ -9182,16 +9263,16 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="14" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B146" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D146" s="14" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="E146" s="14" t="s">
         <v>5</v>
@@ -9204,10 +9285,10 @@
       </c>
       <c r="H146" s="14"/>
       <c r="I146" s="14" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="J146" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K146" s="14" t="s">
         <v>47</v>
@@ -9215,16 +9296,16 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="14" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B147" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="E147" s="14" t="s">
         <v>5</v>
@@ -9237,7 +9318,7 @@
       </c>
       <c r="H147" s="14"/>
       <c r="I147" s="14" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="J147" s="14"/>
       <c r="K147" s="14" t="s">
@@ -9246,16 +9327,16 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="14" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B148" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="E148" s="14" t="s">
         <v>5</v>
@@ -9268,7 +9349,7 @@
       </c>
       <c r="H148" s="14"/>
       <c r="I148" s="14" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="J148" s="14"/>
       <c r="K148" s="14" t="s">
@@ -9277,16 +9358,16 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="14" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B149" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="E149" s="14" t="s">
         <v>5</v>
@@ -9299,7 +9380,7 @@
       </c>
       <c r="H149" s="14"/>
       <c r="I149" s="14" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="J149" s="14"/>
       <c r="K149" s="14" t="s">
@@ -9308,16 +9389,16 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="14" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B150" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D150" s="14" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="E150" s="14" t="s">
         <v>5</v>
@@ -9330,7 +9411,7 @@
       </c>
       <c r="H150" s="14"/>
       <c r="I150" s="14" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="J150" s="14"/>
       <c r="K150" s="14" t="s">
@@ -9339,16 +9420,16 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="14" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="B151" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="D151" s="14" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="E151" s="14" t="s">
         <v>5</v>
@@ -9361,7 +9442,7 @@
       </c>
       <c r="H151" s="14"/>
       <c r="I151" s="14" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="J151" s="14"/>
       <c r="K151" s="14" t="s">
@@ -9370,16 +9451,16 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="14" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B152" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="E152" s="14" t="s">
         <v>5</v>
@@ -9392,7 +9473,7 @@
       </c>
       <c r="H152" s="14"/>
       <c r="I152" s="14" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="J152" s="14"/>
       <c r="K152" s="14" t="s">
@@ -9401,16 +9482,16 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="14" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="B153" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="D153" s="14" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="E153" s="14" t="s">
         <v>5</v>
@@ -9423,7 +9504,7 @@
       </c>
       <c r="H153" s="14"/>
       <c r="I153" s="14" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="J153" s="14"/>
       <c r="K153" s="14" t="s">
@@ -9432,16 +9513,16 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="14" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B154" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="D154" s="14" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="E154" s="14" t="s">
         <v>5</v>
@@ -9454,7 +9535,7 @@
       </c>
       <c r="H154" s="14"/>
       <c r="I154" s="14" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="J154" s="14"/>
       <c r="K154" s="14" t="s">
@@ -9463,16 +9544,16 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="14" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B155" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="D155" s="14" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="E155" s="14" t="s">
         <v>5</v>
@@ -9485,7 +9566,7 @@
       </c>
       <c r="H155" s="14"/>
       <c r="I155" s="14" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="J155" s="14"/>
       <c r="K155" s="14" t="s">
@@ -9494,16 +9575,16 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="14" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B156" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D156" s="14" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="E156" s="14" t="s">
         <v>5</v>
@@ -9516,7 +9597,7 @@
       </c>
       <c r="H156" s="14"/>
       <c r="I156" s="14" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="J156" s="14"/>
       <c r="K156" s="14" t="s">
@@ -9525,16 +9606,16 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="14" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="B157" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="D157" s="14" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>5</v>
@@ -9547,7 +9628,7 @@
       </c>
       <c r="H157" s="14"/>
       <c r="I157" s="14" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="J157" s="14"/>
       <c r="K157" s="14" t="s">
@@ -9556,16 +9637,16 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="14" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B158" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E158" s="14" t="s">
         <v>5</v>
@@ -9578,7 +9659,7 @@
       </c>
       <c r="H158" s="14"/>
       <c r="I158" s="14" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="J158" s="14"/>
       <c r="K158" s="14" t="s">
@@ -9587,16 +9668,16 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="14" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="B159" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="D159" s="14" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="E159" s="14" t="s">
         <v>5</v>
@@ -9609,7 +9690,7 @@
       </c>
       <c r="H159" s="14"/>
       <c r="I159" s="14" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="J159" s="14"/>
       <c r="K159" s="14" t="s">
@@ -9618,16 +9699,16 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="14" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="B160" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="E160" s="14" t="s">
         <v>5</v>
@@ -9640,7 +9721,7 @@
       </c>
       <c r="H160" s="14"/>
       <c r="I160" s="14" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="J160" s="14"/>
       <c r="K160" s="14" t="s">
@@ -9649,16 +9730,16 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="14" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B161" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="E161" s="14" t="s">
         <v>5</v>
@@ -9671,7 +9752,7 @@
       </c>
       <c r="H161" s="14"/>
       <c r="I161" s="14" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="J161" s="14"/>
       <c r="K161" s="14" t="s">
@@ -9680,16 +9761,16 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="14" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="B162" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="D162" s="14" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="E162" s="14" t="s">
         <v>5</v>
@@ -9702,7 +9783,7 @@
       </c>
       <c r="H162" s="14"/>
       <c r="I162" s="14" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="J162" s="14"/>
       <c r="K162" s="14" t="s">
@@ -9711,16 +9792,16 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="14" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="B163" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="D163" s="14" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="E163" s="14" t="s">
         <v>5</v>
@@ -9733,7 +9814,7 @@
       </c>
       <c r="H163" s="14"/>
       <c r="I163" s="14" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="J163" s="14"/>
       <c r="K163" s="14" t="s">
@@ -9742,16 +9823,16 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="14" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="B164" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="D164" s="14" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="E164" s="14" t="s">
         <v>5</v>
@@ -9764,7 +9845,7 @@
       </c>
       <c r="H164" s="14"/>
       <c r="I164" s="14" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="J164" s="14"/>
       <c r="K164" s="14" t="s">
@@ -9773,16 +9854,16 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="14" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="B165" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="D165" s="14" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="E165" s="14" t="s">
         <v>5</v>
@@ -9795,7 +9876,7 @@
       </c>
       <c r="H165" s="14"/>
       <c r="I165" s="14" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="J165" s="14"/>
       <c r="K165" s="14" t="s">
@@ -9804,16 +9885,16 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="14" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B166" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D166" s="14" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="E166" s="14" t="s">
         <v>5</v>
@@ -9826,7 +9907,7 @@
       </c>
       <c r="H166" s="14"/>
       <c r="I166" s="14" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="J166" s="14"/>
       <c r="K166" s="14" t="s">
@@ -9835,16 +9916,16 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="14" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="B167" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="E167" s="14" t="s">
         <v>5</v>
@@ -9857,7 +9938,7 @@
       </c>
       <c r="H167" s="14"/>
       <c r="I167" s="14" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="J167" s="14"/>
       <c r="K167" s="14" t="s">
@@ -9866,16 +9947,16 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="14" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B168" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E168" s="14" t="s">
         <v>5</v>
@@ -9888,7 +9969,7 @@
       </c>
       <c r="H168" s="14"/>
       <c r="I168" s="14" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="J168" s="14"/>
       <c r="K168" s="14" t="s">
@@ -9897,16 +9978,16 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="14" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="B169" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="E169" s="14" t="s">
         <v>5</v>
@@ -9919,7 +10000,7 @@
       </c>
       <c r="H169" s="14"/>
       <c r="I169" s="14" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="J169" s="14"/>
       <c r="K169" s="14" t="s">
@@ -9928,16 +10009,16 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="14" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B170" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E170" s="14" t="s">
         <v>5</v>
@@ -9950,7 +10031,7 @@
       </c>
       <c r="H170" s="14"/>
       <c r="I170" s="14" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="J170" s="14"/>
       <c r="K170" s="14" t="s">
@@ -9959,16 +10040,16 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="14" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B171" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E171" s="14" t="s">
         <v>5</v>
@@ -9981,7 +10062,7 @@
       </c>
       <c r="H171" s="14"/>
       <c r="I171" s="14" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="J171" s="14"/>
       <c r="K171" s="14" t="s">
@@ -9990,16 +10071,16 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="14" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="B172" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="E172" s="14" t="s">
         <v>5</v>
@@ -10012,7 +10093,7 @@
       </c>
       <c r="H172" s="14"/>
       <c r="I172" s="14" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="J172" s="14"/>
       <c r="K172" s="14" t="s">
@@ -10021,16 +10102,16 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="B173" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="E173" s="14" t="s">
         <v>5</v>
@@ -10043,7 +10124,7 @@
       </c>
       <c r="H173" s="14"/>
       <c r="I173" s="14" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="J173" s="14"/>
       <c r="K173" s="14" t="s">
@@ -10052,16 +10133,16 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="14" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="B174" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="D174" s="14" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="E174" s="14" t="s">
         <v>5</v>
@@ -10074,7 +10155,7 @@
       </c>
       <c r="H174" s="14"/>
       <c r="I174" s="14" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="J174" s="14"/>
       <c r="K174" s="14" t="s">
@@ -10083,16 +10164,16 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="14" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B175" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="D175" s="14" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="E175" s="14" t="s">
         <v>5</v>
@@ -10105,7 +10186,7 @@
       </c>
       <c r="H175" s="14"/>
       <c r="I175" s="14" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="J175" s="14"/>
       <c r="K175" s="14" t="s">
@@ -10114,16 +10195,16 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="14" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="B176" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="D176" s="14" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="E176" s="14" t="s">
         <v>5</v>
@@ -10136,7 +10217,7 @@
       </c>
       <c r="H176" s="14"/>
       <c r="I176" s="14" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="J176" s="14"/>
       <c r="K176" s="14" t="s">
@@ -10145,16 +10226,16 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="14" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B177" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="E177" s="14" t="s">
         <v>5</v>
@@ -10167,7 +10248,7 @@
       </c>
       <c r="H177" s="14"/>
       <c r="I177" s="14" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="J177" s="14"/>
       <c r="K177" s="14" t="s">
@@ -10176,16 +10257,16 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="14" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="B178" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="E178" s="14" t="s">
         <v>5</v>
@@ -10198,7 +10279,7 @@
       </c>
       <c r="H178" s="14"/>
       <c r="I178" s="14" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="J178" s="14"/>
       <c r="K178" s="14" t="s">
@@ -10207,16 +10288,16 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="14" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="B179" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="E179" s="14" t="s">
         <v>5</v>
@@ -10229,7 +10310,7 @@
       </c>
       <c r="H179" s="14"/>
       <c r="I179" s="14" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="J179" s="14"/>
       <c r="K179" s="14" t="s">
@@ -10238,16 +10319,16 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="14" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="B180" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="E180" s="14" t="s">
         <v>5</v>
@@ -10260,7 +10341,7 @@
       </c>
       <c r="H180" s="14"/>
       <c r="I180" s="14" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="J180" s="14"/>
       <c r="K180" s="14" t="s">
@@ -10269,16 +10350,16 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="14" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="B181" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="E181" s="14" t="s">
         <v>5</v>
@@ -10291,7 +10372,7 @@
       </c>
       <c r="H181" s="14"/>
       <c r="I181" s="14" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="J181" s="14"/>
       <c r="K181" s="14" t="s">
@@ -10300,16 +10381,16 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="14" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="B182" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="E182" s="14" t="s">
         <v>5</v>
@@ -10322,7 +10403,7 @@
       </c>
       <c r="H182" s="14"/>
       <c r="I182" s="14" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="J182" s="14"/>
       <c r="K182" s="14" t="s">
@@ -10331,16 +10412,16 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="14" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="B183" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E183" s="14" t="s">
         <v>3</v>
@@ -10353,10 +10434,10 @@
       </c>
       <c r="H183" s="14"/>
       <c r="I183" s="14" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="J183" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="K183" s="14" t="s">
         <v>47</v>
@@ -10364,16 +10445,16 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="14" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="B184" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="D184" s="14" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E184" s="14" t="s">
         <v>3</v>
@@ -10386,10 +10467,10 @@
       </c>
       <c r="H184" s="14"/>
       <c r="I184" s="14" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="J184" s="14" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="K184" s="14" t="s">
         <v>47</v>
@@ -10397,16 +10478,16 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="14" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="B185" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E185" s="14" t="s">
         <v>6</v>
@@ -10420,7 +10501,7 @@
       <c r="H185" s="14"/>
       <c r="I185" s="14"/>
       <c r="J185" s="14" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="K185" s="14" t="s">
         <v>47</v>
@@ -10428,16 +10509,16 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="14" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="B186" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="E186" s="14" t="s">
         <v>5</v>
@@ -10450,7 +10531,7 @@
       </c>
       <c r="H186" s="14"/>
       <c r="I186" s="14" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="J186" s="14"/>
       <c r="K186" s="14" t="s">
@@ -10459,16 +10540,16 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="14" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="B187" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="D187" s="14" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="E187" s="14" t="s">
         <v>5</v>
@@ -10481,7 +10562,7 @@
       </c>
       <c r="H187" s="14"/>
       <c r="I187" s="14" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="J187" s="14"/>
       <c r="K187" s="14" t="s">
@@ -10490,16 +10571,16 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="14" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="B188" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="D188" s="14" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="E188" s="14" t="s">
         <v>5</v>
@@ -10512,7 +10593,7 @@
       </c>
       <c r="H188" s="14"/>
       <c r="I188" s="14" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="J188" s="14"/>
       <c r="K188" s="14" t="s">
@@ -10521,16 +10602,16 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="14" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="B189" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="D189" s="14" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="E189" s="14" t="s">
         <v>5</v>
@@ -10543,7 +10624,7 @@
       </c>
       <c r="H189" s="14"/>
       <c r="I189" s="14" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="J189" s="14"/>
       <c r="K189" s="14" t="s">
@@ -10552,16 +10633,16 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="14" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="B190" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="E190" s="14" t="s">
         <v>5</v>
@@ -10574,7 +10655,7 @@
       </c>
       <c r="H190" s="14"/>
       <c r="I190" s="14" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="J190" s="14"/>
       <c r="K190" s="14" t="s">
@@ -10583,16 +10664,16 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="14" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="B191" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C191" s="14" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="D191" s="14" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="E191" s="14" t="s">
         <v>5</v>
@@ -10605,7 +10686,7 @@
       </c>
       <c r="H191" s="14"/>
       <c r="I191" s="14" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="J191" s="14"/>
       <c r="K191" s="14" t="s">
@@ -10614,16 +10695,16 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="14" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="B192" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="D192" s="14" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="E192" s="14" t="s">
         <v>5</v>
@@ -10636,7 +10717,7 @@
       </c>
       <c r="H192" s="14"/>
       <c r="I192" s="14" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="J192" s="14"/>
       <c r="K192" s="14" t="s">
@@ -10645,16 +10726,16 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="14" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="B193" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="E193" s="14" t="s">
         <v>5</v>
@@ -10667,7 +10748,7 @@
       </c>
       <c r="H193" s="14"/>
       <c r="I193" s="14" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="J193" s="14"/>
       <c r="K193" s="14" t="s">
@@ -10676,16 +10757,16 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="14" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="B194" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="D194" s="14" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="E194" s="14" t="s">
         <v>5</v>
@@ -10698,7 +10779,7 @@
       </c>
       <c r="H194" s="14"/>
       <c r="I194" s="14" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="J194" s="14"/>
       <c r="K194" s="14" t="s">
@@ -10707,16 +10788,16 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="14" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="B195" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="E195" s="14" t="s">
         <v>5</v>
@@ -10729,7 +10810,7 @@
       </c>
       <c r="H195" s="14"/>
       <c r="I195" s="14" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="J195" s="14"/>
       <c r="K195" s="14" t="s">
@@ -10738,16 +10819,16 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="14" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="B196" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="E196" s="14" t="s">
         <v>5</v>
@@ -10760,7 +10841,7 @@
       </c>
       <c r="H196" s="14"/>
       <c r="I196" s="14" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="J196" s="14"/>
       <c r="K196" s="14" t="s">
@@ -10769,16 +10850,16 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="14" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="B197" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="E197" s="14" t="s">
         <v>5</v>
@@ -10791,7 +10872,7 @@
       </c>
       <c r="H197" s="14"/>
       <c r="I197" s="14" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="J197" s="14"/>
       <c r="K197" s="14" t="s">
@@ -10800,16 +10881,16 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="14" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="B198" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="E198" s="14" t="s">
         <v>5</v>
@@ -10822,7 +10903,7 @@
       </c>
       <c r="H198" s="14"/>
       <c r="I198" s="14" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="J198" s="14"/>
       <c r="K198" s="14" t="s">
@@ -10831,16 +10912,16 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="14" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C199" s="14" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="D199" s="14" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="E199" s="14" t="s">
         <v>5</v>
@@ -10853,7 +10934,7 @@
       </c>
       <c r="H199" s="14"/>
       <c r="I199" s="14" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="J199" s="14"/>
       <c r="K199" s="14" t="s">
@@ -10862,16 +10943,16 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="14" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B200" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="D200" s="14" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="E200" s="14" t="s">
         <v>5</v>
@@ -10884,7 +10965,7 @@
       </c>
       <c r="H200" s="14"/>
       <c r="I200" s="14" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="J200" s="14"/>
       <c r="K200" s="14" t="s">
@@ -10893,16 +10974,16 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="14" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="B201" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C201" s="14" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="D201" s="14" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="E201" s="14" t="s">
         <v>5</v>
@@ -10915,7 +10996,7 @@
       </c>
       <c r="H201" s="14"/>
       <c r="I201" s="14" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="J201" s="14"/>
       <c r="K201" s="14" t="s">
@@ -10924,16 +11005,16 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="14" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="B202" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="D202" s="14" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="E202" s="14" t="s">
         <v>5</v>
@@ -10946,7 +11027,7 @@
       </c>
       <c r="H202" s="14"/>
       <c r="I202" s="14" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="J202" s="14"/>
       <c r="K202" s="14" t="s">
@@ -10955,16 +11036,16 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="14" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="B203" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C203" s="14" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="D203" s="14" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="E203" s="14" t="s">
         <v>5</v>
@@ -10977,7 +11058,7 @@
       </c>
       <c r="H203" s="14"/>
       <c r="I203" s="14" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="J203" s="14"/>
       <c r="K203" s="14" t="s">
@@ -10986,13 +11067,13 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="14" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B204" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="D204" s="14" t="s">
         <v>44</v>
@@ -11004,14 +11085,14 @@
         <v>25</v>
       </c>
       <c r="G204" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H204" s="14"/>
       <c r="I204" s="14" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="K204" s="14" t="s">
         <v>47</v>
@@ -11019,19 +11100,19 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="14" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="B205" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C205" s="14" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="D205" s="14" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="E205" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F205" s="14" t="s">
         <v>25</v>
@@ -11043,10 +11124,10 @@
         <v>13</v>
       </c>
       <c r="I205" s="14" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="J205" s="14" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="K205" s="14" t="s">
         <v>47</v>
@@ -11054,16 +11135,16 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="14" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="B206" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="D206" s="14" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="E206" s="14" t="s">
         <v>5</v>
@@ -11072,14 +11153,14 @@
         <v>27</v>
       </c>
       <c r="G206" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H206" s="14"/>
       <c r="I206" s="14" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="J206" s="14" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="K206" s="14" t="s">
         <v>47</v>
@@ -11087,16 +11168,16 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="14" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C207" s="14" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="D207" s="14" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="E207" s="14" t="s">
         <v>5</v>
@@ -11105,11 +11186,11 @@
         <v>27</v>
       </c>
       <c r="G207" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H207" s="14"/>
       <c r="I207" s="14" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="J207" s="14"/>
       <c r="K207" s="14" t="s">
@@ -11118,16 +11199,16 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="14" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="B208" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="D208" s="14" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="E208" s="14" t="s">
         <v>5</v>
@@ -11136,11 +11217,11 @@
         <v>29</v>
       </c>
       <c r="G208" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H208" s="14"/>
       <c r="I208" s="14" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="J208" s="14"/>
       <c r="K208" s="14" t="s">
@@ -11149,17 +11230,17 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="14" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B209" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C209" s="14" t="s">
+        <v>898</v>
+      </c>
+      <c r="D209" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="D209" s="14" t="s">
-        <v>886</v>
-      </c>
       <c r="E209" s="14" t="s">
         <v>5</v>
       </c>
@@ -11167,11 +11248,11 @@
         <v>29</v>
       </c>
       <c r="G209" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H209" s="14"/>
       <c r="I209" s="14" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="J209" s="14"/>
       <c r="K209" s="14" t="s">
@@ -11180,16 +11261,16 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="14" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="B210" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="E210" s="14" t="s">
         <v>5</v>
@@ -11202,7 +11283,7 @@
       </c>
       <c r="H210" s="14"/>
       <c r="I210" s="14" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="J210" s="14"/>
       <c r="K210" s="14" t="s">
@@ -11211,16 +11292,16 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="14" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="E211" s="14" t="s">
         <v>7</v>
@@ -11234,7 +11315,7 @@
       <c r="H211" s="14"/>
       <c r="I211" s="14"/>
       <c r="J211" s="14" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="K211" s="14" t="s">
         <v>47</v>
@@ -11242,16 +11323,16 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="14" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="B212" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="D212" s="14" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="E212" s="14" t="s">
         <v>5</v>
@@ -11260,14 +11341,14 @@
         <v>29</v>
       </c>
       <c r="G212" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H212" s="14"/>
       <c r="I212" s="14" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="J212" s="14" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="K212" s="14" t="s">
         <v>47</v>
@@ -11275,16 +11356,16 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="14" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C213" s="14" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="D213" s="14" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="E213" s="14" t="s">
         <v>5</v>
@@ -11297,10 +11378,10 @@
       </c>
       <c r="H213" s="14"/>
       <c r="I213" s="14" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="J213" s="14" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="K213" s="14" t="s">
         <v>47</v>
@@ -11308,16 +11389,16 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="14" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B214" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D214" s="14" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="E214" s="14" t="s">
         <v>3</v>
@@ -11330,10 +11411,10 @@
       </c>
       <c r="H214" s="14"/>
       <c r="I214" s="14" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="J214" s="14" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="K214" s="14" t="s">
         <v>47</v>
@@ -11341,16 +11422,16 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="14" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B215" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C215" s="14" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="D215" s="14" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="E215" s="14" t="s">
         <v>5</v>
@@ -11359,14 +11440,14 @@
         <v>27</v>
       </c>
       <c r="G215" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H215" s="14"/>
       <c r="I215" s="14" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="J215" s="14" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="K215" s="14" t="s">
         <v>47</v>
@@ -11374,16 +11455,16 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="14" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B216" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D216" s="14" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="E216" s="14" t="s">
         <v>5</v>
@@ -11392,11 +11473,11 @@
         <v>29</v>
       </c>
       <c r="G216" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H216" s="14"/>
       <c r="I216" s="14" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="J216" s="14"/>
       <c r="K216" s="14" t="s">
@@ -11405,16 +11486,16 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="14" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="B217" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C217" s="14" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="D217" s="14" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="E217" s="14" t="s">
         <v>5</v>
@@ -11423,11 +11504,11 @@
         <v>29</v>
       </c>
       <c r="G217" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H217" s="14"/>
       <c r="I217" s="14" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="J217" s="14"/>
       <c r="K217" s="14" t="s">
@@ -11436,16 +11517,16 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="14" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="B218" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="E218" s="14" t="s">
         <v>5</v>
@@ -11454,14 +11535,14 @@
         <v>27</v>
       </c>
       <c r="G218" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H218" s="14"/>
       <c r="I218" s="14" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="J218" s="14" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="K218" s="14" t="s">
         <v>47</v>
@@ -11469,16 +11550,16 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="14" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B219" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C219" s="14" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="D219" s="14" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="E219" s="14" t="s">
         <v>5</v>
@@ -11491,7 +11572,7 @@
       </c>
       <c r="H219" s="14"/>
       <c r="I219" s="14" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="J219" s="14"/>
       <c r="K219" s="14" t="s">
@@ -11500,19 +11581,19 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="14" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="B220" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="E220" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F220" s="14" t="s">
         <v>25</v>
@@ -11524,10 +11605,10 @@
         <v>14</v>
       </c>
       <c r="I220" s="14" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="J220" s="14" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="K220" s="14" t="s">
         <v>47</v>
@@ -11535,16 +11616,16 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="14" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="B221" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="D221" s="14" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="E221" s="14" t="s">
         <v>5</v>
@@ -11553,14 +11634,14 @@
         <v>29</v>
       </c>
       <c r="G221" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H221" s="14"/>
       <c r="I221" s="14" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="J221" s="14" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="K221" s="14" t="s">
         <v>47</v>
@@ -11568,16 +11649,16 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="14" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="D222" s="14" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="E222" s="14" t="s">
         <v>5</v>
@@ -11586,11 +11667,11 @@
         <v>29</v>
       </c>
       <c r="G222" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H222" s="14"/>
       <c r="I222" s="14" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="J222" s="14"/>
       <c r="K222" s="14" t="s">
@@ -11599,16 +11680,16 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="14" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="B223" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E223" s="14" t="s">
         <v>5</v>
@@ -11622,7 +11703,7 @@
       <c r="H223" s="14"/>
       <c r="I223" s="14"/>
       <c r="J223" s="14" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="K223" s="14" t="s">
         <v>47</v>
@@ -11630,16 +11711,16 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="14" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="D224" s="14" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="E224" s="14" t="s">
         <v>5</v>
@@ -11659,16 +11740,16 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="14" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="B225" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C225" s="14" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="D225" s="14" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="E225" s="14" t="s">
         <v>5</v>
@@ -11677,12 +11758,12 @@
         <v>27</v>
       </c>
       <c r="G225" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H225" s="14"/>
       <c r="I225" s="14"/>
       <c r="J225" s="14" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="K225" s="14" t="s">
         <v>47</v>
@@ -11690,16 +11771,16 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="14" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="B226" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="D226" s="14" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="E226" s="14" t="s">
         <v>5</v>
@@ -11719,16 +11800,16 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="14" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B227" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C227" s="14" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="D227" s="14" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="E227" s="14" t="s">
         <v>5</v>
@@ -11742,7 +11823,7 @@
       <c r="H227" s="14"/>
       <c r="I227" s="14"/>
       <c r="J227" s="14" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="K227" s="14" t="s">
         <v>47</v>
@@ -11750,16 +11831,16 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="14" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="B228" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D228" s="14" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="E228" s="14" t="s">
         <v>5</v>
@@ -11768,12 +11849,12 @@
         <v>25</v>
       </c>
       <c r="G228" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H228" s="14"/>
       <c r="I228" s="14"/>
       <c r="J228" s="14" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="K228" s="14" t="s">
         <v>47</v>
@@ -11781,16 +11862,16 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="14" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="B229" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C229" s="14" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="D229" s="14" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="E229" s="14" t="s">
         <v>5</v>
@@ -11810,16 +11891,16 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="14" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B230" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="D230" s="14" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="E230" s="14" t="s">
         <v>5</v>
@@ -11828,12 +11909,12 @@
         <v>27</v>
       </c>
       <c r="G230" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H230" s="14"/>
       <c r="I230" s="14"/>
       <c r="J230" s="14" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="K230" s="14" t="s">
         <v>47</v>
@@ -11841,16 +11922,16 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="14" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="B231" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D231" s="14" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="E231" s="14" t="s">
         <v>5</v>
@@ -11870,16 +11951,16 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="14" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="B232" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="D232" s="14" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="E232" s="14" t="s">
         <v>5</v>
@@ -11893,7 +11974,7 @@
       <c r="H232" s="14"/>
       <c r="I232" s="14"/>
       <c r="J232" s="14" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="K232" s="14" t="s">
         <v>47</v>
@@ -11901,16 +11982,16 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="14" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="B233" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C233" s="14" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="D233" s="14" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="E233" s="14" t="s">
         <v>5</v>
@@ -11930,16 +12011,16 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="14" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="D234" s="14" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="E234" s="14" t="s">
         <v>4</v>
@@ -11953,7 +12034,7 @@
       <c r="H234" s="14"/>
       <c r="I234" s="14"/>
       <c r="J234" s="14" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="K234" s="14" t="s">
         <v>47</v>
@@ -11961,16 +12042,16 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="14" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="B235" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C235" s="14" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="D235" s="14" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="E235" s="14" t="s">
         <v>3</v>
@@ -11984,7 +12065,7 @@
       <c r="H235" s="14"/>
       <c r="I235" s="14"/>
       <c r="J235" s="14" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="K235" s="14" t="s">
         <v>47</v>
@@ -11992,16 +12073,16 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="14" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="B236" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C236" s="14" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="E236" s="14" t="s">
         <v>3</v>
@@ -12015,7 +12096,7 @@
       <c r="H236" s="14"/>
       <c r="I236" s="14"/>
       <c r="J236" s="14" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="K236" s="14" t="s">
         <v>47</v>
@@ -12023,16 +12104,16 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="14" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="B237" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C237" s="14" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="D237" s="14" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="E237" s="14" t="s">
         <v>3</v>
@@ -12041,12 +12122,12 @@
         <v>25</v>
       </c>
       <c r="G237" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H237" s="14"/>
       <c r="I237" s="14"/>
       <c r="J237" s="14" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="K237" s="14" t="s">
         <v>47</v>
@@ -12054,16 +12135,16 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="14" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="B238" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="D238" s="14" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="E238" s="14" t="s">
         <v>3</v>
@@ -12077,7 +12158,7 @@
       <c r="H238" s="14"/>
       <c r="I238" s="14"/>
       <c r="J238" s="14" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="K238" s="14" t="s">
         <v>47</v>
@@ -12085,16 +12166,16 @@
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="14" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="B239" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C239" s="14" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="D239" s="14" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="E239" s="14" t="s">
         <v>6</v>
@@ -12110,7 +12191,7 @@
       </c>
       <c r="I239" s="14"/>
       <c r="J239" s="14" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="K239" s="14" t="s">
         <v>47</v>
@@ -12118,16 +12199,16 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="14" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="D240" s="14" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="E240" s="14" t="s">
         <v>6</v>
@@ -12143,7 +12224,7 @@
       </c>
       <c r="I240" s="14"/>
       <c r="J240" s="14" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="K240" s="14" t="s">
         <v>47</v>
@@ -12151,16 +12232,16 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="14" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="B241" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C241" s="14" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="D241" s="14" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="E241" s="14" t="s">
         <v>6</v>
@@ -12176,7 +12257,7 @@
       </c>
       <c r="I241" s="14"/>
       <c r="J241" s="14" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="K241" s="14" t="s">
         <v>47</v>
@@ -12184,16 +12265,16 @@
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="14" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="B242" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="D242" s="14" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="E242" s="14" t="s">
         <v>3</v>
@@ -12209,7 +12290,7 @@
       </c>
       <c r="I242" s="14"/>
       <c r="J242" s="14" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="K242" s="14" t="s">
         <v>47</v>
@@ -12217,16 +12298,16 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="14" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="B243" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C243" s="14" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="D243" s="14" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="E243" s="14" t="s">
         <v>3</v>
@@ -12242,7 +12323,7 @@
       </c>
       <c r="I243" s="14"/>
       <c r="J243" s="14" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="K243" s="14" t="s">
         <v>47</v>
@@ -12250,16 +12331,16 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="14" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="B244" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="D244" s="14" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="E244" s="14" t="s">
         <v>4</v>
@@ -12275,7 +12356,7 @@
       </c>
       <c r="I244" s="14"/>
       <c r="J244" s="14" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="K244" s="14" t="s">
         <v>47</v>
@@ -12283,16 +12364,16 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="14" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="B245" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C245" s="14" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="D245" s="14" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="E245" s="14" t="s">
         <v>6</v>
@@ -12308,7 +12389,7 @@
       </c>
       <c r="I245" s="14"/>
       <c r="J245" s="14" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="K245" s="14" t="s">
         <v>47</v>
@@ -12316,16 +12397,16 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="14" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="B246" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="D246" s="14" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E246" s="14" t="s">
         <v>6</v>
@@ -12339,7 +12420,7 @@
       <c r="H246" s="14"/>
       <c r="I246" s="14"/>
       <c r="J246" s="14" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="K246" s="14" t="s">
         <v>47</v>
@@ -12347,16 +12428,16 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="14" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="B247" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C247" s="14" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="D247" s="14" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="E247" s="14" t="s">
         <v>5</v>
@@ -12370,7 +12451,7 @@
       <c r="H247" s="14"/>
       <c r="I247" s="14"/>
       <c r="J247" s="14" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="K247" s="14" t="s">
         <v>47</v>
@@ -12378,16 +12459,16 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="14" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="B248" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="D248" s="14" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="E248" s="14" t="s">
         <v>5</v>
@@ -12407,16 +12488,16 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="14" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="B249" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C249" s="14" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="E249" s="14" t="s">
         <v>5</v>
@@ -12430,7 +12511,7 @@
       <c r="H249" s="14"/>
       <c r="I249" s="14"/>
       <c r="J249" s="14" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="K249" s="14" t="s">
         <v>47</v>
@@ -12438,16 +12519,16 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="14" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="B250" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="D250" s="14" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="E250" s="14" t="s">
         <v>5</v>
@@ -12461,7 +12542,7 @@
       <c r="H250" s="14"/>
       <c r="I250" s="14"/>
       <c r="J250" s="14" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="K250" s="14" t="s">
         <v>47</v>
@@ -12469,16 +12550,16 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="14" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="B251" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C251" s="14" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="D251" s="14" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="E251" s="14" t="s">
         <v>5</v>
@@ -12498,16 +12579,16 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="14" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="B252" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="D252" s="14" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="E252" s="14" t="s">
         <v>5</v>
@@ -12527,16 +12608,16 @@
     </row>
     <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="14" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="B253" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C253" s="14" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="D253" s="14" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="E253" s="14" t="s">
         <v>5</v>
@@ -12545,12 +12626,12 @@
         <v>27</v>
       </c>
       <c r="G253" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H253" s="14"/>
       <c r="I253" s="14"/>
       <c r="J253" s="14" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="K253" s="14" t="s">
         <v>47</v>
@@ -12558,16 +12639,16 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="14" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="B254" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="D254" s="14" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="E254" s="14" t="s">
         <v>6</v>
@@ -12583,7 +12664,7 @@
       </c>
       <c r="I254" s="14"/>
       <c r="J254" s="14" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="K254" s="14" t="s">
         <v>47</v>
@@ -12591,16 +12672,16 @@
     </row>
     <row r="255" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="B255" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="E255" s="14" t="s">
         <v>3</v>
@@ -12614,7 +12695,7 @@
       <c r="H255" s="14"/>
       <c r="I255" s="14"/>
       <c r="J255" s="14" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="K255" s="14" t="s">
         <v>47</v>
@@ -12683,7 +12764,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>33</v>
@@ -12712,7 +12793,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C2" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B2,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12744,7 +12825,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="C3" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B3,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12776,7 +12857,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="C4" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B4,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12808,7 +12889,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="C5" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B5,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12840,7 +12921,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="C6" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B6,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12872,7 +12953,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C7" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B7,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12904,7 +12985,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="C8" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B8,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12936,7 +13017,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C9" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B9,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12968,7 +13049,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C10" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B10,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12988,11 +13069,11 @@
       </c>
       <c r="G10" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B10,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Partial</v>
       </c>
       <c r="H10" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B10,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>FinosTaxCore.savingsPlan() is not ported yet; taxNew/taxOld/best are</v>
+        <v>Tax Savings Tracker done: regime compare, deduction headroom per section, break-even deductions, saves finos_tax_savings (parity-tested savingsPlan). Tax Planner (HRA, surcharge, capital gains: finos-tax-calc.js) still to build.</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13000,7 +13081,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C11" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B11,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13020,11 +13101,11 @@
       </c>
       <c r="G11" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B11,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="H11" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B11,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Uses the shared tax core</v>
+        <v>CTC breakup → gross, HRA three-way minimum, tax in both regimes, take-home, restructuring tips; parity-tested. Take-home becomes income only on tap (the website overwrites finos_monthly_income on every render).</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13032,7 +13113,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C12" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B12,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13052,11 +13133,11 @@
       </c>
       <c r="G12" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B12,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
-      </c>
-      <c r="H12" s="14" t="n">
+        <v>Done</v>
+      </c>
+      <c r="H12" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B12,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>0</v>
+        <v>Flat vs stepped-up SIP, scenario cards (5/10/15/20%), corpus chart, year table, milestones; parity-tested vs js/finos-sip-stepup.js incl. out-of-range inputs</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13064,7 +13145,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B13,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13084,11 +13165,11 @@
       </c>
       <c r="G13" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B13,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
-      </c>
-      <c r="H13" s="14" t="n">
+        <v>Done</v>
+      </c>
+      <c r="H13" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B13,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>0</v>
+        <v>Avalanche vs snowball + home-loan prepayment impact; shares balances with Net Worth; parity-tested vs js/finos-debt-optimizer.js</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13096,7 +13177,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C14" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B14,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13116,11 +13197,11 @@
       </c>
       <c r="G14" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B14,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="H14" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B14,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Amortisation schedule + 24(b)/80C benefits</v>
+        <v>EMI, amortisation, affordability, 24(b)/80C deductions, prepayment impact; parity-tested. Website's PMAY-CLSS 'eligible' banner deliberately not ported (scheme bands ended); writes loan keys only on 'Save as my home loan'.</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13128,7 +13209,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C15" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B15,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13148,11 +13229,11 @@
       </c>
       <c r="G15" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B15,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="H15" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B15,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Feeds net worth</v>
+        <v>FD, RD, PPF, NSC, SCSS, Sukanya, bonds, post office; same finos_fd_portfolio key as the web; parity-tested; RD 0% division guarded</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13160,7 +13241,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C16" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B16,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13180,11 +13261,11 @@
       </c>
       <c r="G16" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B16,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="H16" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B16,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Feeds net worth</v>
+        <v>Physical, SGB, gold ETF, gold MF; user-typed price only (no invented rate); coupon; parity-tested vs js/finos-gold-tracker.js</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13192,7 +13273,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B17,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13212,11 +13293,11 @@
       </c>
       <c r="G17" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B17,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Partial</v>
       </c>
       <c r="H17" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B17,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Subscriptions, SIPs, renewals, tax dates; needs local notifications</v>
+        <v>Month grid, day detail, coming-up list, summary cards: SIP, deposit maturities (real terms), insurance, goals, subscriptions, tax dates; parity-tested. Phone notifications NOT built: need an OS notification permission, which the privacy guard test currently forbids (owner decision).</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13224,7 +13305,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C18" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B18,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13244,11 +13325,11 @@
       </c>
       <c r="G18" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B18,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="H18" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B18,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Money Score uses finos_leak_monthly if present</v>
+        <v>Monthly leak from the ledger + subscriptions, 10/20/30-year future value, redirect share; parity-tested vs js/finos-leak.js</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13256,7 +13337,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C19" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B19,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13276,11 +13357,11 @@
       </c>
       <c r="G19" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B19,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="H19" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B19,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Reuse the CSV helpers already ported for statements</v>
+        <v>Zerodha / Groww / generic CSV parsed identically to js/finos-import.js; rows become Portfolio holdings (replace units + avg cost, never add twice); holdings with no ticker/scheme code keep the broker price. CAS PDF import (S-03) still needs the document-ai backend.</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13288,7 +13369,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="C20" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B20,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13308,16 +13389,16 @@
       </c>
       <c r="G20" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B20,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="H20" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B20,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Port the pure guardrail rules; important before store release</v>
+        <v>Same rules and wording as js/arya-guardrails.js (parity-tested on 420+ pairs); tax-evasion requests are refused on the phone before any network call; notes are appended to finished or stopped answers.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
     </row>
   </sheetData>
@@ -13336,7 +13417,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -13347,70 +13428,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13418,16 +13499,16 @@
         <v>47</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13435,16 +13516,16 @@
         <v>47</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13452,33 +13533,118 @@
         <v>47</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1094</v>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -13506,7 +13672,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>1095</v>
+        <v>1120</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>22</v>
@@ -13517,7 +13683,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1096</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13525,7 +13691,7 @@
         <v>20</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1097</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13533,7 +13699,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1098</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13541,31 +13707,31 @@
         <v>38</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1099</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1101</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>1102</v>
+        <v>1127</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1103</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>1104</v>
+        <v>1129</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1105</v>
+        <v>1130</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2614" uniqueCount="1162">
   <si>
     <t xml:space="preserve">FIN·OS phone app — parity with the website</t>
   </si>
@@ -329,93 +329,99 @@
     <t xml:space="preserve">html/goal-optimizer.html</t>
   </si>
   <si>
+    <t xml:space="preserve">tools/goalopt (from Goals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflation-adjusted SIP per goal, priority score, feasibility vs what you can invest, competing-goal conflicts; parity-tested vs js/finos-goal-optimizer.js. Website corrected in the same pass: saved money compounds as today's rupees (it was taken as a % of the inflated target, counting inflation twice).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Tracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html/gold-tracker.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tracker/gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical, SGB, gold ETF, gold MF; user-typed price only (no invented rate); coupon; parity-tested vs js/finos-gold-tracker.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Loan EMI Planner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html/home-loan.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools/homeloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMI, amortisation, affordability, 24(b)/80C deductions, prepayment impact; parity-tested. Website's PMAY-CLSS 'eligible' banner deliberately not ported (scheme bands ended); writes loan keys only on 'Save as my home loan'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance Hub (directory, compare)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html/insurance-hub.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tracker/insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies, gaps and renewals are done; directory/compare is not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITR Filing Prep Kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html/itr-summary.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools/itr (from Tax planner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income, 80C itemised, 80CCD/80D/24(b)/80E/80TTA, both regimes, TDS and balance/refund; the calculation is sliced unchanged from js/finos-itr-summary.js and parity-tested; figures live under the website's keys. Capital gains and surcharge are not in this worksheet (the Tax Planner has them).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Insurance Need Calculator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html/life-cover.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools/lifecover (from Insurance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human life value + income replacement + debts − existing cover, status band, rough premium illustration; parity-tested vs js/finos-life-cover.js; prefilled from income, spending, policies and loans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Goals Planner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html/life-goals-planner.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">tracker/goals</t>
   </si>
   <si>
-    <t xml:space="preserve">Goals tracker is done; the optimizer is not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">html/gold-tracker.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tracker/gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical, SGB, gold ETF, gold MF; user-typed price only (no invented rate); coupon; parity-tested vs js/finos-gold-tracker.js</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Loan EMI Planner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">html/home-loan.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tools/homeloan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMI, amortisation, affordability, 24(b)/80C deductions, prepayment impact; parity-tested. Website's PMAY-CLSS 'eligible' banner deliberately not ported (scheme bands ended); writes loan keys only on 'Save as my home loan'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurance Hub (directory, compare)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">html/insurance-hub.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tracker/insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policies, gaps and renewals are done; directory/compare is not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITR Filing Prep Kit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">html/itr-summary.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tools/itr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uses the shared tax core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life Insurance Need Calculator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">html/life-cover.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommended cover is shown; the full need calculator is not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life Goals Planner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">html/life-goals-planner.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">T-19</t>
   </si>
   <si>
@@ -464,6 +470,9 @@
     <t xml:space="preserve">tracker/passive</t>
   </si>
   <si>
+    <t xml:space="preserve">Streams (dividend, FD, rental, SWP, SGB, other), coverage of monthly spending, freedom milestones, what-if, extra corpus at 4%; totals parity-tested vs js/finos-passive-income.js; FD/SGB seed lines are labelled as estimates.</t>
+  </si>
+  <si>
     <t xml:space="preserve">T-23</t>
   </si>
   <si>
@@ -473,7 +482,10 @@
     <t xml:space="preserve">html/portfolio-rebalancer.html</t>
   </si>
   <si>
-    <t xml:space="preserve">portfolio/rebalance</t>
+    <t xml:space="preserve">tools/rebalance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six asset classes from the other trackers, target presets + editor, drift and action per class, new-money split; parity-tested vs js/finos-rebalancer.js. Differences: empty portfolio is not flagged, property and govt savings are advised as 'send new money elsewhere'.</t>
   </si>
   <si>
     <t xml:space="preserve">T-24</t>
@@ -572,6 +584,9 @@
     <t xml:space="preserve">tools/windfall</t>
   </si>
   <si>
+    <t xml:space="preserve">Same waterfall as js/finos-windfall.js (parity-tested on 1,000 households) plus bonus/RSU tax impact; unknown spending is flagged instead of silently assuming ₹50,000; property note updated to the July 2024 rules.</t>
+  </si>
+  <si>
     <t xml:space="preserve">T-31</t>
   </si>
   <si>
@@ -581,10 +596,10 @@
     <t xml:space="preserve">html/tax.html</t>
   </si>
   <si>
-    <t xml:space="preserve">tools/tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax Savings Tracker done: regime compare, deduction headroom per section, break-even deductions, saves finos_tax_savings (parity-tested savingsPlan). Tax Planner (HRA, surcharge, capital gains: finos-tax-calc.js) still to build.</t>
+    <t xml:space="preserve">tools/tax + tools/taxplanner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savings tracker (headroom per section) and the full Tax Planner (both regimes with surcharge, HRA, 80C/80D/NPS/24(b), LTCG/STCG, action list); parity-tested vs js/finos-tax-calc.js. Web surcharge fixed in the same pass (taxable income, new-regime top rate 25%).</t>
   </si>
   <si>
     <t xml:space="preserve">T-32</t>
@@ -3014,7 +3029,7 @@
     <t xml:space="preserve">html/settings.html</t>
   </si>
   <si>
-    <t xml:space="preserve">Notification toggle and a few fields are cosmetic</t>
+    <t xml:space="preserve">The no-effect 'Price Alerts' switch was removed; Settings now says reminders are not available and points to the Financial calendar. Name, income and backend host all take effect.</t>
   </si>
   <si>
     <t xml:space="preserve">P-13</t>
@@ -3185,7 +3200,7 @@
     <t xml:space="preserve">Accessibility pass (labels, contrast, large text)</t>
   </si>
   <si>
-    <t xml:space="preserve">The website has axe checks; the phone app has none</t>
+    <t xml:space="preserve">Static pass done and guarded by __tests__/a11y.test.mts: every touchable/input has a role or label, icon-only buttons are labelled, text colours reach 4.5:1 (textDim raised from 2.6:1, purple text uses purpleInk), system font scaling is left on. Not yet tried with VoiceOver / TalkBack on a device.</t>
   </si>
   <si>
     <t xml:space="preserve">R-13</t>
@@ -3387,6 +3402,84 @@
   </si>
   <si>
     <t xml:space="preserve">Both screens rendered in the preview without console errors; their parity tests are part of the 146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-31 (Tax Planner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax Planner: both regimes side by side with surcharge, HRA, deductions, capital gains and actions; website surcharge corrected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to the website on 1,500 random taxpayers (incl. 100+ above ₹50L); agrees with the shared tax core up to ₹50L; website tax-consistency tests pass; preview run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-12, P-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessibility pass (labels, roles, contrast, guard test); Settings no longer shows a toggle that does nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a11y guard test (4 checks); contrast computed against the theme; preview run of Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus &amp; windfall allocator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall identical to the website on 1,000 random households; bonus tax figures equal what the website prints; preview run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive income tracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total and coverage identical to the website's _recompute on 800 random stream lists; preview run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life cover needed calculator (linked from Insurance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to the website on 1,500 random profiles incl. equal discount/inflation; preview run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio rebalancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class rows, normalised target and drift flag identical to the website on 1,000 portfolios; preview run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITR prep kit (linked from the Tax planner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every figure identical to the website's _compute on 800 random sets of stored values with a frozen clock; preview run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal optimizer (linked from Goals); website double-counted inflation on saved money and was fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to the corrected website on 800 random goal sets with a frozen clock; website suite 327/327; preview run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183</t>
   </si>
   <si>
     <t xml:space="preserve">Term</t>
@@ -4091,15 +4184,15 @@
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A5,'Parity Tracker'!$E$2:$E$255,"Done")</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A5,'Parity Tracker'!$E$2:$E$255,"Partial")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A5,'Parity Tracker'!$E$2:$E$255,"Pending")</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A5,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
@@ -4115,7 +4208,7 @@
       </c>
       <c r="H5" s="7" t="n">
         <f aca="false">IF((G5-F5)=0,0,(B5+0.5*C5)/(G5-F5))</f>
-        <v>0.58974358974359</v>
+        <v>0.730769230769231</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4289,11 +4382,11 @@
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A11,'Parity Tracker'!$E$2:$E$255,"Done")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A11,'Parity Tracker'!$E$2:$E$255,"Partial")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A11,'Parity Tracker'!$E$2:$E$255,"Pending")</f>
@@ -4313,7 +4406,7 @@
       </c>
       <c r="H11" s="7" t="n">
         <f aca="false">IF((G11-F11)=0,0,(B11+0.5*C11)/(G11-F11))</f>
-        <v>0.28125</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4326,11 +4419,11 @@
       </c>
       <c r="C12" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A12,'Parity Tracker'!$E$2:$E$255,"Partial")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A12,'Parity Tracker'!$E$2:$E$255,"Pending")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="6" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$B$2:$B$255,$A12,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
@@ -4346,7 +4439,7 @@
       </c>
       <c r="H12" s="7" t="n">
         <f aca="false">IF((G12-F12)=0,0,(B12+0.5*C12)/(G12-F12))</f>
-        <v>0.205882352941176</v>
+        <v>0.235294117647059</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4355,15 +4448,15 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">SUM(B5:B12)</f>
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">SUM(C5:C12)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">SUM(D5:D12)</f>
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">SUM(E5:E12)</f>
@@ -4379,7 +4472,7 @@
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">IF((G13-F13)=0,0,(B13+0.5*C13)/(G13-F13))</f>
-        <v>0.154761904761905</v>
+        <v>0.180555555555556</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4416,7 +4509,7 @@
       </c>
       <c r="B18" s="5" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$F$2:$F$255,$A18,'Parity Tracker'!$E$2:$E$255,"Partial")+COUNTIFS('Parity Tracker'!$F$2:$F$255,$A18,'Parity Tracker'!$E$2:$E$255,"Pending")+COUNTIFS('Parity Tracker'!$F$2:$F$255,$A18,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>26</v>
@@ -4428,7 +4521,7 @@
       </c>
       <c r="B19" s="5" t="n">
         <f aca="false">COUNTIFS('Parity Tracker'!$F$2:$F$255,$A19,'Parity Tracker'!$E$2:$E$255,"Partial")+COUNTIFS('Parity Tracker'!$F$2:$F$255,$A19,'Parity Tracker'!$E$2:$E$255,"Pending")+COUNTIFS('Parity Tracker'!$F$2:$F$255,$A19,'Parity Tracker'!$E$2:$E$255,"Blocked")</f>
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>28</v>
@@ -4898,7 +4991,7 @@
         <v>99</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>27</v>
@@ -5034,7 +5127,7 @@
         <v>119</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>27</v>
@@ -5067,7 +5160,7 @@
         <v>124</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>27</v>
@@ -5077,10 +5170,10 @@
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="14" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>47</v>
@@ -5088,16 +5181,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>5</v>
@@ -5110,7 +5203,7 @@
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="14" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="14" t="s">
@@ -5119,16 +5212,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>5</v>
@@ -5141,7 +5234,7 @@
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="14" t="s">
@@ -5150,16 +5243,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>3</v>
@@ -5172,7 +5265,7 @@
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="14" t="s">
@@ -5181,16 +5274,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>3</v>
@@ -5203,7 +5296,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="14" t="s">
@@ -5212,19 +5305,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>27</v>
@@ -5234,28 +5327,30 @@
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" s="14"/>
+        <v>146</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>147</v>
+      </c>
       <c r="K23" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>27</v>
@@ -5265,25 +5360,27 @@
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="J24" s="14"/>
+        <v>151</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>152</v>
+      </c>
       <c r="K24" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>3</v>
@@ -5296,7 +5393,7 @@
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J25" s="14"/>
       <c r="K25" s="14" t="s">
@@ -5305,16 +5402,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>5</v>
@@ -5327,7 +5424,7 @@
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J26" s="14"/>
       <c r="K26" s="14" t="s">
@@ -5336,16 +5433,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>3</v>
@@ -5360,10 +5457,10 @@
         <v>3</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>47</v>
@@ -5371,16 +5468,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>3</v>
@@ -5395,10 +5492,10 @@
         <v>5</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>47</v>
@@ -5406,16 +5503,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>3</v>
@@ -5430,10 +5527,10 @@
         <v>6</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K29" s="14" t="s">
         <v>47</v>
@@ -5441,16 +5538,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>5</v>
@@ -5463,10 +5560,10 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K30" s="14" t="s">
         <v>47</v>
@@ -5474,19 +5571,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>27</v>
@@ -5496,28 +5593,30 @@
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="J31" s="14"/>
+        <v>184</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>185</v>
+      </c>
       <c r="K31" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>25</v>
@@ -5529,10 +5628,10 @@
         <v>4</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K32" s="14" t="s">
         <v>47</v>
@@ -5540,16 +5639,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>3</v>
@@ -5562,10 +5661,10 @@
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K33" s="14" t="s">
         <v>47</v>
@@ -5573,16 +5672,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>3</v>
@@ -5597,10 +5696,10 @@
         <v>12</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K34" s="14" t="s">
         <v>47</v>
@@ -5608,16 +5707,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>3</v>
@@ -5630,7 +5729,7 @@
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J35" s="14"/>
       <c r="K35" s="14" t="s">
@@ -5639,16 +5738,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>3</v>
@@ -5661,10 +5760,10 @@
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>47</v>
@@ -5672,16 +5771,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>3</v>
@@ -5694,7 +5793,7 @@
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="14" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="14" t="s">
@@ -5703,16 +5802,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>5</v>
@@ -5725,7 +5824,7 @@
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="14" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="J38" s="14"/>
       <c r="K38" s="14" t="s">
@@ -5734,16 +5833,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>5</v>
@@ -5756,10 +5855,10 @@
       </c>
       <c r="H39" s="14"/>
       <c r="I39" s="14" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K39" s="14" t="s">
         <v>47</v>
@@ -5767,16 +5866,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>5</v>
@@ -5789,7 +5888,7 @@
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="14" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="J40" s="14"/>
       <c r="K40" s="14" t="s">
@@ -5798,16 +5897,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>5</v>
@@ -5820,10 +5919,10 @@
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="14" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K41" s="14" t="s">
         <v>47</v>
@@ -5831,16 +5930,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>5</v>
@@ -5853,10 +5952,10 @@
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K42" s="14" t="s">
         <v>47</v>
@@ -5864,16 +5963,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>5</v>
@@ -5886,10 +5985,10 @@
       </c>
       <c r="H43" s="14"/>
       <c r="I43" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K43" s="14" t="s">
         <v>47</v>
@@ -5897,16 +5996,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>5</v>
@@ -5919,10 +6018,10 @@
       </c>
       <c r="H44" s="14"/>
       <c r="I44" s="14" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K44" s="14" t="s">
         <v>47</v>
@@ -5930,16 +6029,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>5</v>
@@ -5952,10 +6051,10 @@
       </c>
       <c r="H45" s="14"/>
       <c r="I45" s="14" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K45" s="14" t="s">
         <v>47</v>
@@ -5963,16 +6062,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E46" s="14" t="s">
         <v>5</v>
@@ -5985,10 +6084,10 @@
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="14" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K46" s="14" t="s">
         <v>47</v>
@@ -5996,16 +6095,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>5</v>
@@ -6018,10 +6117,10 @@
       </c>
       <c r="H47" s="14"/>
       <c r="I47" s="14" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K47" s="14" t="s">
         <v>47</v>
@@ -6029,16 +6128,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>5</v>
@@ -6051,10 +6150,10 @@
       </c>
       <c r="H48" s="14"/>
       <c r="I48" s="14" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K48" s="14" t="s">
         <v>47</v>
@@ -6062,16 +6161,16 @@
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>5</v>
@@ -6084,10 +6183,10 @@
       </c>
       <c r="H49" s="14"/>
       <c r="I49" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K49" s="14" t="s">
         <v>47</v>
@@ -6095,16 +6194,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>5</v>
@@ -6117,10 +6216,10 @@
       </c>
       <c r="H50" s="14"/>
       <c r="I50" s="14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K50" s="14" t="s">
         <v>47</v>
@@ -6128,16 +6227,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>5</v>
@@ -6150,10 +6249,10 @@
       </c>
       <c r="H51" s="14"/>
       <c r="I51" s="14" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K51" s="14" t="s">
         <v>47</v>
@@ -6161,16 +6260,16 @@
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>5</v>
@@ -6183,10 +6282,10 @@
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K52" s="14" t="s">
         <v>47</v>
@@ -6194,16 +6293,16 @@
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>5</v>
@@ -6216,10 +6315,10 @@
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K53" s="14" t="s">
         <v>47</v>
@@ -6227,16 +6326,16 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>5</v>
@@ -6249,10 +6348,10 @@
       </c>
       <c r="H54" s="14"/>
       <c r="I54" s="14" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K54" s="14" t="s">
         <v>47</v>
@@ -6260,16 +6359,16 @@
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>5</v>
@@ -6282,10 +6381,10 @@
       </c>
       <c r="H55" s="14"/>
       <c r="I55" s="14" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K55" s="14" t="s">
         <v>47</v>
@@ -6293,16 +6392,16 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>5</v>
@@ -6315,10 +6414,10 @@
       </c>
       <c r="H56" s="14"/>
       <c r="I56" s="14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K56" s="14" t="s">
         <v>47</v>
@@ -6326,16 +6425,16 @@
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>5</v>
@@ -6348,10 +6447,10 @@
       </c>
       <c r="H57" s="14"/>
       <c r="I57" s="14" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K57" s="14" t="s">
         <v>47</v>
@@ -6359,16 +6458,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>5</v>
@@ -6381,10 +6480,10 @@
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K58" s="14" t="s">
         <v>47</v>
@@ -6392,16 +6491,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>5</v>
@@ -6414,10 +6513,10 @@
       </c>
       <c r="H59" s="14"/>
       <c r="I59" s="14" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K59" s="14" t="s">
         <v>47</v>
@@ -6425,16 +6524,16 @@
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>5</v>
@@ -6447,10 +6546,10 @@
       </c>
       <c r="H60" s="14"/>
       <c r="I60" s="14" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K60" s="14" t="s">
         <v>47</v>
@@ -6458,16 +6557,16 @@
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>5</v>
@@ -6480,10 +6579,10 @@
       </c>
       <c r="H61" s="14"/>
       <c r="I61" s="14" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K61" s="14" t="s">
         <v>47</v>
@@ -6491,16 +6590,16 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>5</v>
@@ -6513,10 +6612,10 @@
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="14" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K62" s="14" t="s">
         <v>47</v>
@@ -6524,16 +6623,16 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>5</v>
@@ -6546,10 +6645,10 @@
       </c>
       <c r="H63" s="14"/>
       <c r="I63" s="14" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K63" s="14" t="s">
         <v>47</v>
@@ -6557,16 +6656,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>5</v>
@@ -6579,10 +6678,10 @@
       </c>
       <c r="H64" s="14"/>
       <c r="I64" s="14" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K64" s="14" t="s">
         <v>47</v>
@@ -6590,16 +6689,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>5</v>
@@ -6612,10 +6711,10 @@
       </c>
       <c r="H65" s="14"/>
       <c r="I65" s="14" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K65" s="14" t="s">
         <v>47</v>
@@ -6623,16 +6722,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>5</v>
@@ -6645,10 +6744,10 @@
       </c>
       <c r="H66" s="14"/>
       <c r="I66" s="14" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K66" s="14" t="s">
         <v>47</v>
@@ -6656,16 +6755,16 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>5</v>
@@ -6678,10 +6777,10 @@
       </c>
       <c r="H67" s="14"/>
       <c r="I67" s="14" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J67" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K67" s="14" t="s">
         <v>47</v>
@@ -6689,16 +6788,16 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>5</v>
@@ -6711,10 +6810,10 @@
       </c>
       <c r="H68" s="14"/>
       <c r="I68" s="14" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K68" s="14" t="s">
         <v>47</v>
@@ -6722,16 +6821,16 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>5</v>
@@ -6744,10 +6843,10 @@
       </c>
       <c r="H69" s="14"/>
       <c r="I69" s="14" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K69" s="14" t="s">
         <v>47</v>
@@ -6755,16 +6854,16 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>5</v>
@@ -6777,10 +6876,10 @@
       </c>
       <c r="H70" s="14"/>
       <c r="I70" s="14" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K70" s="14" t="s">
         <v>47</v>
@@ -6788,16 +6887,16 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>5</v>
@@ -6810,10 +6909,10 @@
       </c>
       <c r="H71" s="14"/>
       <c r="I71" s="14" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K71" s="14" t="s">
         <v>47</v>
@@ -6821,16 +6920,16 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>5</v>
@@ -6843,10 +6942,10 @@
       </c>
       <c r="H72" s="14"/>
       <c r="I72" s="14" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K72" s="14" t="s">
         <v>47</v>
@@ -6854,16 +6953,16 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>5</v>
@@ -6876,10 +6975,10 @@
       </c>
       <c r="H73" s="14"/>
       <c r="I73" s="14" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K73" s="14" t="s">
         <v>47</v>
@@ -6887,16 +6986,16 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B74" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E74" s="14" t="s">
         <v>5</v>
@@ -6909,10 +7008,10 @@
       </c>
       <c r="H74" s="14"/>
       <c r="I74" s="14" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K74" s="14" t="s">
         <v>47</v>
@@ -6920,16 +7019,16 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>5</v>
@@ -6942,10 +7041,10 @@
       </c>
       <c r="H75" s="14"/>
       <c r="I75" s="14" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K75" s="14" t="s">
         <v>47</v>
@@ -6953,16 +7052,16 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E76" s="14" t="s">
         <v>5</v>
@@ -6975,10 +7074,10 @@
       </c>
       <c r="H76" s="14"/>
       <c r="I76" s="14" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K76" s="14" t="s">
         <v>47</v>
@@ -6986,16 +7085,16 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>5</v>
@@ -7008,10 +7107,10 @@
       </c>
       <c r="H77" s="14"/>
       <c r="I77" s="14" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K77" s="14" t="s">
         <v>47</v>
@@ -7019,16 +7118,16 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E78" s="14" t="s">
         <v>5</v>
@@ -7041,10 +7140,10 @@
       </c>
       <c r="H78" s="14"/>
       <c r="I78" s="14" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K78" s="14" t="s">
         <v>47</v>
@@ -7052,16 +7151,16 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>5</v>
@@ -7074,10 +7173,10 @@
       </c>
       <c r="H79" s="14"/>
       <c r="I79" s="14" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K79" s="14" t="s">
         <v>47</v>
@@ -7085,16 +7184,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E80" s="14" t="s">
         <v>5</v>
@@ -7107,10 +7206,10 @@
       </c>
       <c r="H80" s="14"/>
       <c r="I80" s="14" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K80" s="14" t="s">
         <v>47</v>
@@ -7118,16 +7217,16 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E81" s="14" t="s">
         <v>5</v>
@@ -7140,10 +7239,10 @@
       </c>
       <c r="H81" s="14"/>
       <c r="I81" s="14" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K81" s="14" t="s">
         <v>47</v>
@@ -7151,16 +7250,16 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="E82" s="14" t="s">
         <v>5</v>
@@ -7173,10 +7272,10 @@
       </c>
       <c r="H82" s="14"/>
       <c r="I82" s="14" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K82" s="14" t="s">
         <v>47</v>
@@ -7184,16 +7283,16 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>5</v>
@@ -7206,10 +7305,10 @@
       </c>
       <c r="H83" s="14"/>
       <c r="I83" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K83" s="14" t="s">
         <v>47</v>
@@ -7217,16 +7316,16 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="E84" s="14" t="s">
         <v>5</v>
@@ -7239,10 +7338,10 @@
       </c>
       <c r="H84" s="14"/>
       <c r="I84" s="14" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K84" s="14" t="s">
         <v>47</v>
@@ -7250,16 +7349,16 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E85" s="14" t="s">
         <v>5</v>
@@ -7272,10 +7371,10 @@
       </c>
       <c r="H85" s="14"/>
       <c r="I85" s="14" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K85" s="14" t="s">
         <v>47</v>
@@ -7283,16 +7382,16 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E86" s="14" t="s">
         <v>5</v>
@@ -7305,10 +7404,10 @@
       </c>
       <c r="H86" s="14"/>
       <c r="I86" s="14" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K86" s="14" t="s">
         <v>47</v>
@@ -7316,16 +7415,16 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E87" s="14" t="s">
         <v>5</v>
@@ -7338,10 +7437,10 @@
       </c>
       <c r="H87" s="14"/>
       <c r="I87" s="14" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K87" s="14" t="s">
         <v>47</v>
@@ -7349,16 +7448,16 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E88" s="14" t="s">
         <v>5</v>
@@ -7371,10 +7470,10 @@
       </c>
       <c r="H88" s="14"/>
       <c r="I88" s="14" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K88" s="14" t="s">
         <v>47</v>
@@ -7382,16 +7481,16 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E89" s="14" t="s">
         <v>5</v>
@@ -7404,10 +7503,10 @@
       </c>
       <c r="H89" s="14"/>
       <c r="I89" s="14" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K89" s="14" t="s">
         <v>47</v>
@@ -7415,16 +7514,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B90" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="E90" s="14" t="s">
         <v>5</v>
@@ -7437,10 +7536,10 @@
       </c>
       <c r="H90" s="14"/>
       <c r="I90" s="14" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K90" s="14" t="s">
         <v>47</v>
@@ -7448,16 +7547,16 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E91" s="14" t="s">
         <v>5</v>
@@ -7470,10 +7569,10 @@
       </c>
       <c r="H91" s="14"/>
       <c r="I91" s="14" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K91" s="14" t="s">
         <v>47</v>
@@ -7481,16 +7580,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="14" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B92" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E92" s="14" t="s">
         <v>5</v>
@@ -7503,10 +7602,10 @@
       </c>
       <c r="H92" s="14"/>
       <c r="I92" s="14" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K92" s="14" t="s">
         <v>47</v>
@@ -7514,16 +7613,16 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E93" s="14" t="s">
         <v>5</v>
@@ -7536,10 +7635,10 @@
       </c>
       <c r="H93" s="14"/>
       <c r="I93" s="14" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K93" s="14" t="s">
         <v>47</v>
@@ -7547,16 +7646,16 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B94" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E94" s="14" t="s">
         <v>5</v>
@@ -7569,10 +7668,10 @@
       </c>
       <c r="H94" s="14"/>
       <c r="I94" s="14" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K94" s="14" t="s">
         <v>47</v>
@@ -7580,16 +7679,16 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="14" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B95" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E95" s="14" t="s">
         <v>5</v>
@@ -7602,10 +7701,10 @@
       </c>
       <c r="H95" s="14"/>
       <c r="I95" s="14" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K95" s="14" t="s">
         <v>47</v>
@@ -7613,16 +7712,16 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="14" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E96" s="14" t="s">
         <v>5</v>
@@ -7635,10 +7734,10 @@
       </c>
       <c r="H96" s="14"/>
       <c r="I96" s="14" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K96" s="14" t="s">
         <v>47</v>
@@ -7646,16 +7745,16 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="E97" s="14" t="s">
         <v>5</v>
@@ -7668,10 +7767,10 @@
       </c>
       <c r="H97" s="14"/>
       <c r="I97" s="14" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K97" s="14" t="s">
         <v>47</v>
@@ -7679,16 +7778,16 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>5</v>
@@ -7701,10 +7800,10 @@
       </c>
       <c r="H98" s="14"/>
       <c r="I98" s="14" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K98" s="14" t="s">
         <v>47</v>
@@ -7712,16 +7811,16 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B99" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>5</v>
@@ -7734,10 +7833,10 @@
       </c>
       <c r="H99" s="14"/>
       <c r="I99" s="14" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K99" s="14" t="s">
         <v>47</v>
@@ -7745,16 +7844,16 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="14" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>5</v>
@@ -7767,10 +7866,10 @@
       </c>
       <c r="H100" s="14"/>
       <c r="I100" s="14" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K100" s="14" t="s">
         <v>47</v>
@@ -7778,16 +7877,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B101" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E101" s="14" t="s">
         <v>5</v>
@@ -7800,10 +7899,10 @@
       </c>
       <c r="H101" s="14"/>
       <c r="I101" s="14" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K101" s="14" t="s">
         <v>47</v>
@@ -7811,16 +7910,16 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="14" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B102" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E102" s="14" t="s">
         <v>5</v>
@@ -7833,10 +7932,10 @@
       </c>
       <c r="H102" s="14"/>
       <c r="I102" s="14" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K102" s="14" t="s">
         <v>47</v>
@@ -7844,16 +7943,16 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="14" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E103" s="14" t="s">
         <v>5</v>
@@ -7866,10 +7965,10 @@
       </c>
       <c r="H103" s="14"/>
       <c r="I103" s="14" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="J103" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K103" s="14" t="s">
         <v>47</v>
@@ -7877,16 +7976,16 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="14" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E104" s="14" t="s">
         <v>5</v>
@@ -7899,10 +7998,10 @@
       </c>
       <c r="H104" s="14"/>
       <c r="I104" s="14" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K104" s="14" t="s">
         <v>47</v>
@@ -7910,16 +8009,16 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="E105" s="14" t="s">
         <v>3</v>
@@ -7932,10 +8031,10 @@
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="14" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="K105" s="14" t="s">
         <v>47</v>
@@ -7943,16 +8042,16 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="14" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>5</v>
@@ -7965,10 +8064,10 @@
       </c>
       <c r="H106" s="14"/>
       <c r="I106" s="14" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K106" s="14" t="s">
         <v>47</v>
@@ -7976,16 +8075,16 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="14" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B107" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>5</v>
@@ -7998,10 +8097,10 @@
       </c>
       <c r="H107" s="14"/>
       <c r="I107" s="14" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K107" s="14" t="s">
         <v>47</v>
@@ -8009,16 +8108,16 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="14" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B108" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E108" s="14" t="s">
         <v>5</v>
@@ -8031,10 +8130,10 @@
       </c>
       <c r="H108" s="14"/>
       <c r="I108" s="14" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K108" s="14" t="s">
         <v>47</v>
@@ -8042,16 +8141,16 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="14" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="E109" s="14" t="s">
         <v>5</v>
@@ -8064,10 +8163,10 @@
       </c>
       <c r="H109" s="14"/>
       <c r="I109" s="14" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K109" s="14" t="s">
         <v>47</v>
@@ -8075,16 +8174,16 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="14" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B110" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>5</v>
@@ -8097,10 +8196,10 @@
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="14" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K110" s="14" t="s">
         <v>47</v>
@@ -8108,16 +8207,16 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="14" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B111" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E111" s="14" t="s">
         <v>5</v>
@@ -8130,10 +8229,10 @@
       </c>
       <c r="H111" s="14"/>
       <c r="I111" s="14" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="J111" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K111" s="14" t="s">
         <v>47</v>
@@ -8141,16 +8240,16 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="14" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B112" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E112" s="14" t="s">
         <v>5</v>
@@ -8163,10 +8262,10 @@
       </c>
       <c r="H112" s="14"/>
       <c r="I112" s="14" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K112" s="14" t="s">
         <v>47</v>
@@ -8174,16 +8273,16 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="14" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B113" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E113" s="14" t="s">
         <v>5</v>
@@ -8196,10 +8295,10 @@
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="14" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="J113" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K113" s="14" t="s">
         <v>47</v>
@@ -8207,16 +8306,16 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="14" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B114" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E114" s="14" t="s">
         <v>5</v>
@@ -8229,10 +8328,10 @@
       </c>
       <c r="H114" s="14"/>
       <c r="I114" s="14" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="J114" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K114" s="14" t="s">
         <v>47</v>
@@ -8240,16 +8339,16 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B115" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E115" s="14" t="s">
         <v>5</v>
@@ -8262,10 +8361,10 @@
       </c>
       <c r="H115" s="14"/>
       <c r="I115" s="14" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="J115" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K115" s="14" t="s">
         <v>47</v>
@@ -8273,16 +8372,16 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="14" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B116" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E116" s="14" t="s">
         <v>5</v>
@@ -8295,10 +8394,10 @@
       </c>
       <c r="H116" s="14"/>
       <c r="I116" s="14" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K116" s="14" t="s">
         <v>47</v>
@@ -8306,16 +8405,16 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="14" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="E117" s="14" t="s">
         <v>5</v>
@@ -8328,10 +8427,10 @@
       </c>
       <c r="H117" s="14"/>
       <c r="I117" s="14" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="J117" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K117" s="14" t="s">
         <v>47</v>
@@ -8339,16 +8438,16 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="14" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="E118" s="14" t="s">
         <v>5</v>
@@ -8361,10 +8460,10 @@
       </c>
       <c r="H118" s="14"/>
       <c r="I118" s="14" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="J118" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K118" s="14" t="s">
         <v>47</v>
@@ -8372,16 +8471,16 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="14" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="E119" s="14" t="s">
         <v>5</v>
@@ -8394,10 +8493,10 @@
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="14" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="J119" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K119" s="14" t="s">
         <v>47</v>
@@ -8405,16 +8504,16 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="14" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E120" s="14" t="s">
         <v>3</v>
@@ -8427,10 +8526,10 @@
       </c>
       <c r="H120" s="14"/>
       <c r="I120" s="14" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="J120" s="14" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="K120" s="14" t="s">
         <v>47</v>
@@ -8438,16 +8537,16 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="14" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B121" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="E121" s="14" t="s">
         <v>5</v>
@@ -8460,10 +8559,10 @@
       </c>
       <c r="H121" s="14"/>
       <c r="I121" s="14" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="J121" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K121" s="14" t="s">
         <v>47</v>
@@ -8471,16 +8570,16 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="14" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B122" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E122" s="14" t="s">
         <v>5</v>
@@ -8493,10 +8592,10 @@
       </c>
       <c r="H122" s="14"/>
       <c r="I122" s="14" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="J122" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K122" s="14" t="s">
         <v>47</v>
@@ -8504,16 +8603,16 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="14" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E123" s="14" t="s">
         <v>5</v>
@@ -8526,10 +8625,10 @@
       </c>
       <c r="H123" s="14"/>
       <c r="I123" s="14" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K123" s="14" t="s">
         <v>47</v>
@@ -8537,16 +8636,16 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="14" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B124" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="E124" s="14" t="s">
         <v>5</v>
@@ -8559,10 +8658,10 @@
       </c>
       <c r="H124" s="14"/>
       <c r="I124" s="14" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="J124" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K124" s="14" t="s">
         <v>47</v>
@@ -8570,16 +8669,16 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="14" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B125" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="E125" s="14" t="s">
         <v>5</v>
@@ -8592,10 +8691,10 @@
       </c>
       <c r="H125" s="14"/>
       <c r="I125" s="14" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="J125" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K125" s="14" t="s">
         <v>47</v>
@@ -8603,16 +8702,16 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="14" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B126" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="E126" s="14" t="s">
         <v>5</v>
@@ -8625,10 +8724,10 @@
       </c>
       <c r="H126" s="14"/>
       <c r="I126" s="14" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="J126" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K126" s="14" t="s">
         <v>47</v>
@@ -8636,16 +8735,16 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="14" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B127" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E127" s="14" t="s">
         <v>5</v>
@@ -8658,10 +8757,10 @@
       </c>
       <c r="H127" s="14"/>
       <c r="I127" s="14" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="J127" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K127" s="14" t="s">
         <v>47</v>
@@ -8669,16 +8768,16 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="14" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B128" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E128" s="14" t="s">
         <v>5</v>
@@ -8691,10 +8790,10 @@
       </c>
       <c r="H128" s="14"/>
       <c r="I128" s="14" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="J128" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K128" s="14" t="s">
         <v>47</v>
@@ -8702,16 +8801,16 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="14" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B129" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E129" s="14" t="s">
         <v>5</v>
@@ -8724,10 +8823,10 @@
       </c>
       <c r="H129" s="14"/>
       <c r="I129" s="14" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="J129" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K129" s="14" t="s">
         <v>47</v>
@@ -8735,16 +8834,16 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="14" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="E130" s="14" t="s">
         <v>5</v>
@@ -8757,10 +8856,10 @@
       </c>
       <c r="H130" s="14"/>
       <c r="I130" s="14" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="J130" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K130" s="14" t="s">
         <v>47</v>
@@ -8768,16 +8867,16 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="14" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B131" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="E131" s="14" t="s">
         <v>5</v>
@@ -8790,10 +8889,10 @@
       </c>
       <c r="H131" s="14"/>
       <c r="I131" s="14" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K131" s="14" t="s">
         <v>47</v>
@@ -8801,16 +8900,16 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="14" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B132" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="E132" s="14" t="s">
         <v>5</v>
@@ -8823,10 +8922,10 @@
       </c>
       <c r="H132" s="14"/>
       <c r="I132" s="14" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="J132" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K132" s="14" t="s">
         <v>47</v>
@@ -8834,16 +8933,16 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="14" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B133" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="E133" s="14" t="s">
         <v>5</v>
@@ -8856,10 +8955,10 @@
       </c>
       <c r="H133" s="14"/>
       <c r="I133" s="14" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K133" s="14" t="s">
         <v>47</v>
@@ -8867,16 +8966,16 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="14" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B134" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="E134" s="14" t="s">
         <v>5</v>
@@ -8889,10 +8988,10 @@
       </c>
       <c r="H134" s="14"/>
       <c r="I134" s="14" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="J134" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K134" s="14" t="s">
         <v>47</v>
@@ -8900,16 +8999,16 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="14" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B135" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E135" s="14" t="s">
         <v>5</v>
@@ -8922,10 +9021,10 @@
       </c>
       <c r="H135" s="14"/>
       <c r="I135" s="14" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K135" s="14" t="s">
         <v>47</v>
@@ -8933,16 +9032,16 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="14" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B136" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="E136" s="14" t="s">
         <v>5</v>
@@ -8955,10 +9054,10 @@
       </c>
       <c r="H136" s="14"/>
       <c r="I136" s="14" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K136" s="14" t="s">
         <v>47</v>
@@ -8966,16 +9065,16 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="14" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E137" s="14" t="s">
         <v>5</v>
@@ -8988,10 +9087,10 @@
       </c>
       <c r="H137" s="14"/>
       <c r="I137" s="14" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="J137" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K137" s="14" t="s">
         <v>47</v>
@@ -8999,16 +9098,16 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="14" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B138" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="E138" s="14" t="s">
         <v>5</v>
@@ -9021,10 +9120,10 @@
       </c>
       <c r="H138" s="14"/>
       <c r="I138" s="14" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K138" s="14" t="s">
         <v>47</v>
@@ -9032,16 +9131,16 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="14" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B139" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="E139" s="14" t="s">
         <v>5</v>
@@ -9054,10 +9153,10 @@
       </c>
       <c r="H139" s="14"/>
       <c r="I139" s="14" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="J139" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K139" s="14" t="s">
         <v>47</v>
@@ -9065,16 +9164,16 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="14" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B140" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="E140" s="14" t="s">
         <v>5</v>
@@ -9087,10 +9186,10 @@
       </c>
       <c r="H140" s="14"/>
       <c r="I140" s="14" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="J140" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K140" s="14" t="s">
         <v>47</v>
@@ -9098,16 +9197,16 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="14" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B141" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D141" s="14" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="E141" s="14" t="s">
         <v>5</v>
@@ -9120,10 +9219,10 @@
       </c>
       <c r="H141" s="14"/>
       <c r="I141" s="14" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="J141" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K141" s="14" t="s">
         <v>47</v>
@@ -9131,16 +9230,16 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="14" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B142" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D142" s="14" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E142" s="14" t="s">
         <v>5</v>
@@ -9153,10 +9252,10 @@
       </c>
       <c r="H142" s="14"/>
       <c r="I142" s="14" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="J142" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K142" s="14" t="s">
         <v>47</v>
@@ -9164,16 +9263,16 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="14" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B143" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D143" s="14" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E143" s="14" t="s">
         <v>5</v>
@@ -9186,10 +9285,10 @@
       </c>
       <c r="H143" s="14"/>
       <c r="I143" s="14" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="J143" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K143" s="14" t="s">
         <v>47</v>
@@ -9197,16 +9296,16 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="14" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B144" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="E144" s="14" t="s">
         <v>5</v>
@@ -9219,10 +9318,10 @@
       </c>
       <c r="H144" s="14"/>
       <c r="I144" s="14" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="J144" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K144" s="14" t="s">
         <v>47</v>
@@ -9230,16 +9329,16 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="14" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B145" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D145" s="14" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E145" s="14" t="s">
         <v>5</v>
@@ -9252,10 +9351,10 @@
       </c>
       <c r="H145" s="14"/>
       <c r="I145" s="14" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="J145" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K145" s="14" t="s">
         <v>47</v>
@@ -9263,16 +9362,16 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="14" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B146" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D146" s="14" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="E146" s="14" t="s">
         <v>5</v>
@@ -9285,10 +9384,10 @@
       </c>
       <c r="H146" s="14"/>
       <c r="I146" s="14" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="J146" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K146" s="14" t="s">
         <v>47</v>
@@ -9296,16 +9395,16 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="14" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B147" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="E147" s="14" t="s">
         <v>5</v>
@@ -9318,7 +9417,7 @@
       </c>
       <c r="H147" s="14"/>
       <c r="I147" s="14" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="J147" s="14"/>
       <c r="K147" s="14" t="s">
@@ -9327,16 +9426,16 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="14" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B148" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="E148" s="14" t="s">
         <v>5</v>
@@ -9349,7 +9448,7 @@
       </c>
       <c r="H148" s="14"/>
       <c r="I148" s="14" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="J148" s="14"/>
       <c r="K148" s="14" t="s">
@@ -9358,16 +9457,16 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="14" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B149" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="E149" s="14" t="s">
         <v>5</v>
@@ -9380,7 +9479,7 @@
       </c>
       <c r="H149" s="14"/>
       <c r="I149" s="14" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J149" s="14"/>
       <c r="K149" s="14" t="s">
@@ -9389,16 +9488,16 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="14" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B150" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="D150" s="14" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="E150" s="14" t="s">
         <v>5</v>
@@ -9411,7 +9510,7 @@
       </c>
       <c r="H150" s="14"/>
       <c r="I150" s="14" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="J150" s="14"/>
       <c r="K150" s="14" t="s">
@@ -9420,16 +9519,16 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="14" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="B151" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D151" s="14" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="E151" s="14" t="s">
         <v>5</v>
@@ -9442,7 +9541,7 @@
       </c>
       <c r="H151" s="14"/>
       <c r="I151" s="14" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="J151" s="14"/>
       <c r="K151" s="14" t="s">
@@ -9451,16 +9550,16 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="14" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="B152" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E152" s="14" t="s">
         <v>5</v>
@@ -9473,7 +9572,7 @@
       </c>
       <c r="H152" s="14"/>
       <c r="I152" s="14" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="J152" s="14"/>
       <c r="K152" s="14" t="s">
@@ -9482,16 +9581,16 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="14" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="B153" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="D153" s="14" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="E153" s="14" t="s">
         <v>5</v>
@@ -9504,7 +9603,7 @@
       </c>
       <c r="H153" s="14"/>
       <c r="I153" s="14" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="J153" s="14"/>
       <c r="K153" s="14" t="s">
@@ -9513,16 +9612,16 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="14" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B154" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="D154" s="14" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="E154" s="14" t="s">
         <v>5</v>
@@ -9535,7 +9634,7 @@
       </c>
       <c r="H154" s="14"/>
       <c r="I154" s="14" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="J154" s="14"/>
       <c r="K154" s="14" t="s">
@@ -9544,16 +9643,16 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="14" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="B155" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="D155" s="14" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="E155" s="14" t="s">
         <v>5</v>
@@ -9566,7 +9665,7 @@
       </c>
       <c r="H155" s="14"/>
       <c r="I155" s="14" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="J155" s="14"/>
       <c r="K155" s="14" t="s">
@@ -9575,16 +9674,16 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="14" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="B156" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="D156" s="14" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="E156" s="14" t="s">
         <v>5</v>
@@ -9597,7 +9696,7 @@
       </c>
       <c r="H156" s="14"/>
       <c r="I156" s="14" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="J156" s="14"/>
       <c r="K156" s="14" t="s">
@@ -9606,16 +9705,16 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="14" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="B157" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="D157" s="14" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>5</v>
@@ -9628,7 +9727,7 @@
       </c>
       <c r="H157" s="14"/>
       <c r="I157" s="14" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="J157" s="14"/>
       <c r="K157" s="14" t="s">
@@ -9637,16 +9736,16 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="14" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="B158" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E158" s="14" t="s">
         <v>5</v>
@@ -9659,7 +9758,7 @@
       </c>
       <c r="H158" s="14"/>
       <c r="I158" s="14" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="J158" s="14"/>
       <c r="K158" s="14" t="s">
@@ -9668,16 +9767,16 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="14" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="B159" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="D159" s="14" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E159" s="14" t="s">
         <v>5</v>
@@ -9690,7 +9789,7 @@
       </c>
       <c r="H159" s="14"/>
       <c r="I159" s="14" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="J159" s="14"/>
       <c r="K159" s="14" t="s">
@@ -9699,16 +9798,16 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="14" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="B160" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="E160" s="14" t="s">
         <v>5</v>
@@ -9721,7 +9820,7 @@
       </c>
       <c r="H160" s="14"/>
       <c r="I160" s="14" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="J160" s="14"/>
       <c r="K160" s="14" t="s">
@@ -9730,16 +9829,16 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="14" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="B161" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="E161" s="14" t="s">
         <v>5</v>
@@ -9752,7 +9851,7 @@
       </c>
       <c r="H161" s="14"/>
       <c r="I161" s="14" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="J161" s="14"/>
       <c r="K161" s="14" t="s">
@@ -9761,16 +9860,16 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="14" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="B162" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="D162" s="14" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="E162" s="14" t="s">
         <v>5</v>
@@ -9783,7 +9882,7 @@
       </c>
       <c r="H162" s="14"/>
       <c r="I162" s="14" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="J162" s="14"/>
       <c r="K162" s="14" t="s">
@@ -9792,16 +9891,16 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="14" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="B163" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="D163" s="14" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="E163" s="14" t="s">
         <v>5</v>
@@ -9814,7 +9913,7 @@
       </c>
       <c r="H163" s="14"/>
       <c r="I163" s="14" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="J163" s="14"/>
       <c r="K163" s="14" t="s">
@@ -9823,16 +9922,16 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="14" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="B164" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="D164" s="14" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="E164" s="14" t="s">
         <v>5</v>
@@ -9845,7 +9944,7 @@
       </c>
       <c r="H164" s="14"/>
       <c r="I164" s="14" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="J164" s="14"/>
       <c r="K164" s="14" t="s">
@@ -9854,16 +9953,16 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="14" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="B165" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="D165" s="14" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="E165" s="14" t="s">
         <v>5</v>
@@ -9876,7 +9975,7 @@
       </c>
       <c r="H165" s="14"/>
       <c r="I165" s="14" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="J165" s="14"/>
       <c r="K165" s="14" t="s">
@@ -9885,16 +9984,16 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="14" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B166" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="D166" s="14" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="E166" s="14" t="s">
         <v>5</v>
@@ -9907,7 +10006,7 @@
       </c>
       <c r="H166" s="14"/>
       <c r="I166" s="14" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="J166" s="14"/>
       <c r="K166" s="14" t="s">
@@ -9916,16 +10015,16 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="14" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B167" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="E167" s="14" t="s">
         <v>5</v>
@@ -9938,7 +10037,7 @@
       </c>
       <c r="H167" s="14"/>
       <c r="I167" s="14" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="J167" s="14"/>
       <c r="K167" s="14" t="s">
@@ -9947,16 +10046,16 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="14" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B168" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="E168" s="14" t="s">
         <v>5</v>
@@ -9969,7 +10068,7 @@
       </c>
       <c r="H168" s="14"/>
       <c r="I168" s="14" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="J168" s="14"/>
       <c r="K168" s="14" t="s">
@@ -9978,16 +10077,16 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="14" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B169" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="E169" s="14" t="s">
         <v>5</v>
@@ -10000,7 +10099,7 @@
       </c>
       <c r="H169" s="14"/>
       <c r="I169" s="14" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="J169" s="14"/>
       <c r="K169" s="14" t="s">
@@ -10009,16 +10108,16 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="14" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B170" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E170" s="14" t="s">
         <v>5</v>
@@ -10031,7 +10130,7 @@
       </c>
       <c r="H170" s="14"/>
       <c r="I170" s="14" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="J170" s="14"/>
       <c r="K170" s="14" t="s">
@@ -10040,16 +10139,16 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="14" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B171" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="E171" s="14" t="s">
         <v>5</v>
@@ -10062,7 +10161,7 @@
       </c>
       <c r="H171" s="14"/>
       <c r="I171" s="14" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="J171" s="14"/>
       <c r="K171" s="14" t="s">
@@ -10071,16 +10170,16 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="14" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B172" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="E172" s="14" t="s">
         <v>5</v>
@@ -10093,7 +10192,7 @@
       </c>
       <c r="H172" s="14"/>
       <c r="I172" s="14" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="J172" s="14"/>
       <c r="K172" s="14" t="s">
@@ -10102,16 +10201,16 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B173" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="E173" s="14" t="s">
         <v>5</v>
@@ -10124,7 +10223,7 @@
       </c>
       <c r="H173" s="14"/>
       <c r="I173" s="14" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="J173" s="14"/>
       <c r="K173" s="14" t="s">
@@ -10133,16 +10232,16 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="14" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="B174" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="D174" s="14" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="E174" s="14" t="s">
         <v>5</v>
@@ -10155,7 +10254,7 @@
       </c>
       <c r="H174" s="14"/>
       <c r="I174" s="14" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="J174" s="14"/>
       <c r="K174" s="14" t="s">
@@ -10164,16 +10263,16 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="14" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B175" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="D175" s="14" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="E175" s="14" t="s">
         <v>5</v>
@@ -10186,7 +10285,7 @@
       </c>
       <c r="H175" s="14"/>
       <c r="I175" s="14" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="J175" s="14"/>
       <c r="K175" s="14" t="s">
@@ -10195,16 +10294,16 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="14" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B176" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="D176" s="14" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="E176" s="14" t="s">
         <v>5</v>
@@ -10217,7 +10316,7 @@
       </c>
       <c r="H176" s="14"/>
       <c r="I176" s="14" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="J176" s="14"/>
       <c r="K176" s="14" t="s">
@@ -10226,16 +10325,16 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="14" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="B177" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="E177" s="14" t="s">
         <v>5</v>
@@ -10248,7 +10347,7 @@
       </c>
       <c r="H177" s="14"/>
       <c r="I177" s="14" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="J177" s="14"/>
       <c r="K177" s="14" t="s">
@@ -10257,16 +10356,16 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="14" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="B178" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="E178" s="14" t="s">
         <v>5</v>
@@ -10279,7 +10378,7 @@
       </c>
       <c r="H178" s="14"/>
       <c r="I178" s="14" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="J178" s="14"/>
       <c r="K178" s="14" t="s">
@@ -10288,16 +10387,16 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="14" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="B179" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="E179" s="14" t="s">
         <v>5</v>
@@ -10310,7 +10409,7 @@
       </c>
       <c r="H179" s="14"/>
       <c r="I179" s="14" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="J179" s="14"/>
       <c r="K179" s="14" t="s">
@@ -10319,16 +10418,16 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="14" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="B180" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="E180" s="14" t="s">
         <v>5</v>
@@ -10341,7 +10440,7 @@
       </c>
       <c r="H180" s="14"/>
       <c r="I180" s="14" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="J180" s="14"/>
       <c r="K180" s="14" t="s">
@@ -10350,16 +10449,16 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="14" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="B181" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="E181" s="14" t="s">
         <v>5</v>
@@ -10372,7 +10471,7 @@
       </c>
       <c r="H181" s="14"/>
       <c r="I181" s="14" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="J181" s="14"/>
       <c r="K181" s="14" t="s">
@@ -10381,16 +10480,16 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="14" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B182" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="E182" s="14" t="s">
         <v>5</v>
@@ -10403,7 +10502,7 @@
       </c>
       <c r="H182" s="14"/>
       <c r="I182" s="14" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="J182" s="14"/>
       <c r="K182" s="14" t="s">
@@ -10412,16 +10511,16 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="14" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="B183" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E183" s="14" t="s">
         <v>3</v>
@@ -10434,10 +10533,10 @@
       </c>
       <c r="H183" s="14"/>
       <c r="I183" s="14" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="J183" s="14" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="K183" s="14" t="s">
         <v>47</v>
@@ -10445,16 +10544,16 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="14" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="B184" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="D184" s="14" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E184" s="14" t="s">
         <v>3</v>
@@ -10467,10 +10566,10 @@
       </c>
       <c r="H184" s="14"/>
       <c r="I184" s="14" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="J184" s="14" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="K184" s="14" t="s">
         <v>47</v>
@@ -10478,16 +10577,16 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="14" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="B185" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E185" s="14" t="s">
         <v>6</v>
@@ -10501,7 +10600,7 @@
       <c r="H185" s="14"/>
       <c r="I185" s="14"/>
       <c r="J185" s="14" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="K185" s="14" t="s">
         <v>47</v>
@@ -10509,16 +10608,16 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="14" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="B186" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="E186" s="14" t="s">
         <v>5</v>
@@ -10531,7 +10630,7 @@
       </c>
       <c r="H186" s="14"/>
       <c r="I186" s="14" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="J186" s="14"/>
       <c r="K186" s="14" t="s">
@@ -10540,16 +10639,16 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="14" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B187" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="D187" s="14" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="E187" s="14" t="s">
         <v>5</v>
@@ -10562,7 +10661,7 @@
       </c>
       <c r="H187" s="14"/>
       <c r="I187" s="14" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="J187" s="14"/>
       <c r="K187" s="14" t="s">
@@ -10571,16 +10670,16 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="14" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="B188" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="D188" s="14" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="E188" s="14" t="s">
         <v>5</v>
@@ -10593,7 +10692,7 @@
       </c>
       <c r="H188" s="14"/>
       <c r="I188" s="14" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="J188" s="14"/>
       <c r="K188" s="14" t="s">
@@ -10602,16 +10701,16 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="14" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="B189" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="D189" s="14" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="E189" s="14" t="s">
         <v>5</v>
@@ -10624,7 +10723,7 @@
       </c>
       <c r="H189" s="14"/>
       <c r="I189" s="14" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="J189" s="14"/>
       <c r="K189" s="14" t="s">
@@ -10633,16 +10732,16 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="14" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B190" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="E190" s="14" t="s">
         <v>5</v>
@@ -10655,7 +10754,7 @@
       </c>
       <c r="H190" s="14"/>
       <c r="I190" s="14" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="J190" s="14"/>
       <c r="K190" s="14" t="s">
@@ -10664,16 +10763,16 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="14" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="B191" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C191" s="14" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="D191" s="14" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="E191" s="14" t="s">
         <v>5</v>
@@ -10686,7 +10785,7 @@
       </c>
       <c r="H191" s="14"/>
       <c r="I191" s="14" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="J191" s="14"/>
       <c r="K191" s="14" t="s">
@@ -10695,16 +10794,16 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="14" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="B192" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="D192" s="14" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="E192" s="14" t="s">
         <v>5</v>
@@ -10717,7 +10816,7 @@
       </c>
       <c r="H192" s="14"/>
       <c r="I192" s="14" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="J192" s="14"/>
       <c r="K192" s="14" t="s">
@@ -10726,16 +10825,16 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="14" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="B193" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E193" s="14" t="s">
         <v>5</v>
@@ -10748,7 +10847,7 @@
       </c>
       <c r="H193" s="14"/>
       <c r="I193" s="14" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="J193" s="14"/>
       <c r="K193" s="14" t="s">
@@ -10757,16 +10856,16 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="14" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="B194" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="D194" s="14" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="E194" s="14" t="s">
         <v>5</v>
@@ -10779,7 +10878,7 @@
       </c>
       <c r="H194" s="14"/>
       <c r="I194" s="14" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="J194" s="14"/>
       <c r="K194" s="14" t="s">
@@ -10788,16 +10887,16 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="14" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="B195" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="E195" s="14" t="s">
         <v>5</v>
@@ -10810,7 +10909,7 @@
       </c>
       <c r="H195" s="14"/>
       <c r="I195" s="14" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="J195" s="14"/>
       <c r="K195" s="14" t="s">
@@ -10819,16 +10918,16 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="14" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="B196" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="E196" s="14" t="s">
         <v>5</v>
@@ -10841,7 +10940,7 @@
       </c>
       <c r="H196" s="14"/>
       <c r="I196" s="14" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="J196" s="14"/>
       <c r="K196" s="14" t="s">
@@ -10850,16 +10949,16 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="14" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B197" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="E197" s="14" t="s">
         <v>5</v>
@@ -10872,7 +10971,7 @@
       </c>
       <c r="H197" s="14"/>
       <c r="I197" s="14" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="J197" s="14"/>
       <c r="K197" s="14" t="s">
@@ -10881,16 +10980,16 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="14" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B198" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="E198" s="14" t="s">
         <v>5</v>
@@ -10903,7 +11002,7 @@
       </c>
       <c r="H198" s="14"/>
       <c r="I198" s="14" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="J198" s="14"/>
       <c r="K198" s="14" t="s">
@@ -10912,16 +11011,16 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="14" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C199" s="14" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D199" s="14" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="E199" s="14" t="s">
         <v>5</v>
@@ -10934,7 +11033,7 @@
       </c>
       <c r="H199" s="14"/>
       <c r="I199" s="14" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="J199" s="14"/>
       <c r="K199" s="14" t="s">
@@ -10943,16 +11042,16 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="14" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B200" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="D200" s="14" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="E200" s="14" t="s">
         <v>5</v>
@@ -10965,7 +11064,7 @@
       </c>
       <c r="H200" s="14"/>
       <c r="I200" s="14" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="J200" s="14"/>
       <c r="K200" s="14" t="s">
@@ -10974,16 +11073,16 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="14" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B201" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C201" s="14" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="D201" s="14" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="E201" s="14" t="s">
         <v>5</v>
@@ -10996,7 +11095,7 @@
       </c>
       <c r="H201" s="14"/>
       <c r="I201" s="14" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="J201" s="14"/>
       <c r="K201" s="14" t="s">
@@ -11005,16 +11104,16 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="14" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="B202" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="D202" s="14" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="E202" s="14" t="s">
         <v>5</v>
@@ -11027,7 +11126,7 @@
       </c>
       <c r="H202" s="14"/>
       <c r="I202" s="14" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="J202" s="14"/>
       <c r="K202" s="14" t="s">
@@ -11036,16 +11135,16 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="14" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B203" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C203" s="14" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="D203" s="14" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="E203" s="14" t="s">
         <v>5</v>
@@ -11058,7 +11157,7 @@
       </c>
       <c r="H203" s="14"/>
       <c r="I203" s="14" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="J203" s="14"/>
       <c r="K203" s="14" t="s">
@@ -11067,13 +11166,13 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="14" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="B204" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="D204" s="14" t="s">
         <v>44</v>
@@ -11089,10 +11188,10 @@
       </c>
       <c r="H204" s="14"/>
       <c r="I204" s="14" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="K204" s="14" t="s">
         <v>47</v>
@@ -11100,16 +11199,16 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="14" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="B205" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C205" s="14" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="D205" s="14" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="E205" s="14" t="s">
         <v>3</v>
@@ -11124,10 +11223,10 @@
         <v>13</v>
       </c>
       <c r="I205" s="14" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="J205" s="14" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="K205" s="14" t="s">
         <v>47</v>
@@ -11135,16 +11234,16 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="14" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="B206" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="D206" s="14" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="E206" s="14" t="s">
         <v>5</v>
@@ -11157,10 +11256,10 @@
       </c>
       <c r="H206" s="14"/>
       <c r="I206" s="14" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="J206" s="14" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="K206" s="14" t="s">
         <v>47</v>
@@ -11168,16 +11267,16 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="14" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C207" s="14" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="D207" s="14" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="E207" s="14" t="s">
         <v>5</v>
@@ -11190,7 +11289,7 @@
       </c>
       <c r="H207" s="14"/>
       <c r="I207" s="14" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="J207" s="14"/>
       <c r="K207" s="14" t="s">
@@ -11199,16 +11298,16 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="14" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="B208" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="D208" s="14" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="E208" s="14" t="s">
         <v>5</v>
@@ -11221,7 +11320,7 @@
       </c>
       <c r="H208" s="14"/>
       <c r="I208" s="14" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="J208" s="14"/>
       <c r="K208" s="14" t="s">
@@ -11230,16 +11329,16 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="14" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="B209" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C209" s="14" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="E209" s="14" t="s">
         <v>5</v>
@@ -11252,7 +11351,7 @@
       </c>
       <c r="H209" s="14"/>
       <c r="I209" s="14" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="J209" s="14"/>
       <c r="K209" s="14" t="s">
@@ -11261,16 +11360,16 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="14" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B210" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="E210" s="14" t="s">
         <v>5</v>
@@ -11283,7 +11382,7 @@
       </c>
       <c r="H210" s="14"/>
       <c r="I210" s="14" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="J210" s="14"/>
       <c r="K210" s="14" t="s">
@@ -11292,16 +11391,16 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="14" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="E211" s="14" t="s">
         <v>7</v>
@@ -11315,7 +11414,7 @@
       <c r="H211" s="14"/>
       <c r="I211" s="14"/>
       <c r="J211" s="14" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="K211" s="14" t="s">
         <v>47</v>
@@ -11323,16 +11422,16 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="14" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="B212" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="D212" s="14" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="E212" s="14" t="s">
         <v>5</v>
@@ -11345,10 +11444,10 @@
       </c>
       <c r="H212" s="14"/>
       <c r="I212" s="14" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="J212" s="14" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="K212" s="14" t="s">
         <v>47</v>
@@ -11356,16 +11455,16 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="14" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C213" s="14" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="D213" s="14" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="E213" s="14" t="s">
         <v>5</v>
@@ -11378,10 +11477,10 @@
       </c>
       <c r="H213" s="14"/>
       <c r="I213" s="14" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="J213" s="14" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="K213" s="14" t="s">
         <v>47</v>
@@ -11389,16 +11488,16 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="14" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="B214" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="D214" s="14" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="E214" s="14" t="s">
         <v>3</v>
@@ -11411,10 +11510,10 @@
       </c>
       <c r="H214" s="14"/>
       <c r="I214" s="14" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="J214" s="14" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="K214" s="14" t="s">
         <v>47</v>
@@ -11422,16 +11521,16 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="14" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="B215" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C215" s="14" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="D215" s="14" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="E215" s="14" t="s">
         <v>5</v>
@@ -11444,10 +11543,10 @@
       </c>
       <c r="H215" s="14"/>
       <c r="I215" s="14" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="J215" s="14" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="K215" s="14" t="s">
         <v>47</v>
@@ -11455,16 +11554,16 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="14" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="B216" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="D216" s="14" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="E216" s="14" t="s">
         <v>5</v>
@@ -11477,7 +11576,7 @@
       </c>
       <c r="H216" s="14"/>
       <c r="I216" s="14" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="J216" s="14"/>
       <c r="K216" s="14" t="s">
@@ -11486,16 +11585,16 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="14" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="B217" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C217" s="14" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="D217" s="14" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="E217" s="14" t="s">
         <v>5</v>
@@ -11508,7 +11607,7 @@
       </c>
       <c r="H217" s="14"/>
       <c r="I217" s="14" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="J217" s="14"/>
       <c r="K217" s="14" t="s">
@@ -11517,16 +11616,16 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="14" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="B218" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="E218" s="14" t="s">
         <v>5</v>
@@ -11539,10 +11638,10 @@
       </c>
       <c r="H218" s="14"/>
       <c r="I218" s="14" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="J218" s="14" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="K218" s="14" t="s">
         <v>47</v>
@@ -11550,16 +11649,16 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="14" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B219" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C219" s="14" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="D219" s="14" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="E219" s="14" t="s">
         <v>5</v>
@@ -11572,7 +11671,7 @@
       </c>
       <c r="H219" s="14"/>
       <c r="I219" s="14" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="J219" s="14"/>
       <c r="K219" s="14" t="s">
@@ -11581,16 +11680,16 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="14" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B220" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="E220" s="14" t="s">
         <v>3</v>
@@ -11605,10 +11704,10 @@
         <v>14</v>
       </c>
       <c r="I220" s="14" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="J220" s="14" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="K220" s="14" t="s">
         <v>47</v>
@@ -11616,16 +11715,16 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="14" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="B221" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="D221" s="14" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="E221" s="14" t="s">
         <v>5</v>
@@ -11638,10 +11737,10 @@
       </c>
       <c r="H221" s="14"/>
       <c r="I221" s="14" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="J221" s="14" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="K221" s="14" t="s">
         <v>47</v>
@@ -11649,16 +11748,16 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="14" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D222" s="14" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="E222" s="14" t="s">
         <v>5</v>
@@ -11671,7 +11770,7 @@
       </c>
       <c r="H222" s="14"/>
       <c r="I222" s="14" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="J222" s="14"/>
       <c r="K222" s="14" t="s">
@@ -11680,16 +11779,16 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="14" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B223" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="E223" s="14" t="s">
         <v>5</v>
@@ -11703,7 +11802,7 @@
       <c r="H223" s="14"/>
       <c r="I223" s="14"/>
       <c r="J223" s="14" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="K223" s="14" t="s">
         <v>47</v>
@@ -11711,16 +11810,16 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="14" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="D224" s="14" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="E224" s="14" t="s">
         <v>5</v>
@@ -11740,16 +11839,16 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="14" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="B225" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C225" s="14" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="D225" s="14" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="E225" s="14" t="s">
         <v>5</v>
@@ -11763,7 +11862,7 @@
       <c r="H225" s="14"/>
       <c r="I225" s="14"/>
       <c r="J225" s="14" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="K225" s="14" t="s">
         <v>47</v>
@@ -11771,16 +11870,16 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="14" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="B226" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="D226" s="14" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="E226" s="14" t="s">
         <v>5</v>
@@ -11800,16 +11899,16 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="14" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="B227" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C227" s="14" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="D227" s="14" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="E227" s="14" t="s">
         <v>5</v>
@@ -11823,7 +11922,7 @@
       <c r="H227" s="14"/>
       <c r="I227" s="14"/>
       <c r="J227" s="14" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="K227" s="14" t="s">
         <v>47</v>
@@ -11831,16 +11930,16 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="14" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B228" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="D228" s="14" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="E228" s="14" t="s">
         <v>5</v>
@@ -11854,7 +11953,7 @@
       <c r="H228" s="14"/>
       <c r="I228" s="14"/>
       <c r="J228" s="14" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="K228" s="14" t="s">
         <v>47</v>
@@ -11862,16 +11961,16 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="14" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="B229" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C229" s="14" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="D229" s="14" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="E229" s="14" t="s">
         <v>5</v>
@@ -11891,16 +11990,16 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="14" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="B230" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="D230" s="14" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="E230" s="14" t="s">
         <v>5</v>
@@ -11914,7 +12013,7 @@
       <c r="H230" s="14"/>
       <c r="I230" s="14"/>
       <c r="J230" s="14" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="K230" s="14" t="s">
         <v>47</v>
@@ -11922,16 +12021,16 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="14" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B231" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="D231" s="14" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="E231" s="14" t="s">
         <v>5</v>
@@ -11951,16 +12050,16 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="14" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B232" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="D232" s="14" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="E232" s="14" t="s">
         <v>5</v>
@@ -11974,7 +12073,7 @@
       <c r="H232" s="14"/>
       <c r="I232" s="14"/>
       <c r="J232" s="14" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="K232" s="14" t="s">
         <v>47</v>
@@ -11982,16 +12081,16 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="14" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="B233" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C233" s="14" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="D233" s="14" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="E233" s="14" t="s">
         <v>5</v>
@@ -12011,19 +12110,19 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="14" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="D234" s="14" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="E234" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F234" s="14" t="s">
         <v>27</v>
@@ -12034,7 +12133,7 @@
       <c r="H234" s="14"/>
       <c r="I234" s="14"/>
       <c r="J234" s="14" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="K234" s="14" t="s">
         <v>47</v>
@@ -12042,16 +12141,16 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="14" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="B235" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C235" s="14" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="D235" s="14" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="E235" s="14" t="s">
         <v>3</v>
@@ -12065,7 +12164,7 @@
       <c r="H235" s="14"/>
       <c r="I235" s="14"/>
       <c r="J235" s="14" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="K235" s="14" t="s">
         <v>47</v>
@@ -12073,16 +12172,16 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="14" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="B236" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C236" s="14" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="E236" s="14" t="s">
         <v>3</v>
@@ -12096,7 +12195,7 @@
       <c r="H236" s="14"/>
       <c r="I236" s="14"/>
       <c r="J236" s="14" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="K236" s="14" t="s">
         <v>47</v>
@@ -12104,16 +12203,16 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="14" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="B237" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C237" s="14" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="D237" s="14" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="E237" s="14" t="s">
         <v>3</v>
@@ -12127,7 +12226,7 @@
       <c r="H237" s="14"/>
       <c r="I237" s="14"/>
       <c r="J237" s="14" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="K237" s="14" t="s">
         <v>47</v>
@@ -12135,16 +12234,16 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="14" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="B238" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="D238" s="14" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="E238" s="14" t="s">
         <v>3</v>
@@ -12158,7 +12257,7 @@
       <c r="H238" s="14"/>
       <c r="I238" s="14"/>
       <c r="J238" s="14" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="K238" s="14" t="s">
         <v>47</v>
@@ -12166,16 +12265,16 @@
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="14" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="B239" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C239" s="14" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="D239" s="14" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="E239" s="14" t="s">
         <v>6</v>
@@ -12191,7 +12290,7 @@
       </c>
       <c r="I239" s="14"/>
       <c r="J239" s="14" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="K239" s="14" t="s">
         <v>47</v>
@@ -12199,16 +12298,16 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="14" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="D240" s="14" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="E240" s="14" t="s">
         <v>6</v>
@@ -12224,7 +12323,7 @@
       </c>
       <c r="I240" s="14"/>
       <c r="J240" s="14" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="K240" s="14" t="s">
         <v>47</v>
@@ -12232,16 +12331,16 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="14" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="B241" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C241" s="14" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="D241" s="14" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="E241" s="14" t="s">
         <v>6</v>
@@ -12257,7 +12356,7 @@
       </c>
       <c r="I241" s="14"/>
       <c r="J241" s="14" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="K241" s="14" t="s">
         <v>47</v>
@@ -12265,16 +12364,16 @@
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="14" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="B242" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="D242" s="14" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="E242" s="14" t="s">
         <v>3</v>
@@ -12290,7 +12389,7 @@
       </c>
       <c r="I242" s="14"/>
       <c r="J242" s="14" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="K242" s="14" t="s">
         <v>47</v>
@@ -12298,16 +12397,16 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="14" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="B243" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C243" s="14" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="D243" s="14" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="E243" s="14" t="s">
         <v>3</v>
@@ -12323,7 +12422,7 @@
       </c>
       <c r="I243" s="14"/>
       <c r="J243" s="14" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="K243" s="14" t="s">
         <v>47</v>
@@ -12331,16 +12430,16 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="14" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="B244" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="D244" s="14" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="E244" s="14" t="s">
         <v>4</v>
@@ -12356,7 +12455,7 @@
       </c>
       <c r="I244" s="14"/>
       <c r="J244" s="14" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="K244" s="14" t="s">
         <v>47</v>
@@ -12364,16 +12463,16 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="14" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="B245" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C245" s="14" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="D245" s="14" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="E245" s="14" t="s">
         <v>6</v>
@@ -12389,7 +12488,7 @@
       </c>
       <c r="I245" s="14"/>
       <c r="J245" s="14" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="K245" s="14" t="s">
         <v>47</v>
@@ -12397,16 +12496,16 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="14" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="B246" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="D246" s="14" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="E246" s="14" t="s">
         <v>6</v>
@@ -12420,7 +12519,7 @@
       <c r="H246" s="14"/>
       <c r="I246" s="14"/>
       <c r="J246" s="14" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="K246" s="14" t="s">
         <v>47</v>
@@ -12428,16 +12527,16 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="14" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="B247" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C247" s="14" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="D247" s="14" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="E247" s="14" t="s">
         <v>5</v>
@@ -12451,7 +12550,7 @@
       <c r="H247" s="14"/>
       <c r="I247" s="14"/>
       <c r="J247" s="14" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="K247" s="14" t="s">
         <v>47</v>
@@ -12459,16 +12558,16 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="14" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="B248" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="D248" s="14" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="E248" s="14" t="s">
         <v>5</v>
@@ -12488,16 +12587,16 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="14" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="B249" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C249" s="14" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="E249" s="14" t="s">
         <v>5</v>
@@ -12511,7 +12610,7 @@
       <c r="H249" s="14"/>
       <c r="I249" s="14"/>
       <c r="J249" s="14" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="K249" s="14" t="s">
         <v>47</v>
@@ -12519,19 +12618,19 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="14" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="B250" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="D250" s="14" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="E250" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F250" s="14" t="s">
         <v>25</v>
@@ -12542,7 +12641,7 @@
       <c r="H250" s="14"/>
       <c r="I250" s="14"/>
       <c r="J250" s="14" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="K250" s="14" t="s">
         <v>47</v>
@@ -12550,16 +12649,16 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="14" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="B251" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C251" s="14" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="D251" s="14" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="E251" s="14" t="s">
         <v>5</v>
@@ -12579,16 +12678,16 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="14" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="B252" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="D252" s="14" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="E252" s="14" t="s">
         <v>5</v>
@@ -12608,16 +12707,16 @@
     </row>
     <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="14" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="B253" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C253" s="14" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="D253" s="14" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="E253" s="14" t="s">
         <v>5</v>
@@ -12631,7 +12730,7 @@
       <c r="H253" s="14"/>
       <c r="I253" s="14"/>
       <c r="J253" s="14" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="K253" s="14" t="s">
         <v>47</v>
@@ -12639,16 +12738,16 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="14" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="B254" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="D254" s="14" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="E254" s="14" t="s">
         <v>6</v>
@@ -12664,7 +12763,7 @@
       </c>
       <c r="I254" s="14"/>
       <c r="J254" s="14" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="K254" s="14" t="s">
         <v>47</v>
@@ -12672,16 +12771,16 @@
     </row>
     <row r="255" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="B255" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="E255" s="14" t="s">
         <v>3</v>
@@ -12695,7 +12794,7 @@
       <c r="H255" s="14"/>
       <c r="I255" s="14"/>
       <c r="J255" s="14" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="K255" s="14" t="s">
         <v>47</v>
@@ -12764,7 +12863,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>33</v>
@@ -12793,7 +12892,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="C2" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B2,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12825,7 +12924,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="C3" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B3,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12857,7 +12956,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="C4" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B4,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12889,7 +12988,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="C5" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B5,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12921,7 +13020,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="C6" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B6,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12953,7 +13052,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="C7" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B7,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -12985,7 +13084,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="C8" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B8,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13017,7 +13116,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C9" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B9,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13049,7 +13148,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C10" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B10,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13069,11 +13168,11 @@
       </c>
       <c r="G10" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$E$2:$E$255,MATCH($B10,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Partial</v>
+        <v>Done</v>
       </c>
       <c r="H10" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$J$2:$J$255,MATCH($B10,'Parity Tracker'!$A$2:$A$255,0))</f>
-        <v>Tax Savings Tracker done: regime compare, deduction headroom per section, break-even deductions, saves finos_tax_savings (parity-tested savingsPlan). Tax Planner (HRA, surcharge, capital gains: finos-tax-calc.js) still to build.</v>
+        <v>Savings tracker (headroom per section) and the full Tax Planner (both regimes with surcharge, HRA, 80C/80D/NPS/24(b), LTCG/STCG, action list); parity-tested vs js/finos-tax-calc.js. Web surcharge fixed in the same pass (taxable income, new-regime top rate 25%).</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13081,7 +13180,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C11" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B11,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13113,7 +13212,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C12" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B12,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13305,7 +13404,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C18" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B18,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13337,7 +13436,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="C19" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B19,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13369,7 +13468,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="C20" s="14" t="str">
         <f aca="false">INDEX('Parity Tracker'!$C$2:$C$255,MATCH($B20,'Parity Tracker'!$A$2:$A$255,0))</f>
@@ -13398,7 +13497,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
     </row>
   </sheetData>
@@ -13417,7 +13516,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -13428,70 +13527,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13499,16 +13598,16 @@
         <v>47</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13516,16 +13615,16 @@
         <v>47</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13533,16 +13632,16 @@
         <v>47</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13550,16 +13649,16 @@
         <v>47</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13567,16 +13666,16 @@
         <v>47</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13584,16 +13683,16 @@
         <v>47</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13601,16 +13700,16 @@
         <v>47</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13618,33 +13717,169 @@
         <v>47</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
         <v>47</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>1116</v>
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>1150</v>
       </c>
     </row>
   </sheetData>
@@ -13672,7 +13907,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>22</v>
@@ -13683,7 +13918,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13691,7 +13926,7 @@
         <v>20</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1122</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13699,7 +13934,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1123</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13707,31 +13942,31 @@
         <v>38</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>1127</v>
+        <v>1158</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1128</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>1129</v>
+        <v>1160</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1130</v>
+        <v>1161</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -12910,7 +12910,7 @@
       </c>
       <c r="E228" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F228" s="30" t="inlineStr">
@@ -12924,15 +12924,19 @@
         </is>
       </c>
       <c r="H228" s="30" t="n"/>
-      <c r="I228" s="30" t="n"/>
+      <c r="I228" s="30" t="inlineStr">
+        <is>
+          <t>lib/reminders*.ts, Settings → Reminders</t>
+        </is>
+      </c>
       <c r="J228" s="30" t="inlineStr">
         <is>
-          <t>Settings has a toggle with no effect</t>
+          <t>Planner unit-tested (11 cases); permission flow + OS scheduling built but NOT verified on a device (needs R-08/R-09). Local only, no push token.</t>
         </is>
       </c>
       <c r="K228" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13892,7 +13896,7 @@
       </c>
       <c r="E248" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F248" s="30" t="inlineStr">
@@ -13906,11 +13910,19 @@
         </is>
       </c>
       <c r="H248" s="30" t="n"/>
-      <c r="I248" s="30" t="n"/>
-      <c r="J248" s="30" t="n"/>
+      <c r="I248" s="30" t="inlineStr">
+        <is>
+          <t>lib/reminders*.ts, Settings → Reminders</t>
+        </is>
+      </c>
+      <c r="J248" s="30" t="inlineStr">
+        <is>
+          <t>Planner unit-tested (11 cases); permission flow + OS scheduling built but NOT verified on a device (needs R-08/R-09). Local only, no push token.</t>
+        </is>
+      </c>
       <c r="K248" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -15643,28 +15655,53 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>T-02 (website fix)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Budget Forecast core extracted to js/finos-forecast.js; expenses only, honest short history, no overwrite of recorded values</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>tests/forecast.test.js (7), tests/test_budget_forecast_ui.py (5)</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="16" t="n">
         <v>196</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>P-06, R-10</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Local reminders: planner, permission flow, settings, cleared on erase; stale "not available" notices removed</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>tests/reminders.test.mts (11) + permission guard updated; web preview run (unsupported path)</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -9379,7 +9379,7 @@
       </c>
       <c r="E157" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F157" s="30" t="inlineStr">
@@ -9395,13 +9395,13 @@
       <c r="H157" s="30" t="n"/>
       <c r="I157" s="30" t="inlineStr">
         <is>
-          <t>learn/dna</t>
+          <t>app/tools/dna.tsx</t>
         </is>
       </c>
       <c r="J157" s="30" t="n"/>
       <c r="K157" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="E230" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F230" s="30" t="inlineStr">
@@ -13022,15 +13022,19 @@
         </is>
       </c>
       <c r="H230" s="30" t="n"/>
-      <c r="I230" s="30" t="n"/>
+      <c r="I230" s="30" t="inlineStr">
+        <is>
+          <t>app/tools/dna.tsx</t>
+        </is>
+      </c>
       <c r="J230" s="30" t="inlineStr">
         <is>
-          <t>Health score pillars for DNA/learning show neutral defaults</t>
+          <t>DNA quiz done (feeds Health Score Behaviour). First-run onboarding flow not built: Home action items + Money Score invitation cover it</t>
         </is>
       </c>
       <c r="K230" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -15702,6 +15706,31 @@
       </c>
       <c r="E25" s="16" t="n">
         <v>207</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P-08 (quiz), L-26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Financial DNA quiz on the phone; Health Score Behaviour uses it; shared questions module; missing 36-49 age band added</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tests/dna.test.js (5), dna.parity.test.mts (5); preview run: 9 answers, scores saved, health pillar 11/15</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E42" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F42" s="30" t="inlineStr">
@@ -3340,17 +3340,17 @@
       <c r="H42" s="30" t="n"/>
       <c r="I42" s="30" t="inlineStr">
         <is>
-          <t>calculators/bond</t>
+          <t>app/tools/calc/bond</t>
         </is>
       </c>
       <c r="J42" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K42" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
@@ -3446,17 +3446,17 @@
       <c r="H44" s="30" t="n"/>
       <c r="I44" s="30" t="inlineStr">
         <is>
-          <t>calculators/fd</t>
+          <t>app/tools/calc/fd</t>
         </is>
       </c>
       <c r="J44" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K44" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
@@ -3552,17 +3552,17 @@
       <c r="H46" s="30" t="n"/>
       <c r="I46" s="30" t="inlineStr">
         <is>
-          <t>calculators/postoffice</t>
+          <t>app/tools/calc/postofficemis</t>
         </is>
       </c>
       <c r="J46" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K46" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
@@ -3658,17 +3658,17 @@
       <c r="H48" s="30" t="n"/>
       <c r="I48" s="30" t="inlineStr">
         <is>
-          <t>calculators/rd</t>
+          <t>app/tools/calc/rd</t>
         </is>
       </c>
       <c r="J48" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K48" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E49" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F49" s="30" t="inlineStr">
@@ -3711,17 +3711,17 @@
       <c r="H49" s="30" t="n"/>
       <c r="I49" s="30" t="inlineStr">
         <is>
-          <t>calculators/savingsinvestment</t>
+          <t>app/tools/calc/savingsvsinvest</t>
         </is>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K49" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
@@ -3764,17 +3764,17 @@
       <c r="H50" s="30" t="n"/>
       <c r="I50" s="30" t="inlineStr">
         <is>
-          <t>calculators/scss</t>
+          <t>app/tools/calc/scss</t>
         </is>
       </c>
       <c r="J50" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K50" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F51" s="30" t="inlineStr">
@@ -3817,17 +3817,17 @@
       <c r="H51" s="30" t="n"/>
       <c r="I51" s="30" t="inlineStr">
         <is>
-          <t>calculators/ssy</t>
+          <t>app/tools/calc/ssy</t>
         </is>
       </c>
       <c r="J51" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K51" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
@@ -3870,17 +3870,17 @@
       <c r="H52" s="30" t="n"/>
       <c r="I52" s="30" t="inlineStr">
         <is>
-          <t>calculators/compounding-visualizer</t>
+          <t>app/tools/calc/compounding</t>
         </is>
       </c>
       <c r="J52" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K52" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="E53" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F53" s="30" t="inlineStr">
@@ -3923,17 +3923,17 @@
       <c r="H53" s="30" t="n"/>
       <c r="I53" s="30" t="inlineStr">
         <is>
-          <t>calculators/financial-age-calculator</t>
+          <t>app/tools/calc/financialage</t>
         </is>
       </c>
       <c r="J53" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K53" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
@@ -3976,17 +3976,17 @@
       <c r="H54" s="30" t="n"/>
       <c r="I54" s="30" t="inlineStr">
         <is>
-          <t>calculators/inflation-impact</t>
+          <t>app/tools/calc/inflationimpact</t>
         </is>
       </c>
       <c r="J54" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K54" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F55" s="30" t="inlineStr">
@@ -4029,17 +4029,17 @@
       <c r="H55" s="30" t="n"/>
       <c r="I55" s="30" t="inlineStr">
         <is>
-          <t>calculators/money-behavior-analyzer</t>
+          <t>app/tools/calc/moneybehavior</t>
         </is>
       </c>
       <c r="J55" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K55" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
@@ -4082,17 +4082,17 @@
       <c r="H56" s="30" t="n"/>
       <c r="I56" s="30" t="inlineStr">
         <is>
-          <t>calculators/opportunity-cost</t>
+          <t>app/tools/calc/opportunitycost</t>
         </is>
       </c>
       <c r="J56" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K56" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="E57" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F57" s="30" t="inlineStr">
@@ -4135,17 +4135,17 @@
       <c r="H57" s="30" t="n"/>
       <c r="I57" s="30" t="inlineStr">
         <is>
-          <t>calculators/purchasing-power-loss</t>
+          <t>app/tools/calc/purchasingpower</t>
         </is>
       </c>
       <c r="J57" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K57" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
@@ -4188,17 +4188,17 @@
       <c r="H58" s="30" t="n"/>
       <c r="I58" s="30" t="inlineStr">
         <is>
-          <t>calculators/real-rate-of-return</t>
+          <t>app/tools/calc/realreturn</t>
         </is>
       </c>
       <c r="J58" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K58" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="E59" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F59" s="30" t="inlineStr">
@@ -4241,17 +4241,17 @@
       <c r="H59" s="30" t="n"/>
       <c r="I59" s="30" t="inlineStr">
         <is>
-          <t>calculators/risk-vs-reward</t>
+          <t>app/tools/calc/riskreward</t>
         </is>
       </c>
       <c r="J59" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K59" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
@@ -4294,17 +4294,17 @@
       <c r="H60" s="30" t="n"/>
       <c r="I60" s="30" t="inlineStr">
         <is>
-          <t>calculators/time-value-of-money</t>
+          <t>app/tools/calc/timevalue</t>
         </is>
       </c>
       <c r="J60" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K60" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E61" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F61" s="30" t="inlineStr">
@@ -4347,17 +4347,17 @@
       <c r="H61" s="30" t="n"/>
       <c r="I61" s="30" t="inlineStr">
         <is>
-          <t>calculators/wealth-vs-income-gap</t>
+          <t>app/tools/calc/wealthgap</t>
         </is>
       </c>
       <c r="J61" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K61" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="E63" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F63" s="30" t="inlineStr">
@@ -4453,17 +4453,17 @@
       <c r="H63" s="30" t="n"/>
       <c r="I63" s="30" t="inlineStr">
         <is>
-          <t>calculators/childedu</t>
+          <t>app/tools/calc/childedu</t>
         </is>
       </c>
       <c r="J63" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K63" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
@@ -4506,17 +4506,17 @@
       <c r="H64" s="30" t="n"/>
       <c r="I64" s="30" t="inlineStr">
         <is>
-          <t>calculators/creditaddiction</t>
+          <t>app/tools/calc/creditaddiction</t>
         </is>
       </c>
       <c r="J64" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K64" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="E65" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F65" s="30" t="inlineStr">
@@ -4559,17 +4559,17 @@
       <c r="H65" s="30" t="n"/>
       <c r="I65" s="30" t="inlineStr">
         <is>
-          <t>calculators/emidiease</t>
+          <t>app/tools/calc/emidisease</t>
         </is>
       </c>
       <c r="J65" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K65" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
@@ -4612,17 +4612,17 @@
       <c r="H66" s="30" t="n"/>
       <c r="I66" s="30" t="inlineStr">
         <is>
-          <t>calculators/govvspvt</t>
+          <t>app/tools/calc/govtvsprivate</t>
         </is>
       </c>
       <c r="J66" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K66" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="E67" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F67" s="30" t="inlineStr">
@@ -4665,17 +4665,17 @@
       <c r="H67" s="30" t="n"/>
       <c r="I67" s="30" t="inlineStr">
         <is>
-          <t>calculators/lifestyle</t>
+          <t>app/tools/calc/lifestylecreep</t>
         </is>
       </c>
       <c r="J67" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K67" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
@@ -4718,17 +4718,17 @@
       <c r="H68" s="30" t="n"/>
       <c r="I68" s="30" t="inlineStr">
         <is>
-          <t>calculators/logkyakahenge</t>
+          <t>app/tools/calc/logkyakahenge</t>
         </is>
       </c>
       <c r="J68" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K68" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="E69" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F69" s="30" t="inlineStr">
@@ -4771,17 +4771,17 @@
       <c r="H69" s="30" t="n"/>
       <c r="I69" s="30" t="inlineStr">
         <is>
-          <t>calculators/middleclass</t>
+          <t>app/tools/calc/middleclass</t>
         </is>
       </c>
       <c r="J69" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K69" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
@@ -4824,17 +4824,17 @@
       <c r="H70" s="30" t="n"/>
       <c r="I70" s="30" t="inlineStr">
         <is>
-          <t>calculators/parental</t>
+          <t>app/tools/calc/parental</t>
         </is>
       </c>
       <c r="J70" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K70" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E71" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F71" s="30" t="inlineStr">
@@ -4877,17 +4877,17 @@
       <c r="H71" s="30" t="n"/>
       <c r="I71" s="30" t="inlineStr">
         <is>
-          <t>calculators/shaadicost</t>
+          <t>app/tools/calc/shaadicost</t>
         </is>
       </c>
       <c r="J71" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K71" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="E73" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F73" s="30" t="inlineStr">
@@ -4983,17 +4983,17 @@
       <c r="H73" s="30" t="n"/>
       <c r="I73" s="30" t="inlineStr">
         <is>
-          <t>calculators/expenseratio</t>
+          <t>app/tools/calc/expenseratio</t>
         </is>
       </c>
       <c r="J73" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K73" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
@@ -5036,17 +5036,17 @@
       <c r="H74" s="30" t="n"/>
       <c r="I74" s="30" t="inlineStr">
         <is>
-          <t>calculators/insurancecoverage</t>
+          <t>app/tools/calc/insurancecoverage</t>
         </is>
       </c>
       <c r="J74" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K74" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="E77" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F77" s="30" t="inlineStr">
@@ -5195,17 +5195,17 @@
       <c r="H77" s="30" t="n"/>
       <c r="I77" s="30" t="inlineStr">
         <is>
-          <t>calculators/savings</t>
+          <t>app/tools/calc/savingsrate</t>
         </is>
       </c>
       <c r="J77" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K77" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="E78" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F78" s="30" t="inlineStr">
@@ -5248,17 +5248,17 @@
       <c r="H78" s="30" t="n"/>
       <c r="I78" s="30" t="inlineStr">
         <is>
-          <t>calculators/assetalloc</t>
+          <t>app/tools/calc/assetalloc</t>
         </is>
       </c>
       <c r="J78" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K78" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="E79" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F79" s="30" t="inlineStr">
@@ -5301,17 +5301,17 @@
       <c r="H79" s="30" t="n"/>
       <c r="I79" s="30" t="inlineStr">
         <is>
-          <t>calculators/cagr</t>
+          <t>app/tools/calc/cagr</t>
         </is>
       </c>
       <c r="J79" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K79" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
@@ -5354,17 +5354,17 @@
       <c r="H80" s="30" t="n"/>
       <c r="I80" s="30" t="inlineStr">
         <is>
-          <t>calculators/dividend</t>
+          <t>app/tools/calc/dividend</t>
         </is>
       </c>
       <c r="J80" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K80" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="E81" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
@@ -5407,17 +5407,17 @@
       <c r="H81" s="30" t="n"/>
       <c r="I81" s="30" t="inlineStr">
         <is>
-          <t>calculators/etf</t>
+          <t>app/tools/calc/etf</t>
         </is>
       </c>
       <c r="J81" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K81" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="E83" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F83" s="30" t="inlineStr">
@@ -5513,17 +5513,17 @@
       <c r="H83" s="30" t="n"/>
       <c r="I83" s="30" t="inlineStr">
         <is>
-          <t>calculators/lupsum</t>
+          <t>app/tools/calc/lumpsum</t>
         </is>
       </c>
       <c r="J83" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K83" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
@@ -5566,17 +5566,17 @@
       <c r="H84" s="30" t="n"/>
       <c r="I84" s="30" t="inlineStr">
         <is>
-          <t>calculators/mutualfunds</t>
+          <t>app/tools/calc/mutualfunds</t>
         </is>
       </c>
       <c r="J84" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K84" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="E85" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F85" s="30" t="inlineStr">
@@ -5619,17 +5619,17 @@
       <c r="H85" s="30" t="n"/>
       <c r="I85" s="30" t="inlineStr">
         <is>
-          <t>calculators/portfolio</t>
+          <t>app/tools/calc/growth</t>
         </is>
       </c>
       <c r="J85" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K85" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E87" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F87" s="30" t="inlineStr">
@@ -5725,17 +5725,17 @@
       <c r="H87" s="30" t="n"/>
       <c r="I87" s="30" t="inlineStr">
         <is>
-          <t>calculators/rollingreturns</t>
+          <t>app/tools/calc/rollingreturns</t>
         </is>
       </c>
       <c r="J87" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K87" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="E89" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F89" s="30" t="inlineStr">
@@ -5831,17 +5831,17 @@
       <c r="H89" s="30" t="n"/>
       <c r="I89" s="30" t="inlineStr">
         <is>
-          <t>calculators/sip</t>
+          <t>app/tools/calc/sip</t>
         </is>
       </c>
       <c r="J89" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K89" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="E91" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F91" s="30" t="inlineStr">
@@ -5937,17 +5937,17 @@
       <c r="H91" s="30" t="n"/>
       <c r="I91" s="30" t="inlineStr">
         <is>
-          <t>calculators/swp</t>
+          <t>app/tools/calc/swp</t>
         </is>
       </c>
       <c r="J91" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K91" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="E92" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F92" s="30" t="inlineStr">
@@ -5990,17 +5990,17 @@
       <c r="H92" s="30" t="n"/>
       <c r="I92" s="30" t="inlineStr">
         <is>
-          <t>calculators/taxadj</t>
+          <t>app/tools/calc/taxadj</t>
         </is>
       </c>
       <c r="J92" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K92" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="E93" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F93" s="30" t="inlineStr">
@@ -6043,17 +6043,17 @@
       <c r="H93" s="30" t="n"/>
       <c r="I93" s="30" t="inlineStr">
         <is>
-          <t>calculators/xirr</t>
+          <t>app/tools/calc/xirr</t>
         </is>
       </c>
       <c r="J93" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K93" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
@@ -6096,17 +6096,17 @@
       <c r="H94" s="30" t="n"/>
       <c r="I94" s="30" t="inlineStr">
         <is>
-          <t>calculators/car</t>
+          <t>app/tools/calc/carloan</t>
         </is>
       </c>
       <c r="J94" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K94" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="E95" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F95" s="30" t="inlineStr">
@@ -6149,17 +6149,17 @@
       <c r="H95" s="30" t="n"/>
       <c r="I95" s="30" t="inlineStr">
         <is>
-          <t>calculators/creditcard</t>
+          <t>app/tools/calc/creditcard</t>
         </is>
       </c>
       <c r="J95" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K95" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="E97" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F97" s="30" t="inlineStr">
@@ -6255,17 +6255,17 @@
       <c r="H97" s="30" t="n"/>
       <c r="I97" s="30" t="inlineStr">
         <is>
-          <t>calculators/education</t>
+          <t>app/tools/calc/educationloan</t>
         </is>
       </c>
       <c r="J97" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K97" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E98" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F98" s="30" t="inlineStr">
@@ -6308,17 +6308,17 @@
       <c r="H98" s="30" t="n"/>
       <c r="I98" s="30" t="inlineStr">
         <is>
-          <t>calculators/emi</t>
+          <t>app/tools/calc/emi</t>
         </is>
       </c>
       <c r="J98" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K98" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="E99" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F99" s="30" t="inlineStr">
@@ -6361,17 +6361,17 @@
       <c r="H99" s="30" t="n"/>
       <c r="I99" s="30" t="inlineStr">
         <is>
-          <t>calculators/emiprepay</t>
+          <t>app/tools/calc/emiprepay</t>
         </is>
       </c>
       <c r="J99" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K99" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="E101" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F101" s="30" t="inlineStr">
@@ -6467,17 +6467,17 @@
       <c r="H101" s="30" t="n"/>
       <c r="I101" s="30" t="inlineStr">
         <is>
-          <t>calculators/interest</t>
+          <t>app/tools/calc/interestoutflow</t>
         </is>
       </c>
       <c r="J101" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K101" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
@@ -6520,17 +6520,17 @@
       <c r="H102" s="30" t="n"/>
       <c r="I102" s="30" t="inlineStr">
         <is>
-          <t>calculators/loaneligibility</t>
+          <t>app/tools/calc/loaneligibility</t>
         </is>
       </c>
       <c r="J102" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K102" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="E103" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F103" s="30" t="inlineStr">
@@ -6573,17 +6573,17 @@
       <c r="H103" s="30" t="n"/>
       <c r="I103" s="30" t="inlineStr">
         <is>
-          <t>calculators/loantenure</t>
+          <t>app/tools/calc/loantenure</t>
         </is>
       </c>
       <c r="J103" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K103" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="E104" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F104" s="30" t="inlineStr">
@@ -6626,17 +6626,17 @@
       <c r="H104" s="30" t="n"/>
       <c r="I104" s="30" t="inlineStr">
         <is>
-          <t>calculators/personal</t>
+          <t>app/tools/calc/personalloan</t>
         </is>
       </c>
       <c r="J104" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K104" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
@@ -6732,17 +6732,17 @@
       <c r="H106" s="30" t="n"/>
       <c r="I106" s="30" t="inlineStr">
         <is>
-          <t>calculators/annuity</t>
+          <t>app/tools/calc/annuity</t>
         </is>
       </c>
       <c r="J106" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K106" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="E107" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F107" s="30" t="inlineStr">
@@ -6785,17 +6785,17 @@
       <c r="H107" s="30" t="n"/>
       <c r="I107" s="30" t="inlineStr">
         <is>
-          <t>calculators/healthcare</t>
+          <t>app/tools/calc/healthinflation</t>
         </is>
       </c>
       <c r="J107" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K107" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
@@ -6838,17 +6838,17 @@
       <c r="H108" s="30" t="n"/>
       <c r="I108" s="30" t="inlineStr">
         <is>
-          <t>calculators/lifeexpentancy</t>
+          <t>app/tools/calc/lifeexpectancy</t>
         </is>
       </c>
       <c r="J108" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K108" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="E109" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F109" s="30" t="inlineStr">
@@ -6891,17 +6891,17 @@
       <c r="H109" s="30" t="n"/>
       <c r="I109" s="30" t="inlineStr">
         <is>
-          <t>calculators/longevity</t>
+          <t>app/tools/calc/longevity</t>
         </is>
       </c>
       <c r="J109" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K109" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
@@ -6944,17 +6944,17 @@
       <c r="H110" s="30" t="n"/>
       <c r="I110" s="30" t="inlineStr">
         <is>
-          <t>calculators/pensiongap</t>
+          <t>app/tools/calc/pensiongap</t>
         </is>
       </c>
       <c r="J110" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K110" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="E111" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F111" s="30" t="inlineStr">
@@ -6997,17 +6997,17 @@
       <c r="H111" s="30" t="n"/>
       <c r="I111" s="30" t="inlineStr">
         <is>
-          <t>calculators/postretirement</t>
+          <t>app/tools/calc/postretirement</t>
         </is>
       </c>
       <c r="J111" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K111" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E113" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F113" s="30" t="inlineStr">
@@ -7103,17 +7103,17 @@
       <c r="H113" s="30" t="n"/>
       <c r="I113" s="30" t="inlineStr">
         <is>
-          <t>calculators/80c</t>
+          <t>app/tools/calc/sec80c</t>
         </is>
       </c>
       <c r="J113" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K113" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
@@ -7156,17 +7156,17 @@
       <c r="H114" s="30" t="n"/>
       <c r="I114" s="30" t="inlineStr">
         <is>
-          <t>calculators/captalgains</t>
+          <t>app/tools/calc/capgains</t>
         </is>
       </c>
       <c r="J114" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K114" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E115" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F115" s="30" t="inlineStr">
@@ -7209,17 +7209,17 @@
       <c r="H115" s="30" t="n"/>
       <c r="I115" s="30" t="inlineStr">
         <is>
-          <t>calculators/gratuity</t>
+          <t>app/tools/calc/gratuity</t>
         </is>
       </c>
       <c r="J115" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K115" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F116" s="30" t="inlineStr">
@@ -7262,17 +7262,17 @@
       <c r="H116" s="30" t="n"/>
       <c r="I116" s="30" t="inlineStr">
         <is>
-          <t>calculators/hra</t>
+          <t>app/tools/calc/hra</t>
         </is>
       </c>
       <c r="J116" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K116" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="E119" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F119" s="30" t="inlineStr">
@@ -7421,17 +7421,17 @@
       <c r="H119" s="30" t="n"/>
       <c r="I119" s="30" t="inlineStr">
         <is>
-          <t>calculators/leave</t>
+          <t>app/tools/calc/leaveencash</t>
         </is>
       </c>
       <c r="J119" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K119" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
@@ -7580,17 +7580,17 @@
       <c r="H122" s="30" t="n"/>
       <c r="I122" s="30" t="inlineStr">
         <is>
-          <t>calculators/professional</t>
+          <t>app/tools/calc/professionaltax</t>
         </is>
       </c>
       <c r="J122" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K122" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="E123" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F123" s="30" t="inlineStr">
@@ -7633,17 +7633,17 @@
       <c r="H123" s="30" t="n"/>
       <c r="I123" s="30" t="inlineStr">
         <is>
-          <t>calculators/shortlong</t>
+          <t>app/tools/calc/stcgltcg</t>
         </is>
       </c>
       <c r="J123" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K123" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
@@ -7686,17 +7686,17 @@
       <c r="H124" s="30" t="n"/>
       <c r="I124" s="30" t="inlineStr">
         <is>
-          <t>calculators/breakeven</t>
+          <t>app/tools/calc/breakeven</t>
         </is>
       </c>
       <c r="J124" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K124" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="E125" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F125" s="30" t="inlineStr">
@@ -7739,17 +7739,17 @@
       <c r="H125" s="30" t="n"/>
       <c r="I125" s="30" t="inlineStr">
         <is>
-          <t>calculators/brokerage</t>
+          <t>app/tools/calc/brokerage</t>
         </is>
       </c>
       <c r="J125" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K125" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F126" s="30" t="inlineStr">
@@ -7792,17 +7792,17 @@
       <c r="H126" s="30" t="n"/>
       <c r="I126" s="30" t="inlineStr">
         <is>
-          <t>calculators/futurespl</t>
+          <t>app/tools/calc/futurespl</t>
         </is>
       </c>
       <c r="J126" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K126" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="E127" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F127" s="30" t="inlineStr">
@@ -7845,17 +7845,17 @@
       <c r="H127" s="30" t="n"/>
       <c r="I127" s="30" t="inlineStr">
         <is>
-          <t>calculators/margin</t>
+          <t>app/tools/calc/margin</t>
         </is>
       </c>
       <c r="J127" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K127" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
@@ -7898,17 +7898,17 @@
       <c r="H128" s="30" t="n"/>
       <c r="I128" s="30" t="inlineStr">
         <is>
-          <t>calculators/options</t>
+          <t>app/tools/calc/optionspayoff</t>
         </is>
       </c>
       <c r="J128" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K128" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="E129" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F129" s="30" t="inlineStr">
@@ -7951,17 +7951,17 @@
       <c r="H129" s="30" t="n"/>
       <c r="I129" s="30" t="inlineStr">
         <is>
-          <t>calculators/positionsize</t>
+          <t>app/tools/calc/positionsize</t>
         </is>
       </c>
       <c r="J129" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K129" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="E130" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F130" s="30" t="inlineStr">
@@ -8004,17 +8004,17 @@
       <c r="H130" s="30" t="n"/>
       <c r="I130" s="30" t="inlineStr">
         <is>
-          <t>calculators/riskper</t>
+          <t>app/tools/calc/riskpertrade</t>
         </is>
       </c>
       <c r="J130" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K130" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="E131" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F131" s="30" t="inlineStr">
@@ -8057,17 +8057,17 @@
       <c r="H131" s="30" t="n"/>
       <c r="I131" s="30" t="inlineStr">
         <is>
-          <t>calculators/volatility</t>
+          <t>app/tools/calc/vega</t>
         </is>
       </c>
       <c r="J131" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Same formula and the same text as the page, checked by running the page script (webCalc.parity)</t>
         </is>
       </c>
       <c r="K131" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -15709,28 +15709,53 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>P-08 (quiz), L-26</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Financial DNA quiz on the phone; Health Score Behaviour uses it; shared questions module; missing 36-49 age band added</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>tests/dna.test.js (5), dna.parity.test.mts (5); preview run: 9 answers, scores saved, health pillar 11/15</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="16" t="n">
         <v>212</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C-01…C-90 (71 of 88)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Calculators hub + 71 calculators across 9 groups; parity harness runs each website page script; 3 website bugs found and fixed (SSY double count, Options zero-strike hang, Bond coupon float)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>webCalc.parity.test.mts: 63 pages x ~70 vectors each; preview run</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
@@ -2502,13 +2502,17 @@
       <c r="H26" s="30" t="n"/>
       <c r="I26" s="30" t="inlineStr">
         <is>
-          <t>tools/real-estate</t>
-        </is>
-      </c>
-      <c r="J26" s="30" t="n"/>
+          <t>app/tools/realestate.tsx</t>
+        </is>
+      </c>
+      <c r="J26" s="30" t="inlineStr">
+        <is>
+          <t>Buy vs rent (corrected like-for-like model), true cost, rental yield; shared js/finos-real-estate.js; parity-tested</t>
+        </is>
+      </c>
       <c r="K26" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3381,7 @@
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F43" s="30" t="inlineStr">
@@ -3393,17 +3397,17 @@
       <c r="H43" s="30" t="n"/>
       <c r="I43" s="30" t="inlineStr">
         <is>
-          <t>calculators/epf</t>
+          <t>app/tracker/epf.tsx</t>
         </is>
       </c>
       <c r="J43" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the EPF tracker; the phone has it</t>
         </is>
       </c>
       <c r="K43" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3487,7 @@
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F45" s="30" t="inlineStr">
@@ -3499,17 +3503,17 @@
       <c r="H45" s="30" t="n"/>
       <c r="I45" s="30" t="inlineStr">
         <is>
-          <t>calculators/nps</t>
+          <t>app/tracker/nps.tsx</t>
         </is>
       </c>
       <c r="J45" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the NPS tracker; the phone has it</t>
         </is>
       </c>
       <c r="K45" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3593,7 @@
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F47" s="30" t="inlineStr">
@@ -3605,17 +3609,17 @@
       <c r="H47" s="30" t="n"/>
       <c r="I47" s="30" t="inlineStr">
         <is>
-          <t>calculators/ppf</t>
+          <t>app/tracker/ppf.tsx</t>
         </is>
       </c>
       <c r="J47" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the PPF tracker; the phone has it</t>
         </is>
       </c>
       <c r="K47" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4388,7 @@
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
@@ -4400,17 +4404,17 @@
       <c r="H62" s="30" t="n"/>
       <c r="I62" s="30" t="inlineStr">
         <is>
-          <t>calculators/buyhouse</t>
+          <t>app/tools/realestate.tsx</t>
         </is>
       </c>
       <c r="J62" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Buy vs rent (corrected like-for-like model), true cost, rental yield; shared js/finos-real-estate.js; parity-tested</t>
         </is>
       </c>
       <c r="K62" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4918,7 @@
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
@@ -4930,17 +4934,17 @@
       <c r="H72" s="30" t="n"/>
       <c r="I72" s="30" t="inlineStr">
         <is>
-          <t>calculators/emergencyfund</t>
+          <t>app/tracker/emergency.tsx</t>
         </is>
       </c>
       <c r="J72" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the Emergency Fund tracker; the phone has it</t>
         </is>
       </c>
       <c r="K72" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5077,7 @@
       </c>
       <c r="E75" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F75" s="30" t="inlineStr">
@@ -5089,17 +5093,17 @@
       <c r="H75" s="30" t="n"/>
       <c r="I75" s="30" t="inlineStr">
         <is>
-          <t>calculators/lifestyle</t>
+          <t>app/tools/calc/lifestylecreep</t>
         </is>
       </c>
       <c r="J75" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the Lifestyle Inflation Detector (desi) which is ported</t>
         </is>
       </c>
       <c r="K75" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5130,7 @@
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
@@ -5142,17 +5146,17 @@
       <c r="H76" s="30" t="n"/>
       <c r="I76" s="30" t="inlineStr">
         <is>
-          <t>calculators/networth</t>
+          <t>app/tracker/networth.tsx</t>
         </is>
       </c>
       <c r="J76" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to Net Worth; the phone has it</t>
         </is>
       </c>
       <c r="K76" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5448,7 @@
       </c>
       <c r="E82" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
@@ -5460,17 +5464,17 @@
       <c r="H82" s="30" t="n"/>
       <c r="I82" s="30" t="inlineStr">
         <is>
-          <t>calculators/goalbased</t>
+          <t>app/tools/goalopt.tsx</t>
         </is>
       </c>
       <c r="J82" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the Goal Optimizer; the phone has it</t>
         </is>
       </c>
       <c r="K82" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5660,7 @@
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
@@ -5672,17 +5676,17 @@
       <c r="H86" s="30" t="n"/>
       <c r="I86" s="30" t="inlineStr">
         <is>
-          <t>calculators/rebalancing</t>
+          <t>app/tools/rebalance.tsx</t>
         </is>
       </c>
       <c r="J86" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the Portfolio Rebalancer; the phone has it</t>
         </is>
       </c>
       <c r="K86" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5766,7 @@
       </c>
       <c r="E88" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F88" s="30" t="inlineStr">
@@ -5783,12 +5787,12 @@
       </c>
       <c r="J88" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Random (Math.random) Monte Carlo with a fixed fund list: not reproducible and prescriptive. The Goal Optimizer and Retirement Planner (seeded) cover it</t>
         </is>
       </c>
       <c r="K88" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5872,7 @@
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
@@ -5884,17 +5888,17 @@
       <c r="H90" s="30" t="n"/>
       <c r="I90" s="30" t="inlineStr">
         <is>
-          <t>calculators/stepup</t>
+          <t>app/tools/stepup.tsx</t>
         </is>
       </c>
       <c r="J90" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the SIP Step-up planner; the phone has it</t>
         </is>
       </c>
       <c r="K90" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6190,7 @@
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
@@ -6202,17 +6206,17 @@
       <c r="H96" s="30" t="n"/>
       <c r="I96" s="30" t="inlineStr">
         <is>
-          <t>calculators/debtsnow</t>
+          <t>app/tools/debt.tsx</t>
         </is>
       </c>
       <c r="J96" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the Debt Optimizer; the phone has it</t>
         </is>
       </c>
       <c r="K96" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6402,7 @@
       </c>
       <c r="E100" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F100" s="30" t="inlineStr">
@@ -6414,17 +6418,17 @@
       <c r="H100" s="30" t="n"/>
       <c r="I100" s="30" t="inlineStr">
         <is>
-          <t>calculators/home</t>
+          <t>app/tools/homeloan.tsx</t>
         </is>
       </c>
       <c r="J100" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the Home Loan planner; the phone has it</t>
         </is>
       </c>
       <c r="K100" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7038,7 @@
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
@@ -7050,17 +7054,17 @@
       <c r="H112" s="30" t="n"/>
       <c r="I112" s="30" t="inlineStr">
         <is>
-          <t>calculators/retirement</t>
+          <t>app/tools/retirement.tsx</t>
         </is>
       </c>
       <c r="J112" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the Retirement Planner; the phone has it</t>
         </is>
       </c>
       <c r="K112" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7303,7 @@
       </c>
       <c r="E117" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F117" s="30" t="inlineStr">
@@ -7315,17 +7319,17 @@
       <c r="H117" s="30" t="n"/>
       <c r="I117" s="30" t="inlineStr">
         <is>
-          <t>calculators/income</t>
+          <t>app/tools/taxplanner.tsx</t>
         </is>
       </c>
       <c r="J117" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Uses the shared tax core; the phone Tax Planner compares both regimes on the same port</t>
         </is>
       </c>
       <c r="K117" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7356,7 @@
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
@@ -7368,17 +7372,17 @@
       <c r="H118" s="30" t="n"/>
       <c r="I118" s="30" t="inlineStr">
         <is>
-          <t>calculators/inhand</t>
+          <t>app/tools/salary.tsx</t>
         </is>
       </c>
       <c r="J118" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Website page redirects to the Salary Optimizer; the phone has it</t>
         </is>
       </c>
       <c r="K118" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7515,7 @@
       </c>
       <c r="E121" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F121" s="30" t="inlineStr">
@@ -7527,17 +7531,17 @@
       <c r="H121" s="30" t="n"/>
       <c r="I121" s="30" t="inlineStr">
         <is>
-          <t>calculators/oldnew</t>
+          <t>app/tools/taxplanner.tsx</t>
         </is>
       </c>
       <c r="J121" s="30" t="inlineStr">
         <is>
-          <t>Pure formula; port + parity test</t>
+          <t>Old vs new regime: the phone Tax Planner (parity-tested on the shared tax core)</t>
         </is>
       </c>
       <c r="K121" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -15734,28 +15738,53 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>C-01…C-90 (71 of 88)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Calculators hub + 71 calculators across 9 groups; parity harness runs each website page script; 3 website bugs found and fixed (SSY double count, Options zero-strike hang, Bond coupon float)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>webCalc.parity.test.mts: 63 pages x ~70 vectors each; preview run</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="16" t="n">
         <v>287</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>T-25, C-21</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Real estate: buy vs rent, true cost, rental yield on the phone; website page rewired to a shared tested module with a corrected model</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>tests/real-estate.test.js (11), test_real_estate_ui.py (4), realEstate.parity (3); preview run</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -12820,7 +12820,7 @@
       </c>
       <c r="E226" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F226" s="30" t="inlineStr">
@@ -12834,11 +12834,19 @@
         </is>
       </c>
       <c r="H226" s="30" t="n"/>
-      <c r="I226" s="30" t="n"/>
-      <c r="J226" s="30" t="n"/>
+      <c r="I226" s="30" t="inlineStr">
+        <is>
+          <t>app/search.tsx</t>
+        </is>
+      </c>
+      <c r="J226" s="30" t="inlineStr">
+        <is>
+          <t>Index guard test: every route exists, every tool/tracker is listed</t>
+        </is>
+      </c>
       <c r="K226" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12967,7 +12975,7 @@
       </c>
       <c r="E229" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F229" s="30" t="inlineStr">
@@ -12981,11 +12989,19 @@
         </is>
       </c>
       <c r="H229" s="30" t="n"/>
-      <c r="I229" s="30" t="n"/>
-      <c r="J229" s="30" t="n"/>
+      <c r="I229" s="30" t="inlineStr">
+        <is>
+          <t>components/Nudges.tsx</t>
+        </is>
+      </c>
+      <c r="J229" s="30" t="inlineStr">
+        <is>
+          <t>Nudges done (only from recorded facts, dismissible). Persona greetings and the status strip not built</t>
+        </is>
+      </c>
       <c r="K229" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -15763,28 +15779,53 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>T-25, C-21</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Real estate: buy vs rent, true cost, rental yield on the phone; website page rewired to a shared tested module with a corrected model</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>tests/real-estate.test.js (11), test_real_estate_ui.py (4), realEstate.parity (3); preview run</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="16" t="n">
         <v>290</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P-04, P-07 (nudges)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Phone-wide search with route-existence guard; Home nudges from recorded facts, dismissible</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>search.test.mts (8), nudges.test.mts (6); preview run</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
@@ -3140,13 +3140,17 @@
       <c r="H38" s="30" t="n"/>
       <c r="I38" s="30" t="inlineStr">
         <is>
-          <t>tools/report</t>
-        </is>
-      </c>
-      <c r="J38" s="30" t="n"/>
+          <t>app/tools/report.tsx</t>
+        </is>
+      </c>
+      <c r="J38" s="30" t="inlineStr">
+        <is>
+          <t>Plain-text report via the share sheet; amounts can be left out. PDF needs a native module and a device to verify</t>
+        </is>
+      </c>
       <c r="K38" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12673,7 @@
       </c>
       <c r="E223" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F223" s="30" t="inlineStr">
@@ -12683,15 +12687,19 @@
         </is>
       </c>
       <c r="H223" s="30" t="n"/>
-      <c r="I223" s="30" t="n"/>
+      <c r="I223" s="30" t="inlineStr">
+        <is>
+          <t>lib/theme.ts, Settings → Appearance</t>
+        </is>
+      </c>
       <c r="J223" s="30" t="inlineStr">
         <is>
-          <t>Phone is dark-only</t>
+          <t>Auto / Dark / Light done and contrast-audited. Bloomberg and Saffron are not app-wide themes on the website (stock platform / Arya panel only)</t>
         </is>
       </c>
       <c r="K223" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13081,7 +13089,7 @@
       </c>
       <c r="E231" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F231" s="30" t="inlineStr">
@@ -13095,11 +13103,19 @@
         </is>
       </c>
       <c r="H231" s="30" t="n"/>
-      <c r="I231" s="30" t="n"/>
-      <c r="J231" s="30" t="n"/>
+      <c r="I231" s="30" t="inlineStr">
+        <is>
+          <t>app/profile.tsx</t>
+        </is>
+      </c>
+      <c r="J231" s="30" t="inlineStr">
+        <is>
+          <t>Name, age, income, dependents on the website keys; no PII beyond that by design</t>
+        </is>
+      </c>
       <c r="K231" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -15804,28 +15820,53 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>P-04, P-07 (nudges)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Phone-wide search with route-existence guard; Home nudges from recorded facts, dismissible</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>search.test.mts (8), nudges.test.mts (6); preview run</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="16" t="n">
         <v>304</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P-01, T-37, P-09</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Light theme (runtime colour mapper, contrast-audited), Financial report (text share), Profile; Hindi strings</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>theme.test.mts (9), report.test.mts (6), profile.test.mts (4); 27-screen contrast audit = 0; preview run</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -11859,7 +11859,7 @@
       </c>
       <c r="E207" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F207" s="30" t="inlineStr">
@@ -11875,13 +11875,17 @@
       <c r="H207" s="30" t="n"/>
       <c r="I207" s="30" t="inlineStr">
         <is>
-          <t>portfolio/analytics</t>
-        </is>
-      </c>
-      <c r="J207" s="30" t="n"/>
+          <t>components/XirrCard.tsx</t>
+        </is>
+      </c>
+      <c r="J207" s="30" t="inlineStr">
+        <is>
+          <t>XIRR from entered purchase dates done. Sector heatmap / treemap need a sector mapping source and are not built</t>
+        </is>
+      </c>
       <c r="K207" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12010,7 @@
       </c>
       <c r="E210" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F210" s="30" t="inlineStr">
@@ -12022,13 +12026,17 @@
       <c r="H210" s="30" t="n"/>
       <c r="I210" s="30" t="inlineStr">
         <is>
-          <t>portfolio/watchlist</t>
-        </is>
-      </c>
-      <c r="J210" s="30" t="n"/>
+          <t>app/tracker/watchlist.tsx</t>
+        </is>
+      </c>
+      <c r="J210" s="30" t="inlineStr">
+        <is>
+          <t>Watchlist done (price at add, honest offline). Screener needs a backend and is not built</t>
+        </is>
+      </c>
       <c r="K210" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14038,7 +14046,7 @@
       </c>
       <c r="E250" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F250" s="30" t="inlineStr">
@@ -14052,15 +14060,19 @@
         </is>
       </c>
       <c r="H250" s="30" t="n"/>
-      <c r="I250" s="30" t="n"/>
+      <c r="I250" s="30" t="inlineStr">
+        <is>
+          <t>scripts/theme-audit.py, __tests__/a11y.test.mts</t>
+        </is>
+      </c>
       <c r="J250" s="30" t="inlineStr">
         <is>
-          <t>Static pass done and guarded by __tests__/a11y.test.mts: every touchable/input has a role or label, icon-only buttons are labelled, text colours reach 4.5:1 (textDim raised from 2.6:1, purple text uses purpleInk), system font scaling is left on. Not yet tried with VoiceOver / TalkBack on a device.</t>
+          <t>Roles/labels guard, WCAG AA contrast in dark and light (audited), text scales to 200%. Not yet tried with TalkBack / VoiceOver on a device</t>
         </is>
       </c>
       <c r="K250" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14144,7 @@
       </c>
       <c r="E252" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F252" s="30" t="inlineStr">
@@ -14146,11 +14158,19 @@
         </is>
       </c>
       <c r="H252" s="30" t="n"/>
-      <c r="I252" s="30" t="n"/>
-      <c r="J252" s="30" t="n"/>
+      <c r="I252" s="30" t="inlineStr">
+        <is>
+          <t>lib/aryaOffline.ts, markets banner</t>
+        </is>
+      </c>
+      <c r="J252" s="30" t="inlineStr">
+        <is>
+          <t>Markets shows "Updated offline" and a banner; Arya replies in plain language with links to what works offline; watchlist and holdings keep the last price, marked old</t>
+        </is>
+      </c>
       <c r="K252" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14197,7 @@
       </c>
       <c r="E253" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F253" s="30" t="inlineStr">
@@ -14191,15 +14211,19 @@
         </is>
       </c>
       <c r="H253" s="30" t="n"/>
-      <c r="I253" s="30" t="n"/>
+      <c r="I253" s="30" t="inlineStr">
+        <is>
+          <t>mobile/scripts/smoke-routes.py</t>
+        </is>
+      </c>
       <c r="J253" s="30" t="inlineStr">
         <is>
-          <t>Pure logic is covered (51 tests); screens are verified by hand in the preview</t>
+          <t>Every screen opened empty and populated, dark and light; fails on errors / NaN / empty. Unit tests cover the logic (331)</t>
         </is>
       </c>
       <c r="K253" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -15845,28 +15869,78 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>P-01, T-37, P-09</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Light theme (runtime colour mapper, contrast-audited), Financial report (text share), Profile; Hindi strings</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>theme.test.mts (9), report.test.mts (6), profile.test.mts (4); 27-screen contrast audit = 0; preview run</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="16" t="n">
         <v>322</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>R-12, R-14, R-15, S-07 (watchlist)</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Route smoke script (found nested buttons on Portfolio), plain-language offline Arya reply with links, 200% text cap, watchlist</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>smoke-routes: 55 screens x 4 runs = 0; watchlist.test.mts (5), aryaOffline.test.mts (4)</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S-04 (XIRR)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Annualised return from entered purchase dates; undated holdings left out</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>xirr.test.mts (6); preview run: 20 -&gt; 24 over 2 years = 9.5% a year</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E2" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F2" s="30" t="inlineStr">
@@ -1255,10 +1255,14 @@
           <t>tools/…</t>
         </is>
       </c>
-      <c r="J2" s="30" t="n"/>
+      <c r="J2" s="30" t="inlineStr">
+        <is>
+          <t>app/plan/growth.tsx: holdings at the last fetched price (cost, flagged, when never priced) and their SIPs; the return is never pre-filled, low/high at +-2 points, before tax and costs. Equals the website calculator page on 150 inputs.</t>
+        </is>
+      </c>
       <c r="K2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1289,7 @@
       </c>
       <c r="E3" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F3" s="30" t="inlineStr">
@@ -1306,12 +1310,12 @@
       </c>
       <c r="J3" s="30" t="inlineStr">
         <is>
-          <t>Category limits, pace and suggestions are done; the forecast view is not | Website forecast fixed Oct 13 2026 (js/finos-forecast.js): income no longer counted as spend; port after the Budget screen settles</t>
+          <t>app/plan/forecast.tsx: port of js/finos-forecast.js (parity-tested on 600 ledgers). Figure is for the current month; hidden trend/risk under 3 months of history; writes only finos_forecast_next_month.</t>
         </is>
       </c>
       <c r="K3" s="30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1709,7 @@
       </c>
       <c r="E11" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F11" s="30" t="inlineStr">
@@ -1728,12 +1732,12 @@
       </c>
       <c r="J11" s="30" t="inlineStr">
         <is>
-          <t>Month grid, day detail, coming-up list, summary cards: SIP, deposit maturities (real terms), insurance, goals, subscriptions, tax dates; parity-tested. Phone notifications NOT built: need an OS notification permission, which the privacy guard test currently forbids (owner decision).</t>
+          <t>Month grid, coming-up list and summary as before, plus your own dates (once / monthly / yearly, app/plan/mydates.tsx) on the grid and in reminders, and an .ics export of the next 12 months with an amounts switch. Reminders and notifications exist (lib/reminders*.ts); not verified on a device (R-10).</t>
         </is>
       </c>
       <c r="K11" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1976,7 @@
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
@@ -1993,12 +1997,12 @@
       </c>
       <c r="J16" s="30" t="inlineStr">
         <is>
-          <t>Policies, gaps and renewals are done; directory/compare is not</t>
+          <t>app/insurance: cover-type directory extracted from the website's own pages with file+line provenance, per-type questions, compare of cover types and of your own policies, checklist answers on the phone. No insurer or product is named or ranked (the website has none). Figures the website states are shown as statements: date not stated, not verified.</t>
         </is>
       </c>
       <c r="K16" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2135,7 @@
       </c>
       <c r="E19" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F19" s="30" t="inlineStr">
@@ -2152,12 +2156,12 @@
       </c>
       <c r="J19" s="30" t="inlineStr">
         <is>
-          <t>Funding maths = Goal optimizer (T-12). The phase-by-phase roadmap text is generic advice and is not ported. Website maths fixed Oct 13 (savings were credited to every goal)</t>
+          <t>app/plan/lifegoals.tsx: port of js/finos-life-goals.js (1,500 households) with a roadmap rebuilt from derived figures only; prefill only from recorded data; the earlier generic advice lines were removed on both website and phone. Feasibility saved under finos_life_goals_feasibility.</t>
         </is>
       </c>
       <c r="K19" s="30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2188,7 @@
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
@@ -2203,10 +2207,14 @@
           <t>markets/mf</t>
         </is>
       </c>
-      <c r="J20" s="30" t="n"/>
+      <c r="J20" s="30" t="inlineStr">
+        <is>
+          <t>app/funds: search, detail (Direct/Regular x Growth/IDCW shown separately), compare up to 3, Direct vs Regular expense impact and SIP consistency (both parity-tested). Returns need GET /api/mf/history, which the backend now serves but the phone has not been exercised against end to end. No expense ratio, exit load, holdings or category returns in the feed.</t>
+        </is>
+      </c>
       <c r="K20" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3094,10 +3102,14 @@
           <t>tracker/health</t>
         </is>
       </c>
-      <c r="J37" s="30" t="n"/>
+      <c r="J37" s="30" t="inlineStr">
+        <is>
+          <t>Knowledge &amp; engagement pillar now fed from lessons marked learned (floor(count x 0.43), cap 6, plus streak points, cap 10), golden test against js/finos-health-score.js. The website previously counted only the array shape and so awarded nothing for what learn-ai.js writes; that was fixed on the website in the working tree (uncommitted).</t>
+        </is>
+      </c>
       <c r="K37" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3189,7 @@
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F39" s="30" t="inlineStr">
@@ -3198,12 +3210,12 @@
       </c>
       <c r="J39" s="30" t="inlineStr">
         <is>
-          <t>Needs the couple_* Supabase tables</t>
+          <t>On-device arithmetic on figures typed for two people (app/plan/couple.tsx): joint income/spend/savings, proportional bill split, 15%-of-joint-income large-item flag, joint goals. Kept under a sync-excluded key. No account linking and no server tables needed.</t>
         </is>
       </c>
       <c r="K39" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3242,7 @@
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
@@ -3249,10 +3261,14 @@
           <t>tools/benchmark</t>
         </is>
       </c>
-      <c r="J40" s="30" t="n"/>
+      <c r="J40" s="30" t="inlineStr">
+        <is>
+          <t>Rule-of-thumb targets only (app/plan/benchmark.tsx): your own recorded figures against the Money Score targets, each labelled. Peer comparison deliberately not built: the website's "average peer / top 10%" table has no verifiable source.</t>
+        </is>
+      </c>
       <c r="K40" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8118,7 @@
       </c>
       <c r="E132" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F132" s="30" t="inlineStr">
@@ -8123,12 +8139,12 @@
       </c>
       <c r="J132" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). No passage flagged in the content review. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K132" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8171,7 @@
       </c>
       <c r="E133" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F133" s="30" t="inlineStr">
@@ -8176,12 +8192,12 @@
       </c>
       <c r="J133" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 3 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K133" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8224,7 @@
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
@@ -8229,12 +8245,12 @@
       </c>
       <c r="J134" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). No passage flagged in the content review. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K134" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8277,7 @@
       </c>
       <c r="E135" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F135" s="30" t="inlineStr">
@@ -8282,12 +8298,12 @@
       </c>
       <c r="J135" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 2 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K135" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8330,7 @@
       </c>
       <c r="E136" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F136" s="30" t="inlineStr">
@@ -8335,12 +8351,12 @@
       </c>
       <c r="J136" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 2 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K136" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8383,7 @@
       </c>
       <c r="E137" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F137" s="30" t="inlineStr">
@@ -8388,12 +8404,12 @@
       </c>
       <c r="J137" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 1 passage flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K137" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8436,7 @@
       </c>
       <c r="E138" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F138" s="30" t="inlineStr">
@@ -8441,12 +8457,12 @@
       </c>
       <c r="J138" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 2 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K138" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8489,7 @@
       </c>
       <c r="E139" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F139" s="30" t="inlineStr">
@@ -8494,12 +8510,12 @@
       </c>
       <c r="J139" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 4 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K139" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8542,7 @@
       </c>
       <c r="E140" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F140" s="30" t="inlineStr">
@@ -8547,12 +8563,12 @@
       </c>
       <c r="J140" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). No passage flagged in the content review. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K140" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8595,7 @@
       </c>
       <c r="E141" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F141" s="30" t="inlineStr">
@@ -8600,12 +8616,12 @@
       </c>
       <c r="J141" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 1 passage flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K141" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8648,7 @@
       </c>
       <c r="E142" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F142" s="30" t="inlineStr">
@@ -8653,12 +8669,12 @@
       </c>
       <c r="J142" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 3 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K142" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8701,7 @@
       </c>
       <c r="E143" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F143" s="30" t="inlineStr">
@@ -8706,12 +8722,12 @@
       </c>
       <c r="J143" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 2 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K143" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8754,7 @@
       </c>
       <c r="E144" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F144" s="30" t="inlineStr">
@@ -8759,12 +8775,12 @@
       </c>
       <c r="J144" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 2 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K144" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8807,7 @@
       </c>
       <c r="E145" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F145" s="30" t="inlineStr">
@@ -8812,12 +8828,12 @@
       </c>
       <c r="J145" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 3 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K145" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8860,7 @@
       </c>
       <c r="E146" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F146" s="30" t="inlineStr">
@@ -8865,12 +8881,12 @@
       </c>
       <c r="J146" s="30" t="inlineStr">
         <is>
-          <t>Content-heavy; candidate for the in-app web view</t>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). No passage flagged in the content review. English only; widgets of the page are not reproduced.</t>
         </is>
       </c>
       <c r="K146" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8913,7 @@
       </c>
       <c r="E147" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F147" s="30" t="inlineStr">
@@ -8916,10 +8932,14 @@
           <t>learn/insight-debt</t>
         </is>
       </c>
-      <c r="J147" s="30" t="n"/>
+      <c r="J147" s="30" t="inlineStr">
+        <is>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). No passage flagged in the content review. English only; widgets of the page are not reproduced.</t>
+        </is>
+      </c>
       <c r="K147" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8966,7 @@
       </c>
       <c r="E148" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F148" s="30" t="inlineStr">
@@ -8965,10 +8985,14 @@
           <t>learn/insight-emi</t>
         </is>
       </c>
-      <c r="J148" s="30" t="n"/>
+      <c r="J148" s="30" t="inlineStr">
+        <is>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 1 passage flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
+        </is>
+      </c>
       <c r="K148" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8995,7 +9019,7 @@
       </c>
       <c r="E149" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F149" s="30" t="inlineStr">
@@ -9014,10 +9038,14 @@
           <t>learn/insight-inflation</t>
         </is>
       </c>
-      <c r="J149" s="30" t="n"/>
+      <c r="J149" s="30" t="inlineStr">
+        <is>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 1 passage flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
+        </is>
+      </c>
       <c r="K149" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9072,7 @@
       </c>
       <c r="E150" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F150" s="30" t="inlineStr">
@@ -9063,10 +9091,14 @@
           <t>learn/insight-rbi</t>
         </is>
       </c>
-      <c r="J150" s="30" t="n"/>
+      <c r="J150" s="30" t="inlineStr">
+        <is>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). No passage flagged in the content review. English only; widgets of the page are not reproduced.</t>
+        </is>
+      </c>
       <c r="K150" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9125,7 @@
       </c>
       <c r="E151" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F151" s="30" t="inlineStr">
@@ -9112,10 +9144,14 @@
           <t>learn/insight-sip</t>
         </is>
       </c>
-      <c r="J151" s="30" t="n"/>
+      <c r="J151" s="30" t="inlineStr">
+        <is>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 1 passage flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
+        </is>
+      </c>
       <c r="K151" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9178,7 @@
       </c>
       <c r="E152" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F152" s="30" t="inlineStr">
@@ -9161,10 +9197,14 @@
           <t>learn/finance101</t>
         </is>
       </c>
-      <c r="J152" s="30" t="n"/>
+      <c r="J152" s="30" t="inlineStr">
+        <is>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). 4 passages flagged for fact-check (docs/agent-notes/learn-review.md); the reader shows a notice on each. English only; widgets of the page are not reproduced.</t>
+        </is>
+      </c>
       <c r="K152" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9231,7 @@
       </c>
       <c r="E153" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F153" s="30" t="inlineStr">
@@ -9210,10 +9250,14 @@
           <t>learn/foundations</t>
         </is>
       </c>
-      <c r="J153" s="30" t="n"/>
+      <c r="J153" s="30" t="inlineStr">
+        <is>
+          <t>Interactive page: not flattened into text. It has no phone equivalent, so the lesson screen says it is interactive on the website.</t>
+        </is>
+      </c>
       <c r="K153" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9284,7 @@
       </c>
       <c r="E154" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F154" s="30" t="inlineStr">
@@ -9259,10 +9303,14 @@
           <t>learn/principles</t>
         </is>
       </c>
-      <c r="J154" s="30" t="n"/>
+      <c r="J154" s="30" t="inlineStr">
+        <is>
+          <t>Phone lesson reader (app/learn/[id].tsx), text extracted from the website page by mobile/scripts/extract-learn.py; progress in finos_learned_modules (website shape). No passage flagged in the content review. English only; widgets of the page are not reproduced.</t>
+        </is>
+      </c>
       <c r="K154" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9337,7 @@
       </c>
       <c r="E155" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F155" s="30" t="inlineStr">
@@ -9308,10 +9356,14 @@
           <t>learn/investor-mindset</t>
         </is>
       </c>
-      <c r="J155" s="30" t="n"/>
+      <c r="J155" s="30" t="inlineStr">
+        <is>
+          <t>Interactive page: not flattened into text. The lesson screen links to the matching phone tool: Financial DNA (/tools/dna).</t>
+        </is>
+      </c>
       <c r="K155" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9390,7 @@
       </c>
       <c r="E156" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F156" s="30" t="inlineStr">
@@ -9357,10 +9409,14 @@
           <t>learn/investor-profile</t>
         </is>
       </c>
-      <c r="J156" s="30" t="n"/>
+      <c r="J156" s="30" t="inlineStr">
+        <is>
+          <t>Interactive page: not flattened into text. The lesson screen links to the matching phone tool: Financial DNA (/tools/dna).</t>
+        </is>
+      </c>
       <c r="K156" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10178,7 @@
       </c>
       <c r="E172" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F172" s="30" t="inlineStr">
@@ -10141,10 +10197,14 @@
           <t>learn/simulator-guide</t>
         </is>
       </c>
-      <c r="J172" s="30" t="n"/>
+      <c r="J172" s="30" t="inlineStr">
+        <is>
+          <t>Website only: a manual for the trading simulator's UI; nothing on the phone to apply it to (excluded in the Learn manifest).</t>
+        </is>
+      </c>
       <c r="K172" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10876,7 @@
       </c>
       <c r="E186" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F186" s="30" t="inlineStr">
@@ -10835,10 +10895,14 @@
           <t>markets/equitydetail</t>
         </is>
       </c>
-      <c r="J186" s="30" t="n"/>
+      <c r="J186" s="30" t="inlineStr">
+        <is>
+          <t>app/market/stock/[symbol].tsx: live quote, day and 52-week range, 1M/3M/6M/1Y chart, labelled fundamentals, add to watchlist. The website's masterclass text is editorial and not ported.</t>
+        </is>
+      </c>
       <c r="K186" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10929,7 @@
       </c>
       <c r="E187" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F187" s="30" t="inlineStr">
@@ -10884,10 +10948,14 @@
           <t>markets/etfdetail</t>
         </is>
       </c>
-      <c r="J187" s="30" t="n"/>
+      <c r="J187" s="30" t="inlineStr">
+        <is>
+          <t>An ETF opens the same share screen. Expense ratio and tracking error are not in any source the backend has.</t>
+        </is>
+      </c>
       <c r="K187" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10982,7 @@
       </c>
       <c r="E188" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F188" s="30" t="inlineStr">
@@ -10933,10 +11001,14 @@
           <t>markets/mfdetail</t>
         </is>
       </c>
-      <c r="J188" s="30" t="n"/>
+      <c r="J188" s="30" t="inlineStr">
+        <is>
+          <t>app/market/fund/[code].tsx: NAV, plan and option, NAV history chart, computed point-to-point returns (flagged as not factsheet figures; IDCW understated).</t>
+        </is>
+      </c>
       <c r="K188" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10963,7 +11035,7 @@
       </c>
       <c r="E189" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F189" s="30" t="inlineStr">
@@ -10982,10 +11054,14 @@
           <t>markets/cryptodetail</t>
         </is>
       </c>
-      <c r="J189" s="30" t="n"/>
+      <c r="J189" s="30" t="inlineStr">
+        <is>
+          <t>Live prices only (app/market/crypto.tsx): no detail page, no on-chain or market-cap history.</t>
+        </is>
+      </c>
       <c r="K189" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11088,7 @@
       </c>
       <c r="E190" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F190" s="30" t="inlineStr">
@@ -11031,10 +11107,14 @@
           <t>markets/commoditydetail</t>
         </is>
       </c>
-      <c r="J190" s="30" t="n"/>
+      <c r="J190" s="30" t="inlineStr">
+        <is>
+          <t>Live prices only (app/market/commodities.tsx): gold and silver are world prices converted at a live USD/INR, not MCX; unavailable when no live rate.</t>
+        </is>
+      </c>
       <c r="K190" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11141,7 @@
       </c>
       <c r="E191" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F191" s="30" t="inlineStr">
@@ -11080,10 +11160,14 @@
           <t>markets/forexdetail</t>
         </is>
       </c>
-      <c r="J191" s="30" t="n"/>
+      <c r="J191" s="30" t="inlineStr">
+        <is>
+          <t>Live rates only (app/market/fx.tsx): no detail page or history.</t>
+        </is>
+      </c>
       <c r="K191" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11439,7 @@
       </c>
       <c r="E197" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F197" s="30" t="inlineStr">
@@ -11374,10 +11458,14 @@
           <t>markets/stock-platform</t>
         </is>
       </c>
-      <c r="J197" s="30" t="n"/>
+      <c r="J197" s="30" t="inlineStr">
+        <is>
+          <t>Price-only screener over a 50-name list (day move, distance from 52-week high/low). The list is Nifty 50 membership as of late 2025 and was not checked against NSE. No fundamentals screen: needs the stock-engine service.</t>
+        </is>
+      </c>
       <c r="K197" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11639,7 @@
       </c>
       <c r="E201" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F201" s="30" t="inlineStr">
@@ -11570,10 +11658,14 @@
           <t>markets/news</t>
         </is>
       </c>
-      <c r="J201" s="30" t="n"/>
+      <c r="J201" s="30" t="inlineStr">
+        <is>
+          <t>app/market/news.tsx: headlines with source and time, stated keyword-sentiment, tag filter, "x of y sources answered", last saved answer when offline. Moneycontrol and Business Standard feeds returned 403 to the backend when checked.</t>
+        </is>
+      </c>
       <c r="K201" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11741,7 @@
       </c>
       <c r="E203" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F203" s="30" t="inlineStr">
@@ -11668,10 +11760,14 @@
           <t>markets/insurance-directory</t>
         </is>
       </c>
-      <c r="J203" s="30" t="n"/>
+      <c r="J203" s="30" t="inlineStr">
+        <is>
+          <t>Same hub: the website's insurance directory is a directory of cover types, which is what is shown. A directory of insurers does not exist on the website and was not invented.</t>
+        </is>
+      </c>
       <c r="K203" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12787,7 +12883,7 @@
       </c>
       <c r="E225" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F225" s="30" t="inlineStr">
@@ -12801,15 +12897,19 @@
         </is>
       </c>
       <c r="H225" s="30" t="n"/>
-      <c r="I225" s="30" t="n"/>
+      <c r="I225" s="30" t="inlineStr">
+        <is>
+          <t>app/security.tsx</t>
+        </is>
+      </c>
       <c r="J225" s="30" t="inlineStr">
         <is>
-          <t>Phone could use OS biometrics instead</t>
+          <t>PIN lock + encrypted backup interoperable with the website vault. Lock is a screen gate (not storage encryption). Not yet tried with biometrics / app switcher on a device</t>
         </is>
       </c>
       <c r="K225" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12989,7 @@
       </c>
       <c r="E227" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F227" s="30" t="inlineStr">
@@ -12903,15 +13003,19 @@
         </is>
       </c>
       <c r="H227" s="30" t="n"/>
-      <c r="I227" s="30" t="n"/>
+      <c r="I227" s="30" t="inlineStr">
+        <is>
+          <t>app/alerts.tsx</t>
+        </is>
+      </c>
       <c r="J227" s="30" t="inlineStr">
         <is>
-          <t>Backend runs on the user's machine</t>
+          <t>On-device rules from recorded data; bank-feed rules (missed SIP, salary credit, card bill) and market drop are not faked</t>
         </is>
       </c>
       <c r="K227" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -13044,7 +13148,7 @@
       </c>
       <c r="E230" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F230" s="30" t="inlineStr">
@@ -13065,12 +13169,12 @@
       </c>
       <c r="J230" s="30" t="inlineStr">
         <is>
-          <t>DNA quiz done (feeds Health Score Behaviour). First-run onboarding flow not built: Home action items + Money Score invitation cover it</t>
+          <t>app/onboarding/welcome.tsx: skippable and resumable, shown at most twice, never for a phone that already holds data, re-openable from Settings, writes only answered fields.</t>
         </is>
       </c>
       <c r="K230" s="30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13254,7 @@
       </c>
       <c r="E232" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F232" s="30" t="inlineStr">
@@ -13167,12 +13271,12 @@
       <c r="I232" s="30" t="n"/>
       <c r="J232" s="30" t="inlineStr">
         <is>
-          <t>Enabled on the Supabase project</t>
+          <t>Code path built and unit-tested with fakes (lib/googleAuth.ts); the button is hidden unless EXPO_PUBLIC_GOOGLE_SIGNIN=1. Needs finos://auth-callback in the Supabase redirect list; never run against a real project.</t>
         </is>
       </c>
       <c r="K232" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13199,7 +13303,7 @@
       </c>
       <c r="E233" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F233" s="30" t="inlineStr">
@@ -13214,10 +13318,14 @@
       </c>
       <c r="H233" s="30" t="n"/>
       <c r="I233" s="30" t="n"/>
-      <c r="J233" s="30" t="n"/>
+      <c r="J233" s="30" t="inlineStr">
+        <is>
+          <t>app/feedback.tsx and components/FeedbackPrompt.tsx: saved on the phone first, share sheet only; redaction parity-tested against the website; send() decisions equal the website's. The endpoint is null, as on the website (U3).</t>
+        </is>
+      </c>
       <c r="K233" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14207,7 @@
       </c>
       <c r="E251" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F251" s="30" t="inlineStr">
@@ -14114,10 +14222,14 @@
       </c>
       <c r="H251" s="30" t="n"/>
       <c r="I251" s="30" t="n"/>
-      <c r="J251" s="30" t="n"/>
+      <c r="J251" s="30" t="inlineStr">
+        <is>
+          <t>On-device redacted crash notes, error boundary, Diagnostics screen and opt-in screen counts (default off); nothing is sent automatically and there is no crash service. Fatal native crashes may kill the process before a note is written.</t>
+        </is>
+      </c>
       <c r="K251" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15092,7 +15204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -15919,28 +16031,53 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>S-04 (XIRR)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>Annualised return from entered purchase dates; undated holdings left out</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>xirr.test.mts (6); preview run: 20 -&gt; 24 over 2 years = 9.5% a year</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="16" t="n">
         <v>337</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>P-03, P-05</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>App lock + encrypted backup (interoperates with web vault both ways); on-device alerts bell</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>vaultCrypto.test (5), appLock.test (5), backup.test (3), alerts.test (9); preview: lock/unlock/wrong PIN, real 310k-round backup opened by js/finos-vault.js</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MOBILE_PARITY_TRACKER.xlsx
+++ b/docs/MOBILE_PARITY_TRACKER.xlsx
@@ -664,10 +664,11 @@
     <row r="2" ht="15" customHeight="1" s="17">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Source of truth: the 'Parity Tracker' sheet. Counts below are formulas. Last built 2026-10-12.</t>
-        </is>
-      </c>
-    </row>
+          <t>Source of truth: the 'Parity Tracker' sheet. Counts below are formulas. All rows audited against the code and the agent notes on 2026-10-17 (final integration). Nothing is marked as verified on a device: every status rests on the Expo web preview and unit tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="17">
       <c r="A4" s="20" t="inlineStr">
         <is>
@@ -9231,7 +9232,7 @@
       </c>
       <c r="E153" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F153" s="30" t="inlineStr">
@@ -9252,12 +9253,12 @@
       </c>
       <c r="J153" s="30" t="inlineStr">
         <is>
-          <t>Interactive page: not flattened into text. It has no phone equivalent, so the lesson screen says it is interactive on the website.</t>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a menu page on the website: the phone page lists its five entries, each mapped to a lesson, tool or tab. Web preview only. Not verified on a device.</t>
         </is>
       </c>
       <c r="K153" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9338,7 @@
       </c>
       <c r="E155" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F155" s="30" t="inlineStr">
@@ -9358,12 +9359,12 @@
       </c>
       <c r="J155" s="30" t="inlineStr">
         <is>
-          <t>Interactive page: not flattened into text. The lesson screen links to the matching phone tool: Financial DNA (/tools/dna).</t>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): demonstration panels with example numbers ("Simulated sector momentum scores"); not flattened. The page says so and points to Financial DNA, which is a different tool. Not verified on a device.</t>
         </is>
       </c>
       <c r="K155" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9391,7 @@
       </c>
       <c r="E156" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F156" s="30" t="inlineStr">
@@ -9411,12 +9412,12 @@
       </c>
       <c r="J156" s="30" t="inlineStr">
         <is>
-          <t>Interactive page: not flattened into text. The lesson screen links to the matching phone tool: Financial DNA (/tools/dna).</t>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): an imagined "Indian market translation" of ten investors; not copied. The page says so and points to Financial DNA, a different tool. Not verified on a device.</t>
         </is>
       </c>
       <c r="K156" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9493,7 @@
       </c>
       <c r="E158" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F158" s="30" t="inlineStr">
@@ -9511,10 +9512,14 @@
           <t>learn/mindset-sim</t>
         </is>
       </c>
-      <c r="J158" s="30" t="n"/>
+      <c r="J158" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): the 20 scenarios as case studies (Hinglish as on the website), each passage with its source line. The choose-then-reveal flow, score and AI debrief are not on the phone and the lesson says so. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K158" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9546,7 @@
       </c>
       <c r="E159" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F159" s="30" t="inlineStr">
@@ -9560,10 +9565,14 @@
           <t>learn/mindset-sim-hub</t>
         </is>
       </c>
-      <c r="J159" s="30" t="n"/>
+      <c r="J159" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): the website page only forwards to the Simulator Hub; the phone page says so. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K159" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9599,7 @@
       </c>
       <c r="E160" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F160" s="30" t="inlineStr">
@@ -9609,10 +9618,14 @@
           <t>learn/train-mindset</t>
         </is>
       </c>
-      <c r="J160" s="30" t="n"/>
+      <c r="J160" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): the website page only forwards to the Simulator Hub; the phone page says so. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K160" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9652,7 @@
       </c>
       <c r="E161" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F161" s="30" t="inlineStr">
@@ -9658,10 +9671,14 @@
           <t>learn/not-money</t>
         </is>
       </c>
-      <c r="J161" s="30" t="n"/>
+      <c r="J161" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): the website page only forwards to the AI Mindset Simulator; the phone page says so. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K161" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9705,7 @@
       </c>
       <c r="E162" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F162" s="30" t="inlineStr">
@@ -9707,10 +9724,14 @@
           <t>learn/decision</t>
         </is>
       </c>
-      <c r="J162" s="30" t="n"/>
+      <c r="J162" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): lesson text (fast vs slow thinking, three biases, checklist). The doughnut chart of fixed example slices is left out and said so. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K162" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9758,7 @@
       </c>
       <c r="E163" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F163" s="30" t="inlineStr">
@@ -9756,10 +9777,14 @@
           <t>learn/clarity</t>
         </is>
       </c>
-      <c r="J163" s="30" t="n"/>
+      <c r="J163" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): lesson text plus a link to Net worth. The scanner strip, DONE/CURRENT/LOCKED labels and the EMI slider (rough x120x1.8 rule) are not shown; each is explained. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K163" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9811,7 @@
       </c>
       <c r="E164" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F164" s="30" t="inlineStr">
@@ -9805,10 +9830,14 @@
           <t>learn/scenarios</t>
         </is>
       </c>
-      <c r="J164" s="30" t="n"/>
+      <c r="J164" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a hub: the nine what-if simulations run on stored numbers with AI narration on the website and are not on the phone; each is listed with the closest phone tool (or none). Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K164" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9864,7 @@
       </c>
       <c r="E165" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F165" s="30" t="inlineStr">
@@ -9854,10 +9883,14 @@
           <t>learn/timeline</t>
         </is>
       </c>
-      <c r="J165" s="30" t="n"/>
+      <c r="J165" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): the website page shows generated sample scores whenever it cannot reach its alert service, so it was not copied. The phone page explains this and names Money Score as the nearest real thing. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K165" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9917,7 @@
       </c>
       <c r="E166" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F166" s="30" t="inlineStr">
@@ -9903,10 +9936,14 @@
           <t>learn/fear-roadmap</t>
         </is>
       </c>
-      <c r="J166" s="30" t="n"/>
+      <c r="J166" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a quiz whose answers pick written outcomes, so not lesson text for everyone; the page explains why there is no honest equivalent. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K166" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9970,7 @@
       </c>
       <c r="E167" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F167" s="30" t="inlineStr">
@@ -9952,10 +9989,14 @@
           <t>learn/roadmap</t>
         </is>
       </c>
-      <c r="J167" s="30" t="n"/>
+      <c r="J167" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a hub: the personalised roadmap and mind map are built from stored data on the website and are not on the phone; its 7-path menu is listed with the phone equivalents (e.g. Arya Plan). Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K167" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9982,7 +10023,7 @@
       </c>
       <c r="E168" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F168" s="30" t="inlineStr">
@@ -10001,10 +10042,14 @@
           <t>learn/roadmaps</t>
         </is>
       </c>
-      <c r="J168" s="30" t="n"/>
+      <c r="J168" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): the website page only redirects to Roadmap; the phone page says so. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K168" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10076,7 @@
       </c>
       <c r="E169" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F169" s="30" t="inlineStr">
@@ -10050,10 +10095,14 @@
           <t>learn/trader-roadmap</t>
         </is>
       </c>
-      <c r="J169" s="30" t="n"/>
+      <c r="J169" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a six-question quiz that picks one of five personas (one says to close all trading accounts), so not general advice; the page explains why there is no honest equivalent. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K169" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10129,7 @@
       </c>
       <c r="E170" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F170" s="30" t="inlineStr">
@@ -10099,10 +10148,14 @@
           <t>learn/traditional-roadmap</t>
         </is>
       </c>
-      <c r="J170" s="30" t="n"/>
+      <c r="J170" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a two-question quiz whose step list has out-of-date tax and inflation statements; not copied, the page explains why. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K170" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10182,7 @@
       </c>
       <c r="E171" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F171" s="30" t="inlineStr">
@@ -10148,10 +10201,14 @@
           <t>learn/simulator</t>
         </is>
       </c>
-      <c r="J171" s="30" t="n"/>
+      <c r="J171" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): the website page only redirects to the Simulator Hub; the phone page says so. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K171" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10288,7 @@
       </c>
       <c r="E173" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F173" s="30" t="inlineStr">
@@ -10250,10 +10307,14 @@
           <t>learn/simulator-landing</t>
         </is>
       </c>
-      <c r="J173" s="30" t="n"/>
+      <c r="J173" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a hub: menu of six simulator cards (the ticker strip uses fixed typed-in prices and is not shown); the simulators themselves are not on the phone. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K173" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10341,7 @@
       </c>
       <c r="E174" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F174" s="30" t="inlineStr">
@@ -10299,10 +10360,14 @@
           <t>learn/trading-simulator</t>
         </is>
       </c>
-      <c r="J174" s="30" t="n"/>
+      <c r="J174" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): website only: a practice-trading UI with generated candles. No trading features on the phone; the phone page says so. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K174" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10394,7 @@
       </c>
       <c r="E175" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F175" s="30" t="inlineStr">
@@ -10348,10 +10413,14 @@
           <t>learn/trading-coach</t>
         </is>
       </c>
-      <c r="J175" s="30" t="n"/>
+      <c r="J175" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a 3-question clearance plus an AI assessment; trader-only and needs the website AI service. The page explains why. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K175" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10447,7 @@
       </c>
       <c r="E176" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F176" s="30" t="inlineStr">
@@ -10397,10 +10466,14 @@
           <t>learn/trading-brain</t>
         </is>
       </c>
-      <c r="J176" s="30" t="n"/>
+      <c r="J176" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): live signals from data services, and pattern tables quote win rates with no stated method; not copied. The page explains why. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K176" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10500,7 @@
       </c>
       <c r="E177" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F177" s="30" t="inlineStr">
@@ -10446,10 +10519,14 @@
           <t>learn/know-your-finances</t>
         </is>
       </c>
-      <c r="J177" s="30" t="n"/>
+      <c r="J177" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a long input form plus an AI scan; the page explains why and names the phone parts (Net worth, Money Score, Retirement planner). Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K177" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10553,7 @@
       </c>
       <c r="E178" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F178" s="30" t="inlineStr">
@@ -10495,10 +10572,14 @@
           <t>learn/financial-being</t>
         </is>
       </c>
-      <c r="J178" s="30" t="n"/>
+      <c r="J178" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a long self-assessment ending in an AI report; the page explains why and names Financial DNA as a different, shorter quiz. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K178" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10525,7 +10606,7 @@
       </c>
       <c r="E179" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F179" s="30" t="inlineStr">
@@ -10544,10 +10625,14 @@
           <t>learn/diagnostics</t>
         </is>
       </c>
-      <c r="J179" s="30" t="n"/>
+      <c r="J179" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a hub: menu of two scans and four tools; the phone has Financial DNA, Benchmarks and Future loss (not the phone's crash-notes Diagnostics screen). Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K179" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10659,7 @@
       </c>
       <c r="E180" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F180" s="30" t="inlineStr">
@@ -10593,10 +10678,14 @@
           <t>learn/life-wealth</t>
         </is>
       </c>
-      <c r="J180" s="30" t="n"/>
+      <c r="J180" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): lesson text (milestones and money-vs-soul pairs from the page and its script), source lines on every passage. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K180" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10712,7 @@
       </c>
       <c r="E181" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F181" s="30" t="inlineStr">
@@ -10642,10 +10731,14 @@
           <t>learn/impact</t>
         </is>
       </c>
-      <c r="J181" s="30" t="n"/>
+      <c r="J181" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): a hub: the compound box (= the SIP calculator on the phone) and eight story cards (= Impact stories, L-51). Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K181" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10765,7 @@
       </c>
       <c r="E182" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F182" s="30" t="inlineStr">
@@ -10691,10 +10784,14 @@
           <t>learn/impact-detail</t>
         </is>
       </c>
-      <c r="J182" s="30" t="n"/>
+      <c r="J182" s="30" t="inlineStr">
+        <is>
+          <t>Learn wave 2 (docs/agent-notes/learn2.md): the eight five-step stories from js/impact-detail.js, with source lines; two stated figures are wrong on the website and are flagged in the lesson. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K182" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11132,7 @@
       </c>
       <c r="E189" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F189" s="30" t="inlineStr">
@@ -11051,17 +11148,17 @@
       <c r="H189" s="30" t="n"/>
       <c r="I189" s="30" t="inlineStr">
         <is>
-          <t>markets/cryptodetail</t>
+          <t>market/crypto/[id]</t>
         </is>
       </c>
       <c r="J189" s="30" t="inlineStr">
         <is>
-          <t>Live prices only (app/market/crypto.tsx): no detail page, no on-chain or market-cap history.</t>
+          <t>portfolio-analytics.md: detail with price history. Polygon has no history source (shows today's price and says why). Chart steps on sub-5 prices (backend rounding, U14). Web preview only. Not verified on a device.</t>
         </is>
       </c>
       <c r="K189" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11185,7 @@
       </c>
       <c r="E190" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F190" s="30" t="inlineStr">
@@ -11104,17 +11201,17 @@
       <c r="H190" s="30" t="n"/>
       <c r="I190" s="30" t="inlineStr">
         <is>
-          <t>markets/commoditydetail</t>
+          <t>market/commodity/[key]</t>
         </is>
       </c>
       <c r="J190" s="30" t="inlineStr">
         <is>
-          <t>Live prices only (app/market/commodities.tsx): gold and silver are world prices converted at a live USD/INR, not MCX; unavailable when no live rate.</t>
+          <t>portfolio-analytics.md: gold, silver, crude, natural gas with history; chart is world futures in USD (the rupee card stays labelled as converted, not MCX); futures roll jumps appear. Not verified on a device.</t>
         </is>
       </c>
       <c r="K190" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11238,7 @@
       </c>
       <c r="E191" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F191" s="30" t="inlineStr">
@@ -11157,17 +11254,17 @@
       <c r="H191" s="30" t="n"/>
       <c r="I191" s="30" t="inlineStr">
         <is>
-          <t>markets/forexdetail</t>
+          <t>market/fx/[pair]</t>
         </is>
       </c>
       <c r="J191" s="30" t="inlineStr">
         <is>
-          <t>Live rates only (app/market/fx.tsx): no detail page or history.</t>
+          <t>portfolio-analytics.md: USD/EUR/GBP/JPY/AED to INR with history and a two-way converter at the market rate; JPY chart is stepped (backend rounding). Not verified on a device.</t>
         </is>
       </c>
       <c r="K191" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11487,7 @@
       </c>
       <c r="E196" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F196" s="30" t="inlineStr">
@@ -11406,13 +11503,17 @@
       <c r="H196" s="30" t="n"/>
       <c r="I196" s="30" t="inlineStr">
         <is>
-          <t>markets/market-visualizer</t>
-        </is>
-      </c>
-      <c r="J196" s="30" t="n"/>
+          <t>market/map</t>
+        </is>
+      </c>
+      <c r="J196" s="30" t="inlineStr">
+        <is>
+          <t>portfolio-analytics.md: the website deep-dive needs a port-5000 service and scrapes metrics with invented defaults, so it is not ported. Built a different honest visual: Market map (index and sector tiles, 50 large companies by size, coloured by day move). Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K196" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11492,7 +11593,7 @@
       </c>
       <c r="E198" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F198" s="30" t="inlineStr">
@@ -11508,13 +11609,17 @@
       <c r="H198" s="30" t="n"/>
       <c r="I198" s="30" t="inlineStr">
         <is>
-          <t>markets/options-intelligence</t>
-        </is>
-      </c>
-      <c r="J198" s="30" t="n"/>
+          <t>market/options</t>
+        </is>
+      </c>
+      <c r="J198" s="30" t="inlineStr">
+        <is>
+          <t>portfolio-analytics.md: Black-Scholes price and Greeks (parity-tested against the page's functions), expiry payoff for six strategies from typed strikes and premiums; Nifty spot and India VIX shown for reference. No option chain or IV rank: the page's are random numbers. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K198" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11646,7 @@
       </c>
       <c r="E199" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F199" s="30" t="inlineStr">
@@ -11560,10 +11665,14 @@
           <t>markets/quantedge</t>
         </is>
       </c>
-      <c r="J199" s="30" t="n"/>
+      <c r="J199" s="30" t="inlineStr">
+        <is>
+          <t>portfolio-analytics.md: the page is hard-coded (72% "edge", fixed radar values) with no model or data behind it. Not built, deliberately. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K199" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11699,7 @@
       </c>
       <c r="E200" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F200" s="30" t="inlineStr">
@@ -11606,13 +11715,17 @@
       <c r="H200" s="30" t="n"/>
       <c r="I200" s="30" t="inlineStr">
         <is>
-          <t>markets/hedgefund</t>
-        </is>
-      </c>
-      <c r="J200" s="30" t="n"/>
+          <t>portfolio/risk</t>
+        </is>
+      </c>
+      <c r="J200" s="30" t="inlineStr">
+        <is>
+          <t>portfolio-analytics.md: portfolio risk metrics from real history (volatility, worst fall, Calmar, Ulcer, Sharpe, Sortino, beta, tracking error, IR) plus the page's calculators on your own numbers. The page's invented "trading DNA", override cost and BLOCK/TRADE verdicts are not ported. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K200" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11805,7 @@
       </c>
       <c r="E202" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F202" s="30" t="inlineStr">
@@ -11711,10 +11824,14 @@
           <t>markets/ca-advisor</t>
         </is>
       </c>
-      <c r="J202" s="30" t="n"/>
+      <c r="J202" s="30" t="inlineStr">
+        <is>
+          <t>portfolio-analytics.md: the page is a mock-up (random access codes, a pre-filled fake advisor, buttons that do nothing); real sharing would need a server-side sharing and permissions service that does not exist. The real part (tax dossier) is the phone's Report / ITR tools. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K202" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -11955,7 +12072,7 @@
       </c>
       <c r="E207" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F207" s="30" t="inlineStr">
@@ -11971,17 +12088,17 @@
       <c r="H207" s="30" t="n"/>
       <c r="I207" s="30" t="inlineStr">
         <is>
-          <t>components/XirrCard.tsx</t>
+          <t>portfolio/sectors</t>
         </is>
       </c>
       <c r="J207" s="30" t="inlineStr">
         <is>
-          <t>XIRR from entered purchase dates done. Sector heatmap / treemap need a sector mapping source and are not built</t>
+          <t>portfolio-analytics.md: XIRR (earlier) plus sector heatmap and treemap from Yahoo's sector names; unmapped stocks are "Unmapped", funds are one bucket, no-price holdings are grey not 0%. HHI and effective N ported. Web preview only. Not verified on a device.</t>
         </is>
       </c>
       <c r="K207" s="30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12125,7 @@
       </c>
       <c r="E208" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F208" s="30" t="inlineStr">
@@ -12024,13 +12141,17 @@
       <c r="H208" s="30" t="n"/>
       <c r="I208" s="30" t="inlineStr">
         <is>
-          <t>portfolio/quant</t>
-        </is>
-      </c>
-      <c r="J208" s="30" t="n"/>
+          <t>portfolio/simulate, portfolio/risk</t>
+        </is>
+      </c>
+      <c r="J208" s="30" t="inlineStr">
+        <is>
+          <t>portfolio-analytics.md: seeded Monte Carlo cone from assumptions you type (placeholders labelled) and a one-factor (market) regression vs Nifty 50. Multi-factor (Fama-French) not built: no published Indian factor returns; the website's version is estimated from sector composition, not a regression. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K208" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12178,7 @@
       </c>
       <c r="E209" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F209" s="30" t="inlineStr">
@@ -12076,10 +12197,14 @@
           <t>portfolio/research</t>
         </is>
       </c>
-      <c r="J209" s="30" t="n"/>
+      <c r="J209" s="30" t="inlineStr">
+        <is>
+          <t>portfolio-analytics.md: news matched to holdings with the feed's own sentiment labels, valuation table (P/E, P/B, EPS), opt-in peers. Promoter trend NOT built: no shareholding source, and the website table is hard-coded and a quarter old. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K209" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12122,17 +12247,17 @@
       <c r="H210" s="30" t="n"/>
       <c r="I210" s="30" t="inlineStr">
         <is>
-          <t>app/tracker/watchlist.tsx</t>
+          <t>market/screener</t>
         </is>
       </c>
       <c r="J210" s="30" t="inlineStr">
         <is>
-          <t>Watchlist done (price at add, honest offline). Screener needs a backend and is not built</t>
+          <t>portfolio-analytics.md: watchlist (earlier) plus screener filters on backend fundamentals (sector, P/E, P/B, the Deep Value rule, parity-tested; a missing figure never passes). Presets needing ROE, debt/equity, dividend yield, revenue growth are not built (no data). Not verified on a device.</t>
         </is>
       </c>
       <c r="K210" s="30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12333,7 @@
       </c>
       <c r="E212" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F212" s="30" t="inlineStr">
@@ -12229,12 +12354,12 @@
       </c>
       <c r="J212" s="30" t="inlineStr">
         <is>
-          <t>Standalone app; own sync via a vault id</t>
+          <t>trade-journal.md: log, edit, analytics, psychology as counts only, CSV / broker trade book / website-backup import with preview, dedupe and undo, CSV export. Device-only from cloud sync (finos_sync_never_ prefix). OCR scan of broker screenshots NOT built (needs an OCR dependency or backend and a privacy decision). Broker file formats untested on real files. Many website analytics (Sharpe, Kelly, VaR, scores, XP) deliberately not ported. Not verified on a device.</t>
         </is>
       </c>
       <c r="K212" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12261,7 +12386,7 @@
       </c>
       <c r="E213" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F213" s="30" t="inlineStr">
@@ -12282,12 +12407,12 @@
       </c>
       <c r="J213" s="30" t="inlineStr">
         <is>
-          <t>Separate Vite+Express service; npm advisories open</t>
+          <t>The headlines part is on the phone: app/market/news.tsx (see M-19) via the arya-ai backend's news route, with an honest offline state. The separate News1 app (Vite + Express service, its own sources and npm advisories) is not ported.</t>
         </is>
       </c>
       <c r="K213" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12492,7 @@
       </c>
       <c r="E215" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F215" s="30" t="inlineStr">
@@ -12388,12 +12513,12 @@
       </c>
       <c r="J215" s="30" t="inlineStr">
         <is>
-          <t>Ranking: js/arya-pulse-rank.js</t>
+          <t>arya-tabs.md: the website has 27 ranked widgets (not 24); 17 are on the phone (added net worth timeline, wealth velocity from an on-device history, Monte Carlo "will my money last"); 10 are left out with a reason each (assumption-driven or no source), listed in lib/pulseCards.ts. Not verified on a device.</t>
         </is>
       </c>
       <c r="K215" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12545,7 @@
       </c>
       <c r="E216" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F216" s="30" t="inlineStr">
@@ -12436,13 +12561,17 @@
       <c r="H216" s="30" t="n"/>
       <c r="I216" s="30" t="inlineStr">
         <is>
-          <t>arya/plan</t>
-        </is>
-      </c>
-      <c r="J216" s="30" t="n"/>
+          <t>arya/plan, arya/map, arya/life</t>
+        </is>
+      </c>
+      <c r="J216" s="30" t="inlineStr">
+        <is>
+          <t>arya-tabs.md: Plan (8 steps, "needs a figure" when unrecorded), Map (allocation from recorded assets), Life (timeline of declared events and goal dates). No assumed income, age or return. Website age-benchmark targets not built. Web preview only. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K216" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12598,7 @@
       </c>
       <c r="E217" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F217" s="30" t="inlineStr">
@@ -12485,13 +12614,17 @@
       <c r="H217" s="30" t="n"/>
       <c r="I217" s="30" t="inlineStr">
         <is>
-          <t>arya/agent</t>
-        </is>
-      </c>
-      <c r="J217" s="30" t="n"/>
+          <t>arya/cal, arya/india, arya/agent</t>
+        </is>
+      </c>
+      <c r="J217" s="30" t="inlineStr">
+        <is>
+          <t>arya-tabs.md: Cal (upcoming dates, 26-week spending heatmap), India (income-tax rules with source and year; the website's unsourced state cost-of-life map is NOT ported), Agent (tool loop screen). Rules are FY 2025-26 as coded; the screen warns when today's FY is later. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K217" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12518,7 +12651,7 @@
       </c>
       <c r="E218" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F218" s="30" t="inlineStr">
@@ -12539,12 +12672,12 @@
       </c>
       <c r="J218" s="30" t="inlineStr">
         <is>
-          <t>Backend tools exist; phone has no tool loop</t>
+          <t>arya-tabs.md: a visible phone tool loop with 44 tools (recorded figures, calculator hub, public lookups); every call is listed, results carry source and time, off switch. A model-chosen tool loop is NOT built (needs native tool calling on /api/chat) and personas and run history are not built. Not verified on a device.</t>
         </is>
       </c>
       <c r="K218" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12704,7 @@
       </c>
       <c r="E219" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F219" s="30" t="inlineStr">
@@ -12590,10 +12723,14 @@
           <t>arya/memory</t>
         </is>
       </c>
-      <c r="J219" s="30" t="n"/>
+      <c r="J219" s="30" t="inlineStr">
+        <is>
+          <t>Verified; chat can now write a note through the memory store's refusal rules, the Life tab shows life events with what each changes. Switches default off. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K219" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12696,12 +12833,12 @@
       </c>
       <c r="J221" s="30" t="inlineStr">
         <is>
-          <t>Mic permission is declared in app.json; no feature built</t>
+          <t>Not built. The microphone permission is not declared: RECORD_AUDIO is blocked in app.json and a test fails if a microphone, speech or camera permission returns (R-17).</t>
         </is>
       </c>
       <c r="K221" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12865,7 @@
       </c>
       <c r="E222" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F222" s="30" t="inlineStr">
@@ -12747,10 +12884,14 @@
           <t>arya/</t>
         </is>
       </c>
-      <c r="J222" s="30" t="n"/>
+      <c r="J222" s="30" t="inlineStr">
+        <is>
+          <t>arya-tabs.md: Money AI page = the Arya tab (A-01); the chatbot brain is a server-side proxy the phone already reaches through /api/chat; RAG filings cannot be honest because no NSE/BSE filings are indexed (only regulation and FIN-OS page documents). Backend request in docs/PENDING.md U14. Not verified on a device.</t>
+        </is>
+      </c>
       <c r="K222" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -13063,12 +13204,12 @@
       </c>
       <c r="J228" s="30" t="inlineStr">
         <is>
-          <t>Planner unit-tested (11 cases); permission flow + OS scheduling built but NOT verified on a device (needs R-08/R-09). Local only, no push token.</t>
+          <t>Planner unit-tested (11 cases); the explain-first permission flow (lib/permissions.ts, permissionPrompt) and OS scheduling are built but NOT verified on a device (needs R-08/R-09; checklist rows D-20..D-26). Local only, no push token; scheduled and delivered notices are cleared by Erase.</t>
         </is>
       </c>
       <c r="K228" s="30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13236,7 @@
       </c>
       <c r="E229" s="30" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F229" s="30" t="inlineStr">
@@ -13116,12 +13257,12 @@
       </c>
       <c r="J229" s="30" t="inlineStr">
         <is>
-          <t>Nudges done (only from recorded facts, dismissible). Persona greetings and the status strip not built</t>
+          <t>Home (app/(tabs)/dashboard.tsx, lib/persona.ts, components/PersonaStrip.tsx): time-of-day greeting with the first name only when one is recorded (no stand-in name), 'N-day streak' from day two, and a strip of savings rate, net worth and Money Score, each only when recorded; the cross hides it and Settings brings it back (finos_persona_mobile, device-only). Nudges as before. An honest subset of FinosPersona: left out on purpose are the Financial DNA archetype and life-stage labels, the Health score chip (it rests on a neutral DNA baseline and a 60,000 income fallback), FIRE % and the trade-journal win rate. Web preview only, not a device.</t>
         </is>
       </c>
       <c r="K229" s="30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -13871,12 +14012,12 @@
       <c r="I244" s="30" t="n"/>
       <c r="J244" s="30" t="inlineStr">
         <is>
-          <t>App side built and tested (erase phone, delete cloud copy, delete account via RPC). Needs supabase/delete_account.sql run on the live project before 'Delete my account' works.</t>
+          <t>App side built and tested: one erase flow (signs out first, clears memory, notifications, cache files, secure storage, then checks for leftovers), delete the cloud copy, delete account via RPC. supabase/delete_account.sql now also deletes the rows of tables with no cascade (alerts, push_subscriptions, alert_preferences, health_score_history, memory_embeddings, user_behavior, document_ai_log, couple links), guarded by a test and proved in a throwaway PostgreSQL (scripts/release-sql-check.py), but NOT run on the live project. Owner decision open: deleting a couple link also removes the partner's shared goals.</t>
         </is>
       </c>
       <c r="K244" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -14020,12 +14161,12 @@
       <c r="I247" s="30" t="n"/>
       <c r="J247" s="30" t="inlineStr">
         <is>
-          <t>Everything so far ran in the web preview</t>
+          <t>Everything so far ran in the web preview. docs/DEVICE_TEST_CHECKLIST.md lists what needs a phone (sections A-I); no row has been run.</t>
         </is>
       </c>
       <c r="K247" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -14073,12 +14214,12 @@
       </c>
       <c r="J248" s="30" t="inlineStr">
         <is>
-          <t>Planner unit-tested (11 cases); permission flow + OS scheduling built but NOT verified on a device (needs R-08/R-09). Local only, no push token.</t>
+          <t>Explain-first flow built for reminders and the biometric switch (the OS prompt appears only after the person agrees on our screen); planner unit-tested; denial path shows a plain message and the switch does not claim 'on'. NOT verified on a device (needs R-08/R-09; checklist rows D-20..D-24).</t>
         </is>
       </c>
       <c r="K248" s="30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -14105,7 +14246,7 @@
       </c>
       <c r="E249" s="30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F249" s="30" t="inlineStr">
@@ -14122,12 +14263,12 @@
       <c r="I249" s="30" t="n"/>
       <c r="J249" s="30" t="inlineStr">
         <is>
-          <t>Placeholders only</t>
+          <t>Built: icon, adaptive icon (with monochrome layer), splash, notification icon, Play 512 icon and feature graphic (mobile/scripts/release-assets.py, reproducible, tested for size, alpha and safe zones), 28 store screenshots from the web preview with a synthetic profile (not device captures, taken before the Oct 17 Budget / Goals clipping fix), and listing text in docs/STORE_LISTING.md. Not done: legal operator and URLs, store accounts and forms, screenshots from a device (all need the owner; PENDING U6/U7).</t>
         </is>
       </c>
       <c r="K249" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -14224,12 +14365,12 @@
       <c r="I251" s="30" t="n"/>
       <c r="J251" s="30" t="inlineStr">
         <is>
-          <t>On-device redacted crash notes, error boundary, Diagnostics screen and opt-in screen counts (default off); nothing is sent automatically and there is no crash service. Fatal native crashes may kill the process before a note is written.</t>
+          <t>On-device redacted crash notes, error boundary, Diagnostics screen and opt-in screen counts (default off); nothing is sent automatically and there is no crash service. Fatal native crashes may kill the process before a note is written. Play Android vitals and App Store Connect remain the only automatic crash signals. Not run on a device.</t>
         </is>
       </c>
       <c r="K251" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -14381,12 +14522,12 @@
       <c r="I254" s="30" t="n"/>
       <c r="J254" s="30" t="inlineStr">
         <is>
-          <t>Needs the user's Supabase dashboard login</t>
+          <t>Needs the user's Supabase dashboard login. The file has been rewritten (see R-06) and passes its guard test; it has not been run on any project.</t>
         </is>
       </c>
       <c r="K254" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14576,7 @@
       </c>
       <c r="K255" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -15204,7 +15345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="16" min="1" max="1"/>
@@ -16078,6 +16219,342 @@
       </c>
       <c r="E33" s="16" t="n">
         <v>359</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>L-01..L-26, T-36</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Learn: 25 lessons bundled in the app with on-device progress, search entries, Knowledge pillar follows the website</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Per docs/agent-notes/learn.md: learn.test.mts (14) incl. a golden test against js/finos-health-score.js; preview run. Logged here on 2026-10-17 from the agent note; not re-run line by line</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>T-19, M-21</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Insurance hub (cover types, questions, your policies beside them) and mutual-fund search, detail and compare</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Per docs/agent-notes/insurance-mf.md: parity with js/mf-intelligence.js, extraction script check; preview run. Logged from the note</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>A-02, A-05, A-06</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>PULSE feed (14 of 27 widgets), Arya memory and life events, local Arya tools</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Per docs/agent-notes/arya-pulse.md: ranking vs js/arya-pulse-rank.js on 600 contexts, 33 positive + 15 negative intent phrases; preview run. Logged from the note</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>M-04, M-05, M-06, M-15, M-19</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Market research: stock and fund detail, screener, news with stated sentiment, commodities, FX, crypto lists; offline cache with time</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Per docs/agent-notes/market-data.md: marketData tests (33) + backend pytest (30, stubs only); preview run. Logged from the note</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>T-01, T-02, T-10, T-18, T-38, T-39</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Growth projection, spending forecast, life goals planner, couple finance, benchmarks, your own calendar dates</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Per docs/agent-notes/planners.md: parity vs the website cores, mutation checks, smoke 6 screens x 4 runs = 0; theme audit 0 low-contrast. Logged from the note</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>P-08, P-11, R-06, R-10, R-13, P-10</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>Trust platform: onboarding, feedback, crash notes, erase flow, explain-first permissions, lock hardening, Google sign-in code path (hidden)</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Per docs/agent-notes/trust-platform.md: redaction and feedback parity, erase and lock tests, mutation checks. Google sign-in unit-tested with fakes only. Logged from the note</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>R-11, R-17</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Release pack: brand assets, store screenshots, release config guards, store copy, runbook, SQL harness</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>Per docs/agent-notes/release-pack.md: releaseAssets (7) + releaseConfig (11) tests; SQL run in a throwaway PostgreSQL 16. Logged from the note</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>(robustness, no row)</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Stored and received data of the wrong shape never crashes a screen or becomes NaN; a failed read is never saved over data; backup restore all-or-nothing</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Per docs/agent-notes/mobile-robustness.md: corruptData.test.mts (170) with four mutation checks; corrupt-data web smoke over every route x 5 variants = 0</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>P-07, R-11, R-06, A-02, A-05, A-06</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Cross-links (Budget to Forecast, Goals to Life goals, Portfolio to Growth, Insurance to hub, Watchlist rows to research, feedback on the Money Score); Home facts strip and honest greeting; assumed ages removed; Budget / Goals input clipping and Portfolio title wrap fixed; privacy line for kept-aside values; Hindi first pass; tracker rows audited against the code</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>persona.test.mts (new), privacy and logic tests extended with mutation checks; tsc clean; Playwright run of each new link at 430 px; smoke-routes and theme-audit on the changed screens (see docs/agent-notes/mobile-polish.md). Web preview only, nothing on a device</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>L-22, L-24..L-51</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>Learn wave 2: 5 new lessons (mindset-sim case studies, impact stories, decision, clarity, life-wealth), line provenance on every quoted passage, honest stub pages for the 22 interactive website pages (hub / redirect / not on the phone, each with its reason). Merged from docs/agent-notes/learn2.md.</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>learn2.test.mts (9), learn.test.mts; extract-learn.py --check; smoke on the new routes (per the note, not re-run for each)</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>A-02..A-06, A-09</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Arya Plan / Map / Life / Cal / India / Agent tabs, 44-tool visible tool loop, PULSE 17 of 27, net-worth history. A-09 not built (reasons). Merged from docs/agent-notes/arya-tabs.md.</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>aryaIntent, aryaToolbox, aryaServerTools, aryaAgent, aryaTabs tests; smoke 8 screens x 4 runs 0 problems (per the note)</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>M-07, M-08, M-09, M-14, M-16, M-17, M-18, M-20, S-04..S-07</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>Crypto / commodity / forex detail with history, Market map, Options calculator, Portfolio analytics (sectors and treemap, risk, simulation, research), screener filters. M-17 and M-20 not built (static placeholders / mock-up). Merged from docs/agent-notes/portfolio-analytics.md.</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>Parity tests against the website's own functions in a vm (per the note); smoke per the note</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>S-09</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>Trade journal: log, analytics, psychology counts, CSV / broker / backup import with undo, export; device-only from sync. OCR not built. Merged from docs/agent-notes/trade-journal.md.</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>tradeJournal (39), tradeJournalImport (12), tradeJournal.parity (20: 12 pass, 8 todo = website defects); mutation checks</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>(final integration, no row)</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Shared files: search entries + index guard, privacy notice and data inventory, Hindi first pass, route samples, Home / Portfolio links. Health score no longer computed from no data (Not enough data; only recorded areas scored, missing named). Safe-area insets, screen-title headings, dark purple text, 200% layout fixes. See docs/agent-notes/final-integration.md.</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>npm test + tsc + smoke-routes + theme-audit on a fresh Metro (see the note); nothing on a device</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>1057</v>
       </c>
     </row>
   </sheetData>
